--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Composite_Decomposition_Map" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'260219_DUM_HSV'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'260219_DUM_PSV'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'260219_DUM_VRN'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'260217_SKLAD'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'260219_DUM_HSV'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'260219_DUM_PSV'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'260219_DUM_VRN'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'260217_SKLAD'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -149,7 +149,7 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -1595,19 +1595,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1638,25 +1639,30 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Vzorec / Zdroj výměry</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>URS kód kandidát</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Parent frozen item_id</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Realizuje skladbu</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Pozn.</t>
         </is>
@@ -1677,6 +1683,7 @@
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n">
@@ -1702,21 +1709,26 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
+          <t>L=10 × W=3.5 (zahrada zóna pro BV + dvorek)</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
           <t>121101101</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.001</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -1746,21 +1758,26 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
+          <t>L=10 × W=1.2 × H=1.05 (pata BV 1200 mm × hloubka pod základovou spárou)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
           <t>132201101</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.002</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -1790,21 +1807,26 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
+          <t>L=2.5 × W=2.0 × H=1.2 (dvorek odkop)</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
           <t>131201101</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.003</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -1832,27 +1854,31 @@
       <c r="E6" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="15">
+        <f> HSV1.004 plocha dvorku 30 m²</f>
+        <v/>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.004 → HSV1.004a</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Anglický dvorek</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Dlažba NA LOŽI (596 família) — ne na terče. Leaf dle typu dlažby (zámková 596211 / velkoformát 596811) — verify u dodavatele.</t>
         </is>
@@ -1880,27 +1906,31 @@
       <c r="E7" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="15">
+        <f> HSV1.004 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.004 → HSV1.004b</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>Anglický dvorek</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Podklad ze štěrkodrti (564 família).</t>
         </is>
@@ -1928,27 +1958,31 @@
       <c r="E8" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="15">
+        <f> HSV1.004 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.004 → HSV1.004c</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>Anglický dvorek</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.</t>
         </is>
@@ -1976,27 +2010,31 @@
       <c r="E9" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="15">
+        <f> HSV1.005 plocha terasy 30 m²</f>
+        <v/>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>636311</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.005 → HSV1.005a</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>A2 KOREKCE: dlaždice NA TERČE → 636311 família (NE 762 carpentry — stará dřevěná kompozice nahrazena betonovými dlaždicemi na terče per Alexander Phase 5).</t>
         </is>
@@ -2024,27 +2062,31 @@
       <c r="E10" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.005 → HSV1.005b</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr">
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Podklad štěrkopísek (564 família).</t>
         </is>
@@ -2072,27 +2114,31 @@
       <c r="E11" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.005 → HSV1.005c</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Podklad štěrkodrť (564 família).</t>
         </is>
@@ -2120,27 +2166,31 @@
       <c r="E12" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>693</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.005 → HSV1.005d</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Geotextilie (693 família) nebo zahrnuto v 564.</t>
         </is>
@@ -2170,21 +2220,26 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
+          <t>obvod rýh BV 2×(10+1.2) × hloubka 1.6</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
           <t>151101101</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.006</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2212,19 +2267,23 @@
       <c r="E14" s="19" t="n">
         <v>18.6</v>
       </c>
-      <c r="F14" s="18" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="F14" s="18">
+        <f> V hloubení rýh BV + figura dvorek (12.6 + 6.0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.007</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr"/>
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2254,21 +2313,26 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
+          <t>podlahova_plocha_1NP × 0.15 m štěrkové lože (uvažovat 83 m² × 0.15)</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
           <t>174101101</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.008</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2296,23 +2360,27 @@
       <c r="E16" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="15">
+        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <v/>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.015 → HSV1.015a</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr"/>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr"/>
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).</t>
         </is>
@@ -2340,23 +2408,27 @@
       <c r="E17" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="15">
+        <f> HSV1.015 délka drenáže 12 m</f>
+        <v/>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.015 → HSV1.015b</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr"/>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr"/>
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Obsyp drenáže (212/174 família).</t>
         </is>
@@ -2384,23 +2456,27 @@
       <c r="E18" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="15">
+        <f> HSV1.015 délka 12 m</f>
+        <v/>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>693</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.015 → HSV1.015c</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr"/>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr"/>
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Geotextilie obal + napojení (693 família).</t>
         </is>
@@ -2421,6 +2497,7 @@
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -2446,21 +2523,26 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
+          <t>0.25 × 1.20 × 10 = 3.0</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
           <t>274321321</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.001</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2490,21 +2572,26 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
+          <t>0.25 × 2.05 × 10 = 5.13</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
           <t>274321321</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.002</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2534,21 +2621,26 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
+          <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
           <t>631311115</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.003</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2578,21 +2670,26 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
+          <t>(3.0+5.13) × 120 = 976</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.004</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2620,19 +2717,24 @@
       <c r="E24" s="19" t="n">
         <v>13.2</v>
       </c>
-      <c r="F24" s="18" t="inlineStr"/>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>1.20 × 10 × 1.10 přesah = 13.2</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.005</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr"/>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr"/>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2662,21 +2764,26 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
+          <t>viditelná plocha BV pro ošetřování ~53</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
           <t>279351102</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.006</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2706,21 +2813,26 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
+          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
           <t>274321311</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.007</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2750,21 +2862,26 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
+          <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
           <t>631311115</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.008</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2794,21 +2911,26 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
+          <t>3.1 × 100 = 310</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.009</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2838,25 +2960,30 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
+          <t>104.4 m² × 0.06 m = 6.26</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
           <t>274321111</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.010</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2886,25 +3013,30 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
+          <t>104.4 m² × 4.4 kg/m² = 459</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
           <t>273362441</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.011</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2934,25 +3066,30 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
+          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
           <t>273321311</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.012</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2982,25 +3119,30 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
+          <t>11.0 × 75 = 825</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.013</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3021,6 +3163,7 @@
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
       <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -3046,25 +3189,30 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
+          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
           <t>311232511</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.001</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>S01, S02</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3094,25 +3242,30 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
+          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
           <t>311321411</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.002</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3142,25 +3295,30 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
+          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
           <t>317143112</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.003</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3190,25 +3348,30 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
+          <t>8 otvorů × 2 strany = 16 uložení</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
           <t>317242421</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.004</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3238,25 +3401,30 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
+          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
           <t>767131120</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>✓ cross-disc</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.005</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3284,23 +3452,27 @@
       <c r="E39" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="11">
+        <f> počet překladů (po jednom podstojkování per otvor)</f>
+        <v/>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>962081120</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.006</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3330,25 +3502,30 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
+          <t>podlahova_plocha × 0.4 (typický rozsah příček 30-50%)</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
           <t>342241211</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.007</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3369,6 +3546,7 @@
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
@@ -3394,21 +3572,26 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
+          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.001</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3438,25 +3621,30 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
+          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.002</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3486,25 +3674,30 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
+          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.003</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3534,25 +3727,30 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
+          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.004</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="K45" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3580,27 +3778,31 @@
       <c r="E46" s="12" t="n">
         <v>104.4</v>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F46" s="11">
+        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
+        <v/>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.005</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3628,27 +3830,31 @@
       <c r="E47" s="12" t="n">
         <v>104.4</v>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="11">
+        <f> plocha trapézu 104.4 m²</f>
+        <v/>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>342213131</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.006</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3678,25 +3884,30 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
+          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
           <t>974031150</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>✓ cross-disc</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.007</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3726,25 +3937,30 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
+          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
           <t>271223111</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.008</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3774,25 +3990,30 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
+          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
           <t>631321311</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.009</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3822,25 +4043,30 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
+          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
           <t>974041141</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.010</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3868,27 +4094,31 @@
       <c r="E52" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>713121121</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.011</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3916,27 +4146,31 @@
       <c r="E53" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>342213131</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.012</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="K53" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -3966,25 +4200,30 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
+          <t>100 m² × 0.05 m = 5</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
           <t>631311114</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.013</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="K54" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4012,27 +4251,31 @@
       <c r="E55" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F55" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>771421111</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.014</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr">
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4053,6 +4296,7 @@
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
       <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -4078,21 +4322,26 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
+          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
           <t>762331911</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.001</t>
         </is>
       </c>
-      <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4122,21 +4371,26 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
+          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
           <t>762331912</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.002</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4166,21 +4420,26 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
+          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
           <t>762331923</t>
         </is>
       </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.003</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="J59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4210,21 +4469,26 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
+          <t>24 krokví × 0.8 m námětek = 19.2</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
           <t>762331911</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="I60" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.004</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4254,21 +4518,26 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
+          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.005</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4298,21 +4567,26 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
+          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
+      <c r="I62" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.006</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4340,27 +4614,31 @@
       <c r="E63" s="12" t="n">
         <v>140.94</v>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F63" s="11">
+        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
+        <v/>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>762341711</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.007</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J63" s="11" t="inlineStr">
+      <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4390,25 +4668,30 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
           <t>712311101</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
+      <c r="I64" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.008</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr">
+      <c r="J64" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J64" s="11" t="inlineStr">
+      <c r="K64" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4436,27 +4719,31 @@
       <c r="E65" s="12" t="n">
         <v>140.94</v>
       </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F65" s="11">
+        <f> 141 m² (plocha krytiny krov)</f>
+        <v/>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>713131811</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.009</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
+      <c r="J65" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J65" s="11" t="inlineStr">
+      <c r="K65" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4486,25 +4773,30 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
           <t>712311111</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H66" s="11" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.010</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr">
+      <c r="J66" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J66" s="11" t="inlineStr">
+      <c r="K66" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4532,27 +4824,31 @@
       <c r="E67" s="12" t="n">
         <v>140.94</v>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F67" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>762331923</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H67" s="11" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.011</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr">
+      <c r="J67" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J67" s="11" t="inlineStr">
+      <c r="K67" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4580,27 +4876,31 @@
       <c r="E68" s="12" t="n">
         <v>140.94</v>
       </c>
-      <c r="F68" s="11" t="inlineStr">
+      <c r="F68" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>762341711</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H68" s="11" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.012</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
+      <c r="J68" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="K68" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4628,27 +4928,31 @@
       <c r="E69" s="12" t="n">
         <v>140.94</v>
       </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="F69" s="11">
+        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <v/>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>765791121</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.013</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
+      <c r="J69" s="11" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="J69" s="11" t="inlineStr">
+      <c r="K69" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4678,25 +4982,30 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
+          <t>odhad — spací patro ~5 × 5 m</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
           <t>762341711</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H70" s="11" t="inlineStr">
+      <c r="I70" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.014</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr">
+      <c r="J70" s="11" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="J70" s="11" t="inlineStr">
+      <c r="K70" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4726,21 +5035,26 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
+          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
           <t>311321411</t>
         </is>
       </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.015</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="11" t="inlineStr">
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4770,25 +5084,30 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
+          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
           <t>765791121</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H72" s="11" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.016</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr">
+      <c r="J72" s="11" t="inlineStr">
         <is>
           <t>S12b</t>
         </is>
       </c>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="K72" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4809,6 +5128,7 @@
       <c r="H73" s="9" t="n"/>
       <c r="I73" s="9" t="n"/>
       <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="n">
@@ -4834,21 +5154,26 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
           <t>962041141</t>
         </is>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H74" s="11" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.001</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr"/>
-      <c r="J74" s="11" t="inlineStr">
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4876,19 +5201,23 @@
       <c r="E75" s="19" t="n">
         <v>140.9</v>
       </c>
-      <c r="F75" s="18" t="inlineStr"/>
-      <c r="G75" s="17" t="inlineStr">
+      <c r="F75" s="18">
+        <f> plocha krytiny ~141</f>
+        <v/>
+      </c>
+      <c r="G75" s="18" t="inlineStr"/>
+      <c r="H75" s="17" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H75" s="18" t="inlineStr">
+      <c r="I75" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.002</t>
         </is>
       </c>
-      <c r="I75" s="18" t="inlineStr"/>
-      <c r="J75" s="18" t="inlineStr">
+      <c r="J75" s="18" t="inlineStr"/>
+      <c r="K75" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4918,21 +5247,26 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
           <t>962031132</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H76" s="11" t="inlineStr">
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.003</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr"/>
-      <c r="J76" s="11" t="inlineStr">
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -4960,23 +5294,27 @@
       <c r="E77" s="12" t="n">
         <v>104.4</v>
       </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="F77" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
         <is>
           <t>962041141</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H77" s="11" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.004</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr"/>
-      <c r="J77" s="11" t="inlineStr">
+      <c r="J77" s="11" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5006,21 +5344,26 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
           <t>962031132</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H78" s="11" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.005</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr"/>
-      <c r="J78" s="11" t="inlineStr">
+      <c r="J78" s="11" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5050,21 +5393,26 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
           <t>962031132</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.006</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr"/>
-      <c r="J79" s="11" t="inlineStr">
+      <c r="J79" s="11" t="inlineStr"/>
+      <c r="K79" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5094,21 +5442,26 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
           <t>781473810</t>
         </is>
       </c>
-      <c r="G80" s="13" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H80" s="11" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.007</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="11" t="inlineStr">
+      <c r="J80" s="11" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5138,21 +5491,26 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
           <t>974031132</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.008</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="J81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5182,21 +5540,26 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
           <t>974041151</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.009</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr"/>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="J82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5226,21 +5589,26 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
           <t>968071120</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.010</t>
         </is>
       </c>
-      <c r="I83" s="11" t="inlineStr"/>
-      <c r="J83" s="11" t="inlineStr">
+      <c r="J83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5270,21 +5638,26 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
           <t>725900001</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr">
+      <c r="I84" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.011</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr"/>
-      <c r="J84" s="11" t="inlineStr">
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5314,21 +5687,26 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
           <t>997013501</t>
         </is>
       </c>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H85" s="11" t="inlineStr">
+      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.012</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr"/>
-      <c r="J85" s="11" t="inlineStr">
+      <c r="J85" s="11" t="inlineStr"/>
+      <c r="K85" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5358,21 +5736,26 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
           <t>978013181</t>
         </is>
       </c>
-      <c r="G86" s="13" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H86" s="11" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.013</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr"/>
-      <c r="J86" s="11" t="inlineStr">
+      <c r="J86" s="11" t="inlineStr"/>
+      <c r="K86" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5402,21 +5785,26 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
           <t>978013181</t>
         </is>
       </c>
-      <c r="G87" s="13" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.014</t>
         </is>
       </c>
-      <c r="I87" s="11" t="inlineStr"/>
-      <c r="J87" s="11" t="inlineStr">
+      <c r="J87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5446,21 +5834,26 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
           <t>968072456</t>
         </is>
       </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H88" s="11" t="inlineStr">
+      <c r="I88" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.015</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr"/>
-      <c r="J88" s="11" t="inlineStr">
+      <c r="J88" s="11" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5490,21 +5883,26 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³, × 10 m³ buffer pro suti + manipulace = 6.0 m³</t>
+        </is>
+      </c>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
           <t>962024141</t>
         </is>
       </c>
-      <c r="G89" s="13" t="inlineStr">
+      <c r="H89" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H89" s="11" t="inlineStr">
+      <c r="I89" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.016</t>
         </is>
       </c>
-      <c r="I89" s="11" t="inlineStr"/>
-      <c r="J89" s="11" t="inlineStr">
+      <c r="J89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5534,21 +5932,26 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
           <t>961044111</t>
         </is>
       </c>
-      <c r="G90" s="13" t="inlineStr">
+      <c r="H90" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H90" s="11" t="inlineStr">
+      <c r="I90" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.017</t>
         </is>
       </c>
-      <c r="I90" s="11" t="inlineStr"/>
-      <c r="J90" s="11" t="inlineStr">
+      <c r="J90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5569,6 +5972,7 @@
       <c r="H91" s="9" t="n"/>
       <c r="I91" s="9" t="n"/>
       <c r="J91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
@@ -5594,25 +5998,30 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
+          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr">
+        <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="H92" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H92" s="11" t="inlineStr">
+      <c r="I92" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="J92" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="J92" s="11" t="inlineStr">
+      <c r="K92" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5640,27 +6049,31 @@
       <c r="E93" s="16" t="n">
         <v>276.7</v>
       </c>
-      <c r="F93" s="15" t="inlineStr">
+      <c r="F93" s="15">
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
+        <v/>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
+      <c r="H93" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H93" s="15" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
-      <c r="I93" s="15" t="inlineStr">
+      <c r="J93" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="J93" s="15" t="inlineStr">
+      <c r="K93" s="15" t="inlineStr">
         <is>
           <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.</t>
         </is>
@@ -5688,27 +6101,31 @@
       <c r="E94" s="16" t="n">
         <v>276.7</v>
       </c>
-      <c r="F94" s="15" t="inlineStr">
+      <c r="F94" s="15">
+        <f> HSV7.002 plocha 276.7 m²</f>
+        <v/>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="G94" s="14" t="inlineStr">
+      <c r="H94" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H94" s="15" t="inlineStr">
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.002 → HSV7.002b</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="J94" s="15" t="inlineStr">
+      <c r="K94" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.</t>
         </is>
@@ -5736,27 +6153,31 @@
       <c r="E95" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="F95" s="15" t="inlineStr">
+      <c r="F95" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G95" s="15" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="G95" s="14" t="inlineStr">
+      <c r="H95" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H95" s="15" t="inlineStr">
+      <c r="I95" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
-      <c r="I95" s="15" t="inlineStr">
+      <c r="J95" s="15" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="J95" s="15" t="inlineStr">
+      <c r="K95" s="15" t="inlineStr">
         <is>
           <t>Sokl XPS lepení + soklový profil (713/622 família).</t>
         </is>
@@ -5784,27 +6205,31 @@
       <c r="E96" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="F96" s="15" t="inlineStr">
+      <c r="F96" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
         <is>
           <t>781</t>
         </is>
       </c>
-      <c r="G96" s="14" t="inlineStr">
+      <c r="H96" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H96" s="15" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.003 → HSV7.003b</t>
         </is>
       </c>
-      <c r="I96" s="15" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="J96" s="15" t="inlineStr">
+      <c r="K96" s="15" t="inlineStr">
         <is>
           <t>Cihelný obklad spárovaný (781 família obklady).</t>
         </is>
@@ -5832,27 +6257,31 @@
       <c r="E97" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F97" s="15" t="inlineStr">
+      <c r="F97" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="G97" s="14" t="inlineStr">
+      <c r="H97" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H97" s="15" t="inlineStr">
+      <c r="I97" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004a</t>
         </is>
       </c>
-      <c r="I97" s="15" t="inlineStr">
+      <c r="J97" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="J97" s="15" t="inlineStr">
+      <c r="K97" s="15" t="inlineStr">
         <is>
           <t>Špalety EPS přesah (622 família).</t>
         </is>
@@ -5880,27 +6309,31 @@
       <c r="E98" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F98" s="15" t="inlineStr">
+      <c r="F98" s="15">
+        <f> HSV7.004 obvod 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="G98" s="14" t="inlineStr">
+      <c r="H98" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H98" s="15" t="inlineStr">
+      <c r="I98" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="I98" s="15" t="inlineStr">
+      <c r="J98" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="J98" s="15" t="inlineStr">
+      <c r="K98" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).</t>
         </is>
@@ -5930,25 +6363,30 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
           <t>622221221</t>
         </is>
       </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.005</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="J99" s="11" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="K99" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -5978,40 +6416,45 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
+          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="G100" s="13" t="inlineStr">
+      <c r="H100" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H100" s="11" t="inlineStr">
+      <c r="I100" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr">
+      <c r="J100" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="J100" s="11" t="inlineStr">
+      <c r="K100" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <mergeCells count="7">
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A91:J91"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A56:K56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6023,19 +6466,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6066,25 +6510,30 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Vzorec / Zdroj výměry</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>URS kód kandidát</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Parent frozen item_id</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Realizuje skladbu</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Pozn.</t>
         </is>
@@ -6105,6 +6554,7 @@
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n">
@@ -6130,21 +6580,26 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
+          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
           <t>712311101</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV71.001</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6174,21 +6629,26 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
+          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
           <t>712381111</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV71.002</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6216,19 +6676,24 @@
       <c r="E5" s="19" t="n">
         <v>40.5</v>
       </c>
-      <c r="F5" s="18" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>260219_dum.PSV71.003</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr"/>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr"/>
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6249,6 +6714,7 @@
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n"/>
       <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
@@ -6272,19 +6738,24 @@
       <c r="E7" s="19" t="n">
         <v>177.5</v>
       </c>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>260219_dum.PSV71.001</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr"/>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr"/>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6312,19 +6783,23 @@
       <c r="E8" s="19" t="n">
         <v>104.4</v>
       </c>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="F8" s="18">
+        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
+        <v/>
+      </c>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>260219_dum.PSV71.002</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr"/>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6345,6 +6820,7 @@
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -6370,21 +6846,26 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
           <t>722290515</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.001</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6414,21 +6895,26 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
+          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
           <t>722172011</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.002</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6458,21 +6944,26 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
+          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>721174021</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.003</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6502,21 +6993,26 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
+          <t>1× vana (DXF sanit_vana)</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.004 → PSV72.004a</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr"/>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr"/>
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6546,21 +7042,26 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
+          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.004 → PSV72.004b</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr"/>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr"/>
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6590,21 +7091,26 @@
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
+          <t>1× WC (TZ standard)</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.004 → PSV72.004c</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr"/>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr"/>
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6634,21 +7140,26 @@
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
+          <t>1× umyvadlo (DXF)</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.005 → PSV72.005a</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr"/>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr"/>
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6678,21 +7189,26 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
+          <t>1× WC (TZ standard)</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.005 → PSV72.005b</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr"/>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr"/>
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6722,21 +7238,26 @@
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
+          <t>1× sprcha (TZ standard)</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.005 → PSV72.005c</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr"/>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr"/>
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6766,21 +7287,26 @@
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
+          <t>1× WC (DXF)</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.006 → PSV72.006a</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr"/>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J19" s="15" t="inlineStr"/>
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6810,21 +7336,26 @@
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
+          <t>1× umyvadlo (TZ standard)</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.006 → PSV72.006b</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr"/>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr"/>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6854,21 +7385,26 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
+          <t>1× sprcha (TZ standard)</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.006 → PSV72.006c</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr"/>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr"/>
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>Zařizovací předmět (725 família).</t>
         </is>
@@ -6898,21 +7434,26 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
+          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
           <t>725840111</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.007</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6942,21 +7483,26 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
+          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.008 → PSV72.008a</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr"/>
-      <c r="J23" s="15" t="inlineStr">
+      <c r="J23" s="15" t="inlineStr"/>
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>Armatura (725 família).</t>
         </is>
@@ -6986,21 +7532,26 @@
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
+          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.008 → PSV72.008b</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr"/>
-      <c r="J24" s="15" t="inlineStr">
+      <c r="J24" s="15" t="inlineStr"/>
+      <c r="K24" s="15" t="inlineStr">
         <is>
           <t>Baterie (725 família).</t>
         </is>
@@ -7030,21 +7581,26 @@
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
+          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.008 → PSV72.008c</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr"/>
-      <c r="J25" s="15" t="inlineStr">
+      <c r="J25" s="15" t="inlineStr"/>
+      <c r="K25" s="15" t="inlineStr">
         <is>
           <t>Baterie termostat (725 família).</t>
         </is>
@@ -7074,21 +7630,26 @@
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
+          <t>2× kuchyně (1.06 + 3.05)</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.008 → PSV72.008d</t>
         </is>
       </c>
-      <c r="I26" s="15" t="inlineStr"/>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J26" s="15" t="inlineStr"/>
+      <c r="K26" s="15" t="inlineStr">
         <is>
           <t>Dřezová baterie (725 família).</t>
         </is>
@@ -7118,21 +7679,26 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
           <t>732419411</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.009</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7162,21 +7728,26 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
           <t>732429211</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.010</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7206,21 +7777,26 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
           <t>725211101</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.004.A</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7250,21 +7826,26 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
           <t>725311111</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.004.B</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7294,21 +7875,26 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
           <t>725111101</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.004.C</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7338,21 +7924,26 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
           <t>725311111</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.005.A</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="11" t="inlineStr"/>
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7382,21 +7973,26 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
           <t>725221201</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.005.B</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7426,21 +8022,26 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
           <t>725111101</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.005.C</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7470,21 +8071,26 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
           <t>725111101</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.006.A</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7514,21 +8120,26 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
           <t>725311111</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.006.B</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7558,21 +8169,26 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
           <t>725221201</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV72.006.C</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7593,6 +8209,7 @@
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -7618,21 +8235,26 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
           <t>733241011</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.001</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7660,23 +8282,27 @@
       <c r="E40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="11">
+        <f> ks kamen</f>
+        <v/>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>733281011</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.002</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr"/>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7706,21 +8332,26 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
           <t>733131221</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.003</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr"/>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7750,21 +8381,26 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
           <t>733241011</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.004</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7794,21 +8430,26 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
           <t>733425211</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.005</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7838,21 +8479,26 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
           <t>733425221</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.006</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7882,21 +8528,26 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — komín revize a úpravy stávajícího</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
           <t>734262122</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.007</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7926,21 +8577,26 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
           <t>733111021</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV73.008</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr"/>
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -7961,6 +8617,7 @@
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
       <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
@@ -7986,21 +8643,26 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
+          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
           <t>764312235</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.001</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr"/>
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8028,23 +8690,27 @@
       <c r="E49" s="12" t="n">
         <v>20.8</v>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F49" s="11">
+        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
+        <v/>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>764218201</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.002</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8074,21 +8740,26 @@
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
+          <t>4 svody × ~7 m výška = 28 bm</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
           <t>764</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.003 → PSV76.003a</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr"/>
-      <c r="J50" s="15" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr"/>
+      <c r="K50" s="15" t="inlineStr">
         <is>
           <t>Klempířské svody (764 família).</t>
         </is>
@@ -8116,23 +8787,27 @@
       <c r="E51" s="16" t="n">
         <v>15.5</v>
       </c>
-      <c r="F51" s="15" t="inlineStr">
+      <c r="F51" s="15">
+        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
+        <v/>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>764</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H51" s="15" t="inlineStr">
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.003 → PSV76.003b</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr"/>
-      <c r="J51" s="15" t="inlineStr">
+      <c r="J51" s="15" t="inlineStr"/>
+      <c r="K51" s="15" t="inlineStr">
         <is>
           <t>Klempířské žlaby (764 família).</t>
         </is>
@@ -8162,21 +8837,26 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
+          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
           <t>764315235</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.004</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8197,6 +8877,7 @@
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
       <c r="J53" s="9" t="n"/>
+      <c r="K53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
@@ -8222,21 +8903,26 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
+          <t>2 schodiště × ~8 stupňů = 16</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
           <t>766811111</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.001</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8266,21 +8952,26 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
+          <t>DXF dum_situace PLOT_DREVENY_04 = 57 INSERTs (timber pattern blocks) → odhad terasa ~30 m². NEPOUŽITELNÉ pro 3.NP biodeska (PLOT_DREVENY_04 v dum_DPZ = 0).</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
           <t>771474112</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.002</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8301,6 +8992,7 @@
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
       <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -8326,21 +9018,26 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.001</t>
         </is>
       </c>
-      <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8370,21 +9067,26 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.002</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8414,21 +9116,26 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.003</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="J59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8458,21 +9165,26 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="I60" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.004</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8502,21 +9214,26 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.005</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8546,21 +9263,26 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
+      <c r="I62" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.006</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8590,21 +9312,26 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
           <t>766621011</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.007</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr"/>
-      <c r="J63" s="11" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8634,21 +9361,26 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
           <t>766631211</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
+      <c r="I64" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.008</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr"/>
-      <c r="J64" s="11" t="inlineStr">
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8678,21 +9410,26 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — vstupní plastové dveře</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
           <t>766682111</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.009</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr"/>
-      <c r="J65" s="11" t="inlineStr">
+      <c r="J65" s="11" t="inlineStr"/>
+      <c r="K65" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8722,21 +9459,26 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
           <t>766660035</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H66" s="11" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.010</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr"/>
-      <c r="J66" s="11" t="inlineStr">
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8766,21 +9508,26 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
           <t>766694112</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H67" s="11" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.013</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr"/>
-      <c r="J67" s="11" t="inlineStr">
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8810,21 +9557,26 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
           <t>764811112</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H68" s="11" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.014</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8845,6 +9597,7 @@
       <c r="H69" s="9" t="n"/>
       <c r="I69" s="9" t="n"/>
       <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="n">
@@ -8870,21 +9623,26 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
           <t>767531111</t>
         </is>
       </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H70" s="11" t="inlineStr">
+      <c r="I70" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.001</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr"/>
-      <c r="J70" s="11" t="inlineStr">
+      <c r="J70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8914,21 +9672,26 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
           <t>767531111</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.002</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="11" t="inlineStr">
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -8958,21 +9721,26 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
+          <t>2 vstupy</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
           <t>767532111</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H72" s="11" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.003</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr"/>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9002,21 +9770,26 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
           <t>767163115</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H73" s="11" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV76.004</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr"/>
-      <c r="J73" s="11" t="inlineStr">
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9037,6 +9810,7 @@
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="9" t="n"/>
       <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="n">
@@ -9062,21 +9836,26 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
           <t>776511820</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.001</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr"/>
-      <c r="J75" s="11" t="inlineStr">
+      <c r="J75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9104,23 +9883,27 @@
       <c r="E76" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="F76" s="15">
+        <f> PSV77.002 plocha 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="G76" s="14" t="inlineStr">
+      <c r="H76" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H76" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.002 → PSV77.002a</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr"/>
-      <c r="J76" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr">
         <is>
           <t>Dlažba lepená vč. lepidla (771 família).</t>
         </is>
@@ -9148,23 +9931,27 @@
       <c r="E77" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="F77" s="15" t="inlineStr">
+      <c r="F77" s="15">
+        <f> PSV77.002 plocha 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="H77" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H77" s="15" t="inlineStr">
+      <c r="I77" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.002 → PSV77.002b</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr"/>
-      <c r="J77" s="15" t="inlineStr">
+      <c r="J77" s="15" t="inlineStr"/>
+      <c r="K77" s="15" t="inlineStr">
         <is>
           <t>Spárování (771 família) — často zahrnuto v kladení.</t>
         </is>
@@ -9192,23 +9979,27 @@
       <c r="E78" s="16" t="n">
         <v>32.4</v>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F78" s="15">
+        <f> PSV77.003 plocha 32.4 m²</f>
+        <v/>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr">
+      <c r="H78" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H78" s="15" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.003 → PSV77.003a</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr"/>
-      <c r="J78" s="15" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr">
         <is>
           <t>Dlažba lepená (771 família).</t>
         </is>
@@ -9236,23 +10027,27 @@
       <c r="E79" s="16" t="n">
         <v>32.4</v>
       </c>
-      <c r="F79" s="15" t="inlineStr">
+      <c r="F79" s="15">
+        <f> PSV77.003 plocha 32.4 m²</f>
+        <v/>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="H79" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H79" s="15" t="inlineStr">
+      <c r="I79" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.003 → PSV77.003b</t>
         </is>
       </c>
-      <c r="I79" s="15" t="inlineStr"/>
-      <c r="J79" s="15" t="inlineStr">
+      <c r="J79" s="15" t="inlineStr"/>
+      <c r="K79" s="15" t="inlineStr">
         <is>
           <t>Spárování (771 família).</t>
         </is>
@@ -9282,21 +10077,26 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
           <t>766411111</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H80" s="11" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.004</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="11" t="inlineStr">
+      <c r="J80" s="11" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9326,21 +10126,26 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
           <t>631321311</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.005</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="J81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9370,21 +10175,26 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
           <t>776511831</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.006</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr"/>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="J82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9414,21 +10224,26 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
           <t>771274107</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.007</t>
         </is>
       </c>
-      <c r="I83" s="11" t="inlineStr"/>
-      <c r="J83" s="11" t="inlineStr">
+      <c r="J83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9449,6 +10264,7 @@
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="n"/>
       <c r="J84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
@@ -9472,23 +10288,27 @@
       <c r="E85" s="16" t="n">
         <v>78.2</v>
       </c>
-      <c r="F85" s="15" t="inlineStr">
+      <c r="F85" s="15">
+        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
+        <v/>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G85" s="14" t="inlineStr">
+      <c r="H85" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H85" s="15" t="inlineStr">
+      <c r="I85" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.001 → PSV78.001a</t>
         </is>
       </c>
-      <c r="I85" s="15" t="inlineStr"/>
-      <c r="J85" s="15" t="inlineStr">
+      <c r="J85" s="15" t="inlineStr"/>
+      <c r="K85" s="15" t="inlineStr">
         <is>
           <t>Jádrová omítka VC (612 família).</t>
         </is>
@@ -9516,23 +10336,27 @@
       <c r="E86" s="16" t="n">
         <v>78.2</v>
       </c>
-      <c r="F86" s="15" t="inlineStr">
+      <c r="F86" s="15">
+        <f> PSV78.001 plocha 78.2 m²</f>
+        <v/>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G86" s="14" t="inlineStr">
+      <c r="H86" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H86" s="15" t="inlineStr">
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.001 → PSV78.001b</t>
         </is>
       </c>
-      <c r="I86" s="15" t="inlineStr"/>
-      <c r="J86" s="15" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr">
         <is>
           <t>Štuková omítka (612 família).</t>
         </is>
@@ -9560,23 +10384,27 @@
       <c r="E87" s="16" t="n">
         <v>208.4</v>
       </c>
-      <c r="F87" s="15" t="inlineStr">
+      <c r="F87" s="15">
+        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
+        <v/>
+      </c>
+      <c r="G87" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G87" s="14" t="inlineStr">
+      <c r="H87" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H87" s="15" t="inlineStr">
+      <c r="I87" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.002 → PSV78.002a</t>
         </is>
       </c>
-      <c r="I87" s="15" t="inlineStr"/>
-      <c r="J87" s="15" t="inlineStr">
+      <c r="J87" s="15" t="inlineStr"/>
+      <c r="K87" s="15" t="inlineStr">
         <is>
           <t>Jádrová omítka VC (612 família).</t>
         </is>
@@ -9604,23 +10432,27 @@
       <c r="E88" s="16" t="n">
         <v>208.4</v>
       </c>
-      <c r="F88" s="15" t="inlineStr">
+      <c r="F88" s="15">
+        <f> PSV78.002 plocha 208.4 m²</f>
+        <v/>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G88" s="14" t="inlineStr">
+      <c r="H88" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H88" s="15" t="inlineStr">
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.002 → PSV78.002b</t>
         </is>
       </c>
-      <c r="I88" s="15" t="inlineStr"/>
-      <c r="J88" s="15" t="inlineStr">
+      <c r="J88" s="15" t="inlineStr"/>
+      <c r="K88" s="15" t="inlineStr">
         <is>
           <t>Štuková omítka (612 família).</t>
         </is>
@@ -9648,23 +10480,27 @@
       <c r="E89" s="16" t="n">
         <v>201.6</v>
       </c>
-      <c r="F89" s="15" t="inlineStr">
+      <c r="F89" s="15">
+        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
+        <v/>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G89" s="14" t="inlineStr">
+      <c r="H89" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H89" s="15" t="inlineStr">
+      <c r="I89" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.003 → PSV78.003a</t>
         </is>
       </c>
-      <c r="I89" s="15" t="inlineStr"/>
-      <c r="J89" s="15" t="inlineStr">
+      <c r="J89" s="15" t="inlineStr"/>
+      <c r="K89" s="15" t="inlineStr">
         <is>
           <t>Jádrová omítka VC (612 família).</t>
         </is>
@@ -9692,23 +10528,27 @@
       <c r="E90" s="16" t="n">
         <v>201.6</v>
       </c>
-      <c r="F90" s="15" t="inlineStr">
+      <c r="F90" s="15">
+        <f> PSV78.003 plocha 201.6 m²</f>
+        <v/>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G90" s="14" t="inlineStr">
+      <c r="H90" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H90" s="15" t="inlineStr">
+      <c r="I90" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.003 → PSV78.003b</t>
         </is>
       </c>
-      <c r="I90" s="15" t="inlineStr"/>
-      <c r="J90" s="15" t="inlineStr">
+      <c r="J90" s="15" t="inlineStr"/>
+      <c r="K90" s="15" t="inlineStr">
         <is>
           <t>Štuková omítka (612 família).</t>
         </is>
@@ -9736,23 +10576,27 @@
       <c r="E91" s="16" t="n">
         <v>179.1</v>
       </c>
-      <c r="F91" s="15" t="inlineStr">
+      <c r="F91" s="15">
+        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <v/>
+      </c>
+      <c r="G91" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G91" s="14" t="inlineStr">
+      <c r="H91" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H91" s="15" t="inlineStr">
+      <c r="I91" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.004 → PSV78.004a</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr"/>
-      <c r="J91" s="15" t="inlineStr">
+      <c r="J91" s="15" t="inlineStr"/>
+      <c r="K91" s="15" t="inlineStr">
         <is>
           <t>Jádrová omítka VC (612 família).</t>
         </is>
@@ -9780,23 +10624,27 @@
       <c r="E92" s="16" t="n">
         <v>179.1</v>
       </c>
-      <c r="F92" s="15" t="inlineStr">
+      <c r="F92" s="15">
+        <f> PSV78.004 plocha 179.1 m²</f>
+        <v/>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="G92" s="14" t="inlineStr">
+      <c r="H92" s="14" t="inlineStr">
         <is>
           <t>⚠ family_only</t>
         </is>
       </c>
-      <c r="H92" s="15" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.004 → PSV78.004b</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr"/>
-      <c r="J92" s="15" t="inlineStr">
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr">
         <is>
           <t>Štuková omítka (612 família).</t>
         </is>
@@ -9826,21 +10674,26 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
           <t>612471141</t>
         </is>
       </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="H93" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H93" s="11" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.005</t>
         </is>
       </c>
-      <c r="I93" s="11" t="inlineStr"/>
-      <c r="J93" s="11" t="inlineStr">
+      <c r="J93" s="11" t="inlineStr"/>
+      <c r="K93" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9870,21 +10723,26 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
           <t>612471141</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="H94" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H94" s="11" t="inlineStr">
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.006</t>
         </is>
       </c>
-      <c r="I94" s="11" t="inlineStr"/>
-      <c r="J94" s="11" t="inlineStr">
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9914,21 +10772,26 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
           <t>612471141</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="H95" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr">
+      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.007</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr"/>
-      <c r="J95" s="11" t="inlineStr">
+      <c r="J95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -9958,21 +10821,26 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
           <t>781447001</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="H96" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H96" s="11" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.008</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr"/>
-      <c r="J96" s="11" t="inlineStr">
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10002,21 +10870,26 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
           <t>781447001</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H97" s="11" t="inlineStr">
+      <c r="I97" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.009</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr"/>
-      <c r="J97" s="11" t="inlineStr">
+      <c r="J97" s="11" t="inlineStr"/>
+      <c r="K97" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10046,21 +10919,26 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
           <t>781447001</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="H98" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H98" s="11" t="inlineStr">
+      <c r="I98" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.010</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr"/>
-      <c r="J98" s="11" t="inlineStr">
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10090,21 +10968,26 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
           <t>781447001</t>
         </is>
       </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.011</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr"/>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="J99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10134,21 +11017,26 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
+          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
           <t>784121011</t>
         </is>
       </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="H100" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H100" s="11" t="inlineStr">
+      <c r="I100" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.012</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr"/>
-      <c r="J100" s="11" t="inlineStr">
+      <c r="J100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10178,21 +11066,26 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
           <t>784121011</t>
         </is>
       </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="H101" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H101" s="11" t="inlineStr">
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.012.1_PP</t>
         </is>
       </c>
-      <c r="I101" s="11" t="inlineStr"/>
-      <c r="J101" s="11" t="inlineStr">
+      <c r="J101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10222,21 +11115,26 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
           <t>784121011</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H102" s="11" t="inlineStr">
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.012.1_NP</t>
         </is>
       </c>
-      <c r="I102" s="11" t="inlineStr"/>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="J102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10266,21 +11164,26 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
           <t>784121011</t>
         </is>
       </c>
-      <c r="G103" s="10" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H103" s="11" t="inlineStr">
+      <c r="I103" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.012.2_NP</t>
         </is>
       </c>
-      <c r="I103" s="11" t="inlineStr"/>
-      <c r="J103" s="11" t="inlineStr">
+      <c r="J103" s="11" t="inlineStr"/>
+      <c r="K103" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10310,21 +11213,26 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
           <t>784121011</t>
         </is>
       </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="H104" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H104" s="11" t="inlineStr">
+      <c r="I104" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.012.3_NP</t>
         </is>
       </c>
-      <c r="I104" s="11" t="inlineStr"/>
-      <c r="J104" s="11" t="inlineStr">
+      <c r="J104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10345,6 +11253,7 @@
       <c r="H105" s="9" t="n"/>
       <c r="I105" s="9" t="n"/>
       <c r="J105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="n">
@@ -10370,21 +11279,26 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
           <t>375211101</t>
         </is>
       </c>
-      <c r="G106" s="13" t="inlineStr">
+      <c r="H106" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H106" s="11" t="inlineStr">
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV95.001</t>
         </is>
       </c>
-      <c r="I106" s="11" t="inlineStr"/>
-      <c r="J106" s="11" t="inlineStr">
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10414,21 +11328,26 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
           <t>966067121</t>
         </is>
       </c>
-      <c r="G107" s="10" t="inlineStr">
+      <c r="H107" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr">
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV95.002</t>
         </is>
       </c>
-      <c r="I107" s="11" t="inlineStr"/>
-      <c r="J107" s="11" t="inlineStr">
+      <c r="J107" s="11" t="inlineStr"/>
+      <c r="K107" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10449,6 +11368,7 @@
       <c r="H108" s="9" t="n"/>
       <c r="I108" s="9" t="n"/>
       <c r="J108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="n">
@@ -10474,21 +11394,26 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
           <t>210010011</t>
         </is>
       </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="H109" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H109" s="11" t="inlineStr">
+      <c r="I109" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.001</t>
         </is>
       </c>
-      <c r="I109" s="11" t="inlineStr"/>
-      <c r="J109" s="11" t="inlineStr">
+      <c r="J109" s="11" t="inlineStr"/>
+      <c r="K109" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10518,21 +11443,26 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
           <t>210110023</t>
         </is>
       </c>
-      <c r="G110" s="10" t="inlineStr">
+      <c r="H110" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr">
+      <c r="I110" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.002</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr"/>
-      <c r="J110" s="11" t="inlineStr">
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10562,21 +11492,26 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
           <t>210800012</t>
         </is>
       </c>
-      <c r="G111" s="10" t="inlineStr">
+      <c r="H111" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H111" s="11" t="inlineStr">
+      <c r="I111" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.003</t>
         </is>
       </c>
-      <c r="I111" s="11" t="inlineStr"/>
-      <c r="J111" s="11" t="inlineStr">
+      <c r="J111" s="11" t="inlineStr"/>
+      <c r="K111" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10606,21 +11541,26 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
           <t>210810050</t>
         </is>
       </c>
-      <c r="G112" s="10" t="inlineStr">
+      <c r="H112" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H112" s="11" t="inlineStr">
+      <c r="I112" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.004</t>
         </is>
       </c>
-      <c r="I112" s="11" t="inlineStr"/>
-      <c r="J112" s="11" t="inlineStr">
+      <c r="J112" s="11" t="inlineStr"/>
+      <c r="K112" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10650,21 +11590,26 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
           <t>210820002</t>
         </is>
       </c>
-      <c r="G113" s="10" t="inlineStr">
+      <c r="H113" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H113" s="11" t="inlineStr">
+      <c r="I113" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.005</t>
         </is>
       </c>
-      <c r="I113" s="11" t="inlineStr"/>
-      <c r="J113" s="11" t="inlineStr">
+      <c r="J113" s="11" t="inlineStr"/>
+      <c r="K113" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10694,21 +11639,26 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
           <t>210800099</t>
         </is>
       </c>
-      <c r="G114" s="10" t="inlineStr">
+      <c r="H114" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr">
+      <c r="I114" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.006</t>
         </is>
       </c>
-      <c r="I114" s="11" t="inlineStr"/>
-      <c r="J114" s="11" t="inlineStr">
+      <c r="J114" s="11" t="inlineStr"/>
+      <c r="K114" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10738,41 +11688,46 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
           <t>996019011</t>
         </is>
       </c>
-      <c r="G115" s="10" t="inlineStr">
+      <c r="H115" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H115" s="11" t="inlineStr">
+      <c r="I115" s="11" t="inlineStr">
         <is>
           <t>260219_dum.M21.007</t>
         </is>
       </c>
-      <c r="I115" s="11" t="inlineStr"/>
-      <c r="J115" s="11" t="inlineStr">
+      <c r="J115" s="11" t="inlineStr"/>
+      <c r="K115" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <mergeCells count="12">
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A84:J84"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A105:J105"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A108:J108"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A108:K108"/>
+    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10784,19 +11739,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10827,25 +11783,30 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Vzorec / Zdroj výměry</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>URS kód kandidát</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Parent frozen item_id</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Realizuje skladbu</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Pozn.</t>
         </is>
@@ -10866,6 +11827,7 @@
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n">
@@ -10891,21 +11853,26 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
+          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
           <t>030011000</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10935,21 +11902,26 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
+          <t>1 ks × 8 měs realizace</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
           <t>030013000</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.002</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -10979,21 +11951,26 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
+          <t>Komplexní zřízení + provoz po dobu stavby</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
           <t>031011000</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.003</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11023,21 +12000,26 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
+          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
           <t>012103101</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.020</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11058,6 +12040,7 @@
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -11083,21 +12066,26 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
+          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11127,21 +12115,26 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
+          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
           <t>031031000</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.002</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11171,21 +12164,26 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
+          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.003</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11206,6 +12204,7 @@
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -11231,21 +12230,26 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
+          <t>realizace ~8 měs</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>030091000</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11266,6 +12270,7 @@
       <c r="H13" s="9" t="n"/>
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -11291,21 +12296,26 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
+          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
           <t>030081000</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11335,21 +12345,26 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
+          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>030083000</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.002</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11370,6 +12385,7 @@
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -11395,21 +12411,26 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
           <t>030131000</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11439,21 +12460,26 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
+          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
           <t>030133000</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.002</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11474,6 +12500,7 @@
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -11499,21 +12526,26 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
+          <t>2 etapy geodet × 1 kpl</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11534,6 +12566,7 @@
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -11559,21 +12592,26 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
+          <t>Standard — DSP pro kolaudaci</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
           <t>030151000</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11594,6 +12632,7 @@
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -11619,21 +12658,26 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
+          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
           <t>030161000</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11654,6 +12698,7 @@
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -11679,38 +12724,43 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
+          <t>Standard — paušál kolaudace</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
           <t>030171000</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>260219_dum.VRN.001</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <mergeCells count="9">
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A23:K23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11722,19 +12772,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11765,25 +12816,30 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Vzorec / Zdroj výměry</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>URS kód kandidát</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Parent frozen item_id</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Realizuje skladbu</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Pozn.</t>
         </is>
@@ -11804,6 +12860,7 @@
       <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n">
@@ -11829,21 +12886,26 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
+          <t>TZ ARS sklad §3 — odstranění stávajících kamenných prvků (odhad)</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
           <t>962031132</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>✓ cross-disc</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV1.001</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11873,21 +12935,26 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
+          <t>DXF: L=6.350 × W=3.340 × H=1.2 (DXF DIMENSION ověřeno)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
           <t>131201101</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV1.002</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11917,21 +12984,26 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
+          <t>obvod 2×(6.35+3.34) × W=0.5 × H=0.5</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
           <t>132201101</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV1.003</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11961,21 +13033,26 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
+          <t>DXF: 7 patek × 0.5 × 0.5 × 1.0 (TZ rozteč 1000 mm × 7 m parking)</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
           <t>132211101</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV1.004</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12005,25 +13082,30 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
+          <t>podlaha sklad 21.2 m² × 0.15 m štěrku</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
           <t>174101101</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV1.005</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>S01_sklad</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12051,19 +13133,23 @@
       <c r="E8" s="19" t="n">
         <v>32.1</v>
       </c>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="F8" s="18">
+        <f> součet hloubení sklad + figura + patky (25.5+4.85+1.75)</f>
+        <v/>
+      </c>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV1.006</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr"/>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12084,6 +13170,7 @@
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
@@ -12107,23 +13194,28 @@
       <c r="E10" s="19" t="n">
         <v>4.84</v>
       </c>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.001</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12153,21 +13245,26 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
+          <t>DXF: 7 ks (rozteč 1000 mm × 7000 mm parking délka)</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
           <t>273313811</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.002</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12197,21 +13294,26 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
+          <t>7 ks (= spodní)</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>311233812</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.003</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12241,21 +13343,26 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
+          <t>patky horní (0.3×0.3×0.5×7) + zídka (odhad ~1 m³)</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
           <t>273321321</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.004</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12285,25 +13392,30 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
+          <t>21.2 × 0.10 = 2.12</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
           <t>174101101</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>✓ cross-disc</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.005</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>S01_sklad, S05_sklad</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12333,25 +13445,30 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
+          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.006</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>S05_sklad</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12372,6 +13489,7 @@
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -12397,25 +13515,30 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
+          <t>odhad — výška ~1.6 m × šíře 6.35 m / blok 0.8×0.4 = ~32 bloků × 2 řady = 64; round 60</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
           <t>311233815</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.001</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>S04_sklad</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12445,25 +13568,30 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
+          <t>obvod 19.4 m × výška 2.4 m = 46.6</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
           <t>311233811</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.002</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12493,25 +13621,30 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
+          <t>46.6 × 30 kg/m² = 1398</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.003</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12532,6 +13665,7 @@
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -12557,25 +13691,30 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
+          <t>rozpon 3.34 × počet stropnic (6.35/0.625 = 10) = ~10 ks × 3.34 = 33.4</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
           <t>762341110</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.001</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12603,27 +13742,31 @@
       <c r="E22" s="12" t="n">
         <v>21.209</v>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="11">
+        <f> 21.2 m² strop skladu</f>
+        <v/>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>762331110</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.002</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12653,25 +13796,30 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
+          <t>21.2 × 1.05 přesah</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
           <t>712331101</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.003</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12701,25 +13849,30 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
+          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
           <t>411321414</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.004</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12749,25 +13902,30 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
           <t>411321515</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.005</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12795,27 +13953,31 @@
       <c r="E26" s="12" t="n">
         <v>1551</v>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="11">
+        <f> hmotnost IPE180 (921 kg) + odhad pororoštů (21 m² × 30 kg/m²) = ~1551</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>783201001</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12836,6 +13998,7 @@
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -12861,25 +14024,30 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
           <t>121301101</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV5.001</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>S05_sklad</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12900,6 +14068,7 @@
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
       <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -12925,21 +14094,26 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
           <t>766682111</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.PSV76.001</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -12960,6 +14134,7 @@
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
       <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n">
@@ -12983,23 +14158,28 @@
       <c r="E32" s="19" t="n">
         <v>17.6</v>
       </c>
-      <c r="F32" s="18" t="inlineStr"/>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr"/>
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.PSV77.001</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>S01_sklad</t>
         </is>
       </c>
-      <c r="J32" s="18" t="inlineStr">
+      <c r="K32" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -13020,6 +14200,7 @@
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
       <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -13045,21 +14226,26 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
+          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.001</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -13089,21 +14275,26 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.002</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -13124,6 +14315,7 @@
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -13149,21 +14341,26 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
+          <t>Standard geodet vytýčení pro nový objekt</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.001</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -13184,6 +14381,7 @@
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -13209,39 +14407,44 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
           <t>030001000</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>? needs_lookup</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.001</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <mergeCells count="10">
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -904,17 +904,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -924,17 +924,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -944,80 +944,80 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>VRN — Revize</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B44" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Família</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Počet ops</t>
         </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -1038,77 +1038,77 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -1118,7 +1118,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -1128,7 +1128,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -1138,27 +1138,27 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -1168,7 +1168,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -1178,27 +1178,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -1208,7 +1208,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1218,27 +1218,27 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -1248,7 +1248,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1258,7 +1258,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -1268,27 +1268,27 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -1298,7 +1298,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1308,7 +1308,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -1318,7 +1318,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -1328,7 +1328,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -1338,7 +1338,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1348,7 +1348,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -1358,7 +1358,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -1368,7 +1368,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1378,27 +1378,27 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
@@ -1408,7 +1408,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -1418,7 +1418,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -1428,7 +1428,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -1438,7 +1438,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -1448,7 +1448,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -1458,7 +1458,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1468,7 +1468,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1478,7 +1478,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -1488,7 +1488,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -1498,7 +1498,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -1508,64 +1508,84 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>• Terasa A2 korekce: HSV1.005a = 636311 família (dlaždice NA TERČE, NE 762 carpentry)</t>
         </is>
@@ -1575,13 +1595,13 @@
   <mergeCells count="11">
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A110:C110"/>
     <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A101:C101"/>
     <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A109:C109"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A104:C104"/>
   </mergeCells>
@@ -11739,7 +11759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12749,10 +12769,135 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Přesun hmot  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>VRN — Přesun hmot</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>? needs_lookup</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.VRN.PM01</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr"/>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Lešení  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>VRN — Lešení</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>503.1</v>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>? needs_lookup</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.VRN.PM02</t>
+        </is>
+      </c>
+      <c r="J30" s="18" t="inlineStr"/>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
@@ -12761,6 +12906,7 @@
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A27:K27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_VRN" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260217_SKLAD" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Composite_Decomposition_Map" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PENDING_DECISIONS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'260219_DUM_HSV'!$A$1:$K$1</definedName>
@@ -126,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15215,4 +15219,164 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Téma (čeká rozhodnutí)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Stav v rozpočtu</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Next action</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>⚠ Tyto práce NEJSOU v items.json ani v atomic worklistu — byly ověřeny jako NEzmíněné v ARS dům TZ (Stage 1B-verify). Před cenotvorbou / katalogovým mapováním (Stage 3) je nutné rozhodnutí projektanta/investora. NE zapomenout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Hromosvod / ochrana před bleskem (LPS) — chybí v PBŘ, ČSN EN 62305 risk analysis nutná</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř u projektanta (TUSPO / elektroprojektant) zda dle ČSN EN 62305 je hromosvod požadován. Pokud ano → doplníme M-22 položku (jímací soustava + svody + uzemnění + revize), cca 30-50 tis. Kč.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Terénní + sadové úpravy — pouze v MU rozhodnutí o sjezdu (separate scope), NE v ARS dům TZ</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř zda terénní/sadové úpravy + restoration zeleně (humusová vrstva 10 cm) má být v rozpočtu sjezd/parking (260217?) nebo samostatně. Pokud spadá do našeho scope → doplníme HSV-1 položku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Slaboproud (data/TV/zvonek/domofon/anténa) — není v TZ, ale 3 byty obvykle vyžadují</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř u investora rozsah slaboproudu (data/TV/domofon) — souvisí s vyjasnění #7 (počty zásuvek/svítidel). Pokud požadováno → doplníme M-22 slaboproud položku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PM05</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>SKIP (rekonstrukce — možná existuje)</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -1017,26 +1017,26 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
         <v>13</v>
       </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
-        </is>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -1162,7 +1162,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -1172,7 +1172,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -1182,7 +1182,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -1192,17 +1192,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -1212,7 +1212,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1222,7 +1222,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -1232,17 +1232,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -1252,7 +1252,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1262,7 +1262,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -1272,7 +1272,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -1282,7 +1282,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -2622,49 +2622,45 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>Systémové oboustranné bednění bílé vany — DOKA Framax / PERI MAXIMO, vč. těsnění pracovních spár bobtnavý pásek bentonit (TZ §5.5)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>631311115</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>⚠ wrong_leaf</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>? RECONCILED_274_CONSENSUS</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.003</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="J22" s="18" t="inlineStr"/>
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -2863,49 +2859,45 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Bednění pozedního věnce systémové oboustranné</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="19" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>631311115</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>⚠ wrong_leaf</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>? RECONCILED_274_CONSENSUS</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.008</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="J27" s="18" t="inlineStr"/>
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -978,421 +978,389 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
+          <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Família</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Počet ops</t>
-        </is>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>✓ verified (leaf ověřen)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>24</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>⚠ família ??? (leaf z ÚRS online)</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>030</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>11</v>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>10</v>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa 636311 (na terče, NE 762) · HSV2.003/008 bednění 274.</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>9</v>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>• PRÁCE JE KOMPLETNÍ bez ohledu na stav kódu — seznam (postup prací) = primary deliverable. Code = secondary, doplní se v ÚRS online / KROS.</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>8</v>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>7</v>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Família</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Počet ops</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -1402,107 +1370,107 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -1512,7 +1480,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -1522,7 +1490,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -1532,82 +1500,186 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
-        </is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
-        </is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
-        </is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
-        </is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
-        </is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
-        </is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>METODIKA + PATTERN COMPLIANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
           <t>• Terasa A2 korekce: HSV1.005a = 636311 família (dlaždice NA TERČE, NE 762 carpentry)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A108:C108"/>
+  <mergeCells count="15">
+    <mergeCell ref="A115:C115"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A117:C117"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A114:C114"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1792,7 +1864,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -1841,7 +1913,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -1889,7 +1961,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1904,7 +1976,7 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>Dlažba NA LOŽI (596 família) — ne na terče. Leaf dle typu dlažby (zámková 596211 / velkoformát 596811) — verify u dodavatele.</t>
+          <t>Dlažba NA LOŽI (596 família) — ne na terče. Leaf dle typu dlažby (zámková 596211 / velkoformát 596811) — verify u dodavatele.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2013,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1956,7 +2028,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Podklad ze štěrkodrti (564 família).</t>
+          <t>Podklad ze štěrkodrti (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2065,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -2008,7 +2080,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.</t>
+          <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2117,7 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -2060,7 +2132,7 @@
       </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>A2 KOREKCE: dlaždice NA TERČE → 636311 família (NE 762 carpentry — stará dřevěná kompozice nahrazena betonovými dlaždicemi na terče per Alexander Phase 5).</t>
+          <t>A2 KOREKCE: dlaždice NA TERČE → 636311 família (NE 762 carpentry — stará dřevěná kompozice nahrazena betonovými dlaždicemi na terče per Alexander Phase 5).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2169,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -2112,7 +2184,7 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>Podklad štěrkopísek (564 família).</t>
+          <t>Podklad štěrkopísek (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2221,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -2164,7 +2236,7 @@
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>Podklad štěrkodrť (564 família).</t>
+          <t>Podklad štěrkodrť (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2273,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
@@ -2216,7 +2288,7 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>Geotextilie (693 família) nebo zahrnuto v 564.</t>
+          <t>Geotextilie (693 família) nebo zahrnuto v 564.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2370,7 @@
       <c r="G14" s="18" t="inlineStr"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -2309,7 +2381,7 @@
       <c r="J14" s="18" t="inlineStr"/>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2419,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -2395,7 +2467,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -2406,7 +2478,7 @@
       <c r="J16" s="15" t="inlineStr"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).</t>
+          <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2515,7 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
@@ -2454,7 +2526,7 @@
       <c r="J17" s="15" t="inlineStr"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Obsyp drenáže (212/174 família).</t>
+          <t>Obsyp drenáže (212/174 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2563,7 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -2502,7 +2574,7 @@
       <c r="J18" s="15" t="inlineStr"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>Geotextilie obal + napojení (693 família).</t>
+          <t>Geotextilie obal + napojení (693 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2629,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -2606,7 +2678,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -2651,7 +2723,7 @@
       <c r="G22" s="18" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>? RECONCILED_274_CONSENSUS</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
@@ -2662,7 +2734,7 @@
       <c r="J22" s="18" t="inlineStr"/>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2772,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -2745,7 +2817,7 @@
       <c r="G24" s="18" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>⚠ wrong_leaf</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -2756,7 +2828,7 @@
       <c r="J24" s="18" t="inlineStr"/>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2866,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -2843,7 +2915,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -2888,7 +2960,7 @@
       <c r="G27" s="18" t="inlineStr"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>? RECONCILED_274_CONSENSUS</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -2899,7 +2971,7 @@
       <c r="J27" s="18" t="inlineStr"/>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2937,7 +3009,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -2986,7 +3058,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -3039,7 +3111,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -3092,7 +3164,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -3145,7 +3217,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -3215,7 +3287,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -3321,7 +3393,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -3374,7 +3446,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -3427,7 +3499,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>✓ cross-disc</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -3479,7 +3551,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -3528,7 +3600,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -3598,7 +3670,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -3647,7 +3719,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -3700,7 +3772,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -3753,7 +3825,7 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -3805,7 +3877,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -3857,7 +3929,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -3910,7 +3982,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>✓ cross-disc</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -3963,7 +4035,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -4016,7 +4088,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
@@ -4069,7 +4141,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4121,7 +4193,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -4173,7 +4245,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4226,7 +4298,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -4278,7 +4350,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -4348,7 +4420,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4397,7 +4469,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4446,7 +4518,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -4495,7 +4567,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -4544,7 +4616,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -4593,7 +4665,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -4641,7 +4713,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -4694,7 +4766,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -4799,7 +4871,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -4851,7 +4923,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -4903,7 +4975,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -4955,7 +5027,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -5008,7 +5080,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5061,7 +5133,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -5110,7 +5182,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5180,7 +5252,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -5224,7 +5296,7 @@
       <c r="G75" s="18" t="inlineStr"/>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>⚠ wrong_leaf</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
@@ -5235,7 +5307,7 @@
       <c r="J75" s="18" t="inlineStr"/>
       <c r="K75" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5345,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -5321,7 +5393,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -5370,7 +5442,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -5419,7 +5491,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -5468,7 +5540,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -5517,7 +5589,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -5566,7 +5638,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -5615,7 +5687,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -5664,7 +5736,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -5713,7 +5785,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -5860,7 +5932,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -5909,7 +5981,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -5958,7 +6030,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6024,7 +6096,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -6076,7 +6148,7 @@
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I93" s="15" t="inlineStr">
@@ -6091,7 +6163,7 @@
       </c>
       <c r="K93" s="15" t="inlineStr">
         <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.</t>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6200,7 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -6143,7 +6215,7 @@
       </c>
       <c r="K94" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.</t>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6252,7 @@
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I95" s="15" t="inlineStr">
@@ -6195,7 +6267,7 @@
       </c>
       <c r="K95" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).</t>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6304,7 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
@@ -6247,7 +6319,7 @@
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).</t>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6356,7 @@
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I97" s="15" t="inlineStr">
@@ -6299,7 +6371,7 @@
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).</t>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6408,7 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
@@ -6351,7 +6423,7 @@
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva + omítka špalet (622 família).</t>
+          <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6461,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -6442,7 +6514,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -6606,7 +6678,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -6655,7 +6727,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -6700,7 +6772,7 @@
       <c r="G5" s="18" t="inlineStr"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I5" s="18" t="inlineStr">
@@ -6711,7 +6783,7 @@
       <c r="J5" s="18" t="inlineStr"/>
       <c r="K5" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6834,7 @@
       <c r="G7" s="18" t="inlineStr"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
@@ -6773,7 +6845,7 @@
       <c r="J7" s="18" t="inlineStr"/>
       <c r="K7" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6878,7 @@
       <c r="G8" s="18" t="inlineStr"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -6817,7 +6889,7 @@
       <c r="J8" s="18" t="inlineStr"/>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6944,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -6921,7 +6993,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -6970,7 +7042,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -7019,7 +7091,7 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -7030,7 +7102,7 @@
       <c r="J13" s="15" t="inlineStr"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7140,7 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -7079,7 +7151,7 @@
       <c r="J14" s="15" t="inlineStr"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7189,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
@@ -7128,7 +7200,7 @@
       <c r="J15" s="15" t="inlineStr"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7238,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -7177,7 +7249,7 @@
       <c r="J16" s="15" t="inlineStr"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7287,7 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
@@ -7226,7 +7298,7 @@
       <c r="J17" s="15" t="inlineStr"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7336,7 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -7275,7 +7347,7 @@
       <c r="J18" s="15" t="inlineStr"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7385,7 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I19" s="15" t="inlineStr">
@@ -7324,7 +7396,7 @@
       <c r="J19" s="15" t="inlineStr"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7434,7 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
@@ -7373,7 +7445,7 @@
       <c r="J20" s="15" t="inlineStr"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7483,7 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I21" s="15" t="inlineStr">
@@ -7422,7 +7494,7 @@
       <c r="J21" s="15" t="inlineStr"/>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>Zařizovací předmět (725 família).</t>
+          <t>Zařizovací předmět (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7532,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -7509,7 +7581,7 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -7520,7 +7592,7 @@
       <c r="J23" s="15" t="inlineStr"/>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>Armatura (725 família).</t>
+          <t>Armatura (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7630,7 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
@@ -7569,7 +7641,7 @@
       <c r="J24" s="15" t="inlineStr"/>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>Baterie (725 família).</t>
+          <t>Baterie (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7679,7 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
@@ -7618,7 +7690,7 @@
       <c r="J25" s="15" t="inlineStr"/>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>Baterie termostat (725 família).</t>
+          <t>Baterie termostat (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7728,7 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
@@ -7667,7 +7739,7 @@
       <c r="J26" s="15" t="inlineStr"/>
       <c r="K26" s="15" t="inlineStr">
         <is>
-          <t>Dřezová baterie (725 família).</t>
+          <t>Dřezová baterie (725 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7777,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -7754,7 +7826,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -7803,7 +7875,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -7852,7 +7924,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -7901,7 +7973,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -7950,7 +8022,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -7999,7 +8071,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -8048,7 +8120,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -8097,7 +8169,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -8146,7 +8218,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -8195,7 +8267,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -8261,7 +8333,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -8309,7 +8381,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -8358,7 +8430,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -8407,7 +8479,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -8456,7 +8528,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -8505,7 +8577,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
@@ -8554,7 +8626,7 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -8603,7 +8675,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -8669,7 +8741,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -8717,7 +8789,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -8766,7 +8838,7 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
@@ -8777,7 +8849,7 @@
       <c r="J50" s="15" t="inlineStr"/>
       <c r="K50" s="15" t="inlineStr">
         <is>
-          <t>Klempířské svody (764 família).</t>
+          <t>Klempířské svody (764 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8886,7 @@
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
@@ -8825,7 +8897,7 @@
       <c r="J51" s="15" t="inlineStr"/>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>Klempířské žlaby (764 família).</t>
+          <t>Klempířské žlaby (764 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8935,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -8929,7 +9001,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -8978,7 +9050,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -9044,7 +9116,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -9093,7 +9165,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -9142,7 +9214,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -9191,7 +9263,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -9240,7 +9312,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -9289,7 +9361,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -9338,7 +9410,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -9387,7 +9459,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -9436,7 +9508,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -9485,7 +9557,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -9534,7 +9606,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -9583,7 +9655,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -9649,7 +9721,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -9698,7 +9770,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -9747,7 +9819,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -9796,7 +9868,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -9862,7 +9934,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -9910,7 +9982,7 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
@@ -9921,7 +9993,7 @@
       <c r="J76" s="15" t="inlineStr"/>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>Dlažba lepená vč. lepidla (771 família).</t>
+          <t>Dlažba lepená vč. lepidla (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -9958,7 +10030,7 @@
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I77" s="15" t="inlineStr">
@@ -9969,7 +10041,7 @@
       <c r="J77" s="15" t="inlineStr"/>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>Spárování (771 família) — často zahrnuto v kladení.</t>
+          <t>Spárování (771 família) — často zahrnuto v kladení.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10078,7 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
@@ -10017,7 +10089,7 @@
       <c r="J78" s="15" t="inlineStr"/>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>Dlažba lepená (771 família).</t>
+          <t>Dlažba lepená (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10126,7 @@
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I79" s="15" t="inlineStr">
@@ -10065,7 +10137,7 @@
       <c r="J79" s="15" t="inlineStr"/>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>Spárování (771 família).</t>
+          <t>Spárování (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10175,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -10152,7 +10224,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -10201,7 +10273,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -10250,7 +10322,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -10315,7 +10387,7 @@
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I85" s="15" t="inlineStr">
@@ -10326,7 +10398,7 @@
       <c r="J85" s="15" t="inlineStr"/>
       <c r="K85" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10435,7 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
@@ -10374,7 +10446,7 @@
       <c r="J86" s="15" t="inlineStr"/>
       <c r="K86" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10483,7 @@
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I87" s="15" t="inlineStr">
@@ -10422,7 +10494,7 @@
       <c r="J87" s="15" t="inlineStr"/>
       <c r="K87" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10531,7 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
@@ -10470,7 +10542,7 @@
       <c r="J88" s="15" t="inlineStr"/>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10579,7 @@
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I89" s="15" t="inlineStr">
@@ -10518,7 +10590,7 @@
       <c r="J89" s="15" t="inlineStr"/>
       <c r="K89" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10627,7 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
@@ -10566,7 +10638,7 @@
       <c r="J90" s="15" t="inlineStr"/>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10675,7 @@
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
@@ -10614,7 +10686,7 @@
       <c r="J91" s="15" t="inlineStr"/>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10723,7 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>⚠ family_only</t>
+          <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -10662,7 +10734,7 @@
       <c r="J92" s="15" t="inlineStr"/>
       <c r="K92" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10772,7 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
@@ -10749,7 +10821,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -10798,7 +10870,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -10847,7 +10919,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -10896,7 +10968,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -10945,7 +11017,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -10994,7 +11066,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -11043,7 +11115,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -11092,7 +11164,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
@@ -11141,7 +11213,7 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -11190,7 +11262,7 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -11239,7 +11311,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -11305,7 +11377,7 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -11354,7 +11426,7 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -11420,7 +11492,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -11469,7 +11541,7 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -11518,7 +11590,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
@@ -11567,7 +11639,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -11616,7 +11688,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
@@ -11665,7 +11737,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -11714,7 +11786,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -11879,7 +11951,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -11928,7 +12000,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -11977,7 +12049,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -12026,7 +12098,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -12092,7 +12164,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -12141,7 +12213,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -12190,7 +12262,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -12256,7 +12328,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -12322,7 +12394,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -12371,7 +12443,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -12437,7 +12509,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -12486,7 +12558,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -12552,7 +12624,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -12618,7 +12690,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -12684,7 +12756,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
@@ -12750,7 +12822,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -12812,7 +12884,7 @@
       <c r="G28" s="18" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr">
@@ -12823,7 +12895,7 @@
       <c r="J28" s="18" t="inlineStr"/>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12946,7 @@
       <c r="G30" s="18" t="inlineStr"/>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -12885,7 +12957,7 @@
       <c r="J30" s="18" t="inlineStr"/>
       <c r="K30" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13110,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>✓ cross-disc</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -13185,7 +13257,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -13234,7 +13306,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -13282,7 +13354,7 @@
       <c r="G8" s="18" t="inlineStr"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>⚠ wrong_leaf</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -13293,7 +13365,7 @@
       <c r="J8" s="18" t="inlineStr"/>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -13344,7 +13416,7 @@
       <c r="G10" s="18" t="inlineStr"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>⚠ wrong_leaf</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -13359,7 +13431,7 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13469,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -13446,7 +13518,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -13495,7 +13567,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -13544,7 +13616,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>✓ cross-disc</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -13597,7 +13669,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -13667,7 +13739,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -13720,7 +13792,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -13773,7 +13845,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -13843,7 +13915,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -13895,7 +13967,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -13948,7 +14020,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -14001,7 +14073,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
@@ -14054,7 +14126,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -14106,7 +14178,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -14176,7 +14248,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -14246,7 +14318,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -14308,7 +14380,7 @@
       <c r="G32" s="18" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>⚠ wrong_leaf</t>
+          <t>❌ blank — ÚRS online</t>
         </is>
       </c>
       <c r="I32" s="18" t="inlineStr">
@@ -14323,7 +14395,7 @@
       </c>
       <c r="K32" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14450,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -14427,7 +14499,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -14493,7 +14565,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -14559,7 +14631,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>? needs_lookup</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_HSV" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_PSV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_VRN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260217_SKLAD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Composite_Decomposition_Map" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PENDING_DECISIONS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="260219_DUM_HSV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="260219_DUM_PSV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="260219_DUM_VRN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="260217_SKLAD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composite_Decomposition_Map" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PENDING_DECISIONS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'260219_DUM_HSV'!$A$1:$K$1</definedName>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -1075,26 +1075,26 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
         <v>14</v>
       </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -1110,21 +1110,21 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -1170,17 +1170,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1190,7 +1190,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -1200,7 +1200,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -1210,7 +1210,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -1230,7 +1230,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -1240,7 +1240,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -1250,7 +1250,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -1260,17 +1260,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1280,7 +1280,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -1290,7 +1290,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -1300,17 +1300,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1320,7 +1320,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -1330,7 +1330,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -1340,7 +1340,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,74 +1590,64 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>996</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>1</v>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>METODIKA + PATTERN COMPLIANCE</t>
+        </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>METODIKA + PATTERN COMPLIANCE</t>
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>• Terasa A2 korekce: HSV1.005a = 636311 família (dlaždice NA TERČE, NE 762 carpentry)</t>
         </is>
@@ -1666,6 +1656,7 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A112:C112"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A117:C117"/>
@@ -1673,7 +1664,6 @@
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A4:C4"/>
@@ -1691,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1767,7 +1757,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-1 Zemní práce  (16 atomic operací) ━━</t>
+          <t>━━ HSV-1 Zemní práce  (18 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -1939,7 +1929,7 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Kladení betonové dlažby tl. 50 mm do kladecího lože z kamenné drti 4-8 mm tl. 40 mm — anglický dvorek</t>
+          <t>Kladení betonové dlažby tl. 50 mm — anglický dvorek</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1991,7 +1981,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Podkladní nosná vrstva z kamenné drti frakce 4-8 mm tl. 150 mm + zhutnění — anglický dvorek</t>
+          <t>Kladecí vrstva z kamenné drti frakce 4-8 mm tl. 40 mm — anglický dvorek</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -2003,7 +1993,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="15">
-        <f> HSV1.004 plocha 30 m²</f>
+        <f> HSV1.004 plocha dvorku 30 m²</f>
         <v/>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -2028,7 +2018,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Podklad ze štěrkodrti (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Kladecí lože pod dlažbu (564 família) — řez C-C, dříve sloučeno s dlažbou (op a).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2033,7 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Úprava + zhutnění zemní pláně na Edef ≥ 30 MPa — anglický dvorek</t>
+          <t>Podkladní nosná vrstva z kamenné drti frakce 4-8 mm tl. 150 mm + zhutnění — anglický dvorek</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -2060,7 +2050,7 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -2080,7 +2070,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Podklad ze štěrkodrti (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2085,7 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Kladení betonových dlaždic tl. 50 mm na rektifikovatelné terče výšky ~50 mm — terasa za opěrnou stěnou</t>
+          <t>Úprava + zhutnění zemní pláně na Edef ≥ 30 MPa — anglický dvorek</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -2107,84 +2097,80 @@
         <v>30</v>
       </c>
       <c r="F9" s="15">
+        <f> HSV1.004 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.004 → HSV1.004d</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>Anglický dvorek</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Osazení rektifikovatelných terčů výšky ~50 mm na betonové dlaždice — terasa za opěrnou stěnou (nesou dřevěnou pochozí vrstvu PSV76.002)</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="18">
         <f> HSV1.005 plocha terasy 30 m²</f>
         <v/>
       </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>636311</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.005 → HSV1.005a</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>A2 KOREKCE: dlaždice NA TERČE → 636311 família (NE 762 carpentry — stará dřevěná kompozice nahrazena betonovými dlaždicemi na terče per Alexander Phase 5).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>HSV-1 Zemní práce</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Štěrkový podsyp frakce 16/32 mm tl. 100 mm — terasa</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
-        <v/>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.005 → HSV1.005b</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Terasa</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>Podklad štěrkopísek (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>Rektifikovatelné terče — spec systém (família needs_lookup). Nesou dřevěný rošt + prkna (PSV76.002 Truhlář, 762).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2185,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Hrubý podsyp z kamenné drti frakce 4/8 mm tl. 150 mm — terasa</t>
+          <t>Betonové dlaždice tl. 50 mm jako roznášecí (nosná) vrstva POD rektifikovatelné terče — terasa</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -2211,7 +2197,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
+        <f> HSV1.005 plocha terasy 30 m²</f>
         <v/>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -2226,7 +2212,7 @@
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.005 → HSV1.005c</t>
+          <t>260219_dum.HSV1.005 → HSV1.005b</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
@@ -2236,7 +2222,7 @@
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>Podklad štěrkodrť (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>ŘEZ C-C OPRAVA: dlaždice = roznášecí vrstva POD terče (NE 636311 'na terče' — to byla chyba). Roznášecí betonová dlaždice na podsypu → 564/596 família. Leaf Stage 3.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2237,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Geotextilie separační pod podsyp terasy</t>
+          <t>Štěrkový podsyp frakce 16/32 mm tl. 100 mm — terasa</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -2268,120 +2254,131 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.005 → HSV1.005c</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>Terasa</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Podklad štěrkopísek (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Hrubý podsyp z kamenné drti frakce 4/8 mm tl. 150 mm — terasa</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.005 → HSV1.005d</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>Terasa</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Podklad štěrkodrť (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Geotextilie separační pod podsyp terasy</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.005 → HSV1.005d</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.005 → HSV1.005e</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Geotextilie (693 família) nebo zahrnuto v 564.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>HSV-1 Zemní práce</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Pažení a rozepření dočasných výkopů příložné, hl. do 2 m, v zemině třídy 3</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>obvod rýh BV 2×(10+1.2) × hloubka 1.6</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>151101101</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.006</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>HSV-1 Zemní práce</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Vodorovné přemístění výkopku — odvoz na deponii do 8 km vč. skládkovného (zemina F4)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F14" s="18">
-        <f> V hloubení rýh BV + figura dvorek (12.6 + 6.0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.007</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr"/>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2396,35 +2393,35 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Zhutněný štěrkopískový zásyp + lože pod ŽB deskou 1.NP, Edef2 ≥ 30 MPa na pláni / 45 MPa na štěrku</t>
+          <t>Pažení a rozepření dočasných výkopů příložné, hl. do 2 m, v zemině třídy 3</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha_1NP × 0.15 m štěrkové lože (uvažovat 83 m² × 0.15)</t>
+          <t>obvod rýh BV 2×(10+1.2) × hloubka 1.6</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>151101101</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.008</t>
+          <t>260219_dum.HSV1.006</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr"/>
@@ -2435,98 +2432,95 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>HSV-1 Zemní práce</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F16" s="15">
-        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Vodorovné přemístění výkopku — odvoz na deponii do 8 km vč. skládkovného (zemina F4)</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F16" s="18">
+        <f> V hloubení rýh BV + figura dvorek (12.6 + 6.0)</f>
         <v/>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.015 → HSV1.015a</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="G16" s="18" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.007</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr"/>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>HSV-1 Zemní práce</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F17" s="15">
-        <f> HSV1.015 délka drenáže 12 m</f>
-        <v/>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.015 → HSV1.015b</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr"/>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>Obsyp drenáže (212/174 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Zhutněný štěrkopískový zásyp + lože pod ŽB deskou 1.NP, Edef2 ≥ 30 MPa na pláni / 45 MPa na štěrku</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>podlahova_plocha_1NP × 0.15 m štěrkové lože (uvažovat 83 m² × 0.15)</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.008</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2535,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -2553,188 +2547,190 @@
         <v>12</v>
       </c>
       <c r="F18" s="15">
+        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <v/>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.015 → HSV1.015a</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="15">
+        <f> HSV1.015 délka drenáže 12 m</f>
+        <v/>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.015 → HSV1.015b</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>Obsyp drenáže (212/174 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="15">
         <f> HSV1.015 délka 12 m</f>
         <v/>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>693</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.015 → HSV1.015c</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr"/>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Geotextilie obal + napojení (693 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-2 Základové a ŽB  (13 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Bílá vana ČBS 02 — pata úhlové opěrné stěny 250×1200 mm × L=10 m, C25/30 XC3 XF1 XA1 CL0.4 Dmax22 S3</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>0.25 × 1.20 × 10 = 3.0</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>274321321</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.001</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Bílá vana ČBS 02 — stěna úhlová tl. 250 mm × výška 2050 mm × L=10 m, beton C25/30 XC3 XF1 XA1 (trhliny max 0.20 mm)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>0.25 × 2.05 × 10 = 5.13</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>274321321</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.002</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Systémové oboustranné bednění bílé vany — DOKA Framax / PERI MAXIMO, vč. těsnění pracovních spár bobtnavý pásek bentonit (TZ §5.5)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>65</v>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr"/>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2749,25 +2745,25 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Výztuž bílé vany B500B 120 kg/m³ (empirická sazba Methvin pro úhlové opěrné stěny W0)</t>
+          <t>Bílá vana ČBS 02 — stěna úhlová tl. 250 mm × výška 2050 mm × L=10 m, beton C25/30 XC3 XF1 XA1 (trhliny max 0.20 mm)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>975</v>
+        <v>5.12</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>(3.0+5.13) × 120 = 976</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>273361821</t>
+          <t>0.25 × 2.05 × 10 = 5.13</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>274321321</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -2777,7 +2773,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.004</t>
+          <t>260219_dum.HSV2.002</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
@@ -2798,7 +2794,7 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Separační PE fólie pod základovou patou bílé vany (povinná dle ČBS 02)</t>
+          <t>Systémové oboustranné bednění bílé vany — DOKA Framax / PERI MAXIMO, vč. těsnění pracovních spár bobtnavý pásek bentonit (TZ §5.5)</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -2807,11 +2803,11 @@
         </is>
       </c>
       <c r="E24" s="19" t="n">
-        <v>13.2</v>
+        <v>65</v>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>1.20 × 10 × 1.10 přesah = 13.2</t>
+          <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr"/>
@@ -2822,7 +2818,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.005</t>
+          <t>260219_dum.HSV2.003</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr"/>
@@ -2843,25 +2839,25 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Mokré ošetřování betonu bílé vany min. 7 dní dle ČSN EN 13670 + ČBS 02 (kontrola trhlin max 0.20 mm)</t>
+          <t>Výztuž bílé vany B500B 120 kg/m³ (empirická sazba Methvin pro úhlové opěrné stěny W0)</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>53</v>
+        <v>975</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>viditelná plocha BV pro ošetřování ~53</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>279351102</t>
+          <t>(3.0+5.13) × 120 = 976</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.006</t>
+          <t>260219_dum.HSV2.004</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
@@ -2882,96 +2878,96 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>ŽB pozední věnec 300×250 mm po obvodu nadezdívky 3.NP, beton C25/30 XC1 + výztuž 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>274321311</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.007</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Separační PE fólie pod základovou patou bílé vany (povinná dle ČBS 02)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>1.20 × 10 × 1.10 přesah = 13.2</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.005</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr"/>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n">
+      <c r="A27" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Bednění pozedního věnce systémové oboustranné</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Mokré ošetřování betonu bílé vany min. 7 dní dle ČSN EN 13670 + ČBS 02 (kontrola trhlin max 0.20 mm)</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.008</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr"/>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="E27" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>viditelná plocha BV pro ošetřování ~53</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>279351102</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.006</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2986,25 +2982,25 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Výztuž B500B věnce 100 kg/m³ (Methvin sazba pro pozední věnce)</t>
+          <t>ŽB pozední věnec 300×250 mm po obvodu nadezdívky 3.NP, beton C25/30 XC1 + výztuž 100 kg/m³</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>310</v>
+        <v>2.9</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>3.1 × 100 = 310</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>273361821</t>
+          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>274321311</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -3014,7 +3010,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.009</t>
+          <t>260219_dum.HSV2.007</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
@@ -3025,55 +3021,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Nabetonávka stropu 2.NP/3.NP — beton C25/30 XC1 tl. 60 mm nad vlnu trapézového plechu 40S/160</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>104.4 m² × 0.06 m = 6.26</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>274321111</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.010</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Bednění pozedního věnce systémové oboustranné</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.008</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr"/>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3076,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Výztuž nabetonávky kari síť 5/100/100 (cca 4.4 kg/m²)</t>
+          <t>Výztuž B500B věnce 100 kg/m³ (Methvin sazba pro pozední věnce)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -3097,16 +3085,16 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>459</v>
+        <v>310</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>104.4 m² × 4.4 kg/m² = 459</t>
+          <t>3.1 × 100 = 310</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>273362441</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -3116,14 +3104,10 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.011</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV2.009</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3141,7 +3125,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>ŽB deska podlahy 1.NP na terénu tl. 150 mm, C25/30 XC2 + vyztužení kari 6/150/150 + okrajové pruty</t>
+          <t>Nabetonávka stropu 2.NP/3.NP — beton C25/30 XC1 tl. 60 mm nad vlnu trapézového plechu 40S/160</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -3150,16 +3134,16 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>10.96</v>
+        <v>6.26</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
+          <t>104.4 m² × 0.06 m = 6.26</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>273321311</t>
+          <t>274321111</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -3169,12 +3153,12 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.012</t>
+          <t>260219_dum.HSV2.010</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
@@ -3194,7 +3178,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Výztuž ŽB desky 1.NP — kari 6/150/150 + B500B okrajové pruty (~75 kg/m³ Methvin)</t>
+          <t>Výztuž nabetonávky kari síť 5/100/100 (cca 4.4 kg/m²)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -3203,16 +3187,16 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>825</v>
+        <v>459</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>11.0 × 75 = 825</t>
+          <t>104.4 m² × 4.4 kg/m² = 459</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273362441</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -3222,67 +3206,103 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.013</t>
+          <t>260219_dum.HSV2.011</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>ŽB deska podlahy 1.NP na terénu tl. 150 mm, C25/30 XC2 + vyztužení kari 6/150/150 + okrajové pruty</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>273321311</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.012</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-3 Svislé konstrukce  (7 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Lokální dozdívky a přizdívky z cihel plných pálených P10 na MVC M10 (uvedeno v TZ statika §4)</t>
+          <t>Výztuž ŽB desky 1.NP — kari 6/150/150 + B500B okrajové pruty (~75 kg/m³ Methvin)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>4</v>
+        <v>825</v>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
+          <t>11.0 × 75 = 825</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>311232511</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -3292,12 +3312,12 @@
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.001</t>
+          <t>260219_dum.HSV2.013</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>S01, S02</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -3307,57 +3327,21 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Nadezdívka 3.NP a čela vikýřů — Porotherm 30 Profi P10 na maltu pro tenké spáry, výška 2.65 m</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>311321411</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-3 Svislé konstrukce  (7 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3370,25 +3354,25 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Ocelové překlady IPN160 ve dvojici nad otvory pro nové dveře/okna v 1.NP a 2.NP (8 otvorů odhad)</t>
+          <t>Lokální dozdívky a přizdívky z cihel plných pálených P10 na MVC M10 (uvedeno v TZ statika §4)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>317143112</t>
+          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>311232511</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -3398,12 +3382,12 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.003</t>
+          <t>260219_dum.HSV3.001</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S02</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
@@ -3423,40 +3407,40 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maltové uložení překladů IPN160 — MC25 tl. 50 mm + kari 5/100/100 (po obou stranách otvoru)</t>
+          <t>Nadezdívka 3.NP a čela vikýřů — Porotherm 30 Profi P10 na maltu pro tenké spáry, výška 2.65 m</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>16</v>
+        <v>71.8</v>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>8 otvorů × 2 strany = 16 uložení</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>317242421</t>
+          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>311321411</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.004</t>
+          <t>260219_dum.HSV3.002</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -3476,7 +3460,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Zesílení ostění úhelníky L100/10 dvojicí u otvoru u komínového tělesa (statická limitace)</t>
+          <t>Ocelové překlady IPN160 ve dvojici nad otvory pro nové dveře/okna v 1.NP a 2.NP (8 otvorů odhad)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -3485,26 +3469,26 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>767131120</t>
+          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>317143112</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.005</t>
+          <t>260219_dum.HSV3.003</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -3529,7 +3513,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Dočasné podstojkování stávajících přiléhajících stropů při osazování IPN překladů (8 otvorů)</t>
+          <t>Maltové uložení překladů IPN160 — MC25 tl. 50 mm + kari 5/100/100 (po obou stranách otvoru)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -3538,15 +3522,16 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" s="11">
-        <f> počet překladů (po jednom podstojkování per otvor)</f>
-        <v/>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>962081120</t>
+        <v>16</v>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>8 otvorů × 2 strany = 16 uložení</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>317242421</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -3556,10 +3541,14 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.006</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV3.004</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3577,40 +3566,40 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Nové příčky z pórobetonových tvárnic 150 mm na lepidlo + dilatovány od stropu</t>
+          <t>Zesílení ostění úhelníky L100/10 dvojicí u otvoru u komínového tělesa (statická limitace)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>87.7</v>
+        <v>4</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha × 0.4 (typický rozsah příček 30-50%)</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>342241211</t>
+          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>767131120</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.007</t>
+          <t>260219_dum.HSV3.005</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
@@ -3620,52 +3609,83 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-4 Vodorovné  (14 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
+      <c r="A41" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Dočasné podstojkování stávajících přiléhajících stropů při osazování IPN překladů (8 otvorů)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="11">
+        <f> počet překladů (po jednom podstojkování per otvor)</f>
+        <v/>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>962081120</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV3.006</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Ocelová stropnice IPE180 1.NP v pozici nové příčky 2.NP — dodávka + montáž (1 ks × ~5 m)</t>
+          <t>Nové příčky z pórobetonových tvárnic 150 mm na lepidlo + dilatovány od stropu</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>94</v>
+        <v>87.7</v>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
+          <t>podlahova_plocha × 0.4 (typický rozsah příček 30-50%)</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>342241211</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -3675,10 +3695,14 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV3.007</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3686,57 +3710,21 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Ocelobetonový strop 2.NP/3.NP — stropnice IPE180 á 1000 mm × rozpon ~8 m × ~8 ks</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>1203</v>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV4.002</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="K43" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-4 Vodorovné  (14 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -3749,7 +3737,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop — výztuha 2×HEA180 trakt do ulice (Fibichova), dl. ~10 m</t>
+          <t>Ocelová stropnice IPE180 1.NP v pozici nové příčky 2.NP — dodávka + montáž (1 ks × ~5 m)</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -3758,11 +3746,11 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>710</v>
+        <v>94</v>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -3777,14 +3765,10 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV4.001</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3802,7 +3786,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop — výztuha HEA200 dvorní trakt, dl. ~10 m</t>
+          <t>Ocelobetonový strop 2.NP/3.NP — stropnice IPE180 á 1000 mm × rozpon ~8 m × ~8 ks</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -3811,14 +3795,14 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>423</v>
+        <v>1203</v>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
+          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>411321414</t>
         </is>
@@ -3830,7 +3814,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.004</t>
+          <t>260219_dum.HSV4.002</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
@@ -3855,20 +3839,21 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trapézový plech 40S/160 tl. 0.75 mm — dodávka + montáž na stropnice IPE180</t>
+          <t>Ocelobetonový strop — výztuha 2×HEA180 trakt do ulice (Fibichova), dl. ~10 m</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F46" s="11">
-        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
-        <v/>
+        <v>710</v>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+        </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3867,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.005</t>
+          <t>260219_dum.HSV4.003</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -3907,24 +3892,25 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Protipožární SDK podhled pod trapézovým plechem (EI 30 dle PBŘ — ocelobeton + SDK)</t>
+          <t>Ocelobetonový strop — výztuha HEA200 dvorní trakt, dl. ~10 m</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F47" s="11">
-        <f> plocha trapézu 104.4 m²</f>
-        <v/>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>342213131</t>
+        <v>423</v>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -3934,7 +3920,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.006</t>
+          <t>260219_dum.HSV4.004</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
@@ -3959,40 +3945,39 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Vyvezení původního zásypu z cihelné klenby 1.PP/1.NP — manuálně + odvoz</t>
+          <t>Trapézový plech 40S/160 tl. 0.75 mm — dodávka + montáž na stropnice IPE180</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>974031150</t>
+        <v>104.4</v>
+      </c>
+      <c r="F48" s="11">
+        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.007</t>
+          <t>260219_dum.HSV4.005</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
@@ -4012,25 +3997,24 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Nový zásyp klenby 1.PP/1.NP — perlitbeton (lehký zásyp) tl. 100 mm</t>
+          <t>Protipožární SDK podhled pod trapézovým plechem (EI 30 dle PBŘ — ocelobeton + SDK)</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>271223111</t>
+        <v>104.4</v>
+      </c>
+      <c r="F49" s="11">
+        <f> plocha trapézu 104.4 m²</f>
+        <v/>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>342213131</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -4040,12 +4024,12 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.008</t>
+          <t>260219_dum.HSV4.006</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -4065,35 +4049,35 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Plastická perlitbetonová roznášecí vrstva tl. 50 mm nad zásypem klenby</t>
+          <t>Vyvezení původního zásypu z cihelné klenby 1.PP/1.NP — manuálně + odvoz</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
+          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>974031150</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.009</t>
+          <t>260219_dum.HSV4.007</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
@@ -4118,25 +4102,25 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Strop trámový 1.NP/2.NP — sejmutí podlah, demontáž záklopu a zásypu shora (zachovat prkenný záklop na trámech)</t>
+          <t>Nový zásyp klenby 1.PP/1.NP — perlitbeton (lehký zásyp) tl. 100 mm</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>974041141</t>
+          <t>271223111</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -4146,12 +4130,12 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.010</t>
+          <t>260219_dum.HSV4.008</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
@@ -4171,7 +4155,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Tepelná izolace minerální vata mezi trámy stropu 1.NP/2.NP, tl. 180 mm (= trám 60/180)</t>
+          <t>Plastická perlitbetonová roznášecí vrstva tl. 50 mm nad zásypem klenby</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -4180,15 +4164,16 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="F52" s="11">
-        <f> plocha stropu</f>
-        <v/>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>713121121</t>
+        <v>50</v>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>631321311</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -4198,12 +4183,12 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.011</t>
+          <t>260219_dum.HSV4.009</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
@@ -4223,7 +4208,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Protipožární SDK podhled zespodu trámového stropu (EI 30 dle PBŘ)</t>
+          <t>Strop trámový 1.NP/2.NP — sejmutí podlah, demontáž záklopu a zásypu shora (zachovat prkenný záklop na trámech)</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -4234,13 +4219,14 @@
       <c r="E53" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F53" s="11">
-        <f> plocha stropu</f>
-        <v/>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+        </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>342213131</t>
+          <t>974041141</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -4250,7 +4236,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.012</t>
+          <t>260219_dum.HSV4.010</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
@@ -4275,25 +4261,24 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Suchá podlahová skladba 1.NP/2.NP — zásyp Liapor pro vyrovnání tl. 50 mm</t>
+          <t>Tepelná izolace minerální vata mezi trámy stropu 1.NP/2.NP, tl. 180 mm (= trám 60/180)</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>100 m² × 0.05 m = 5</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>631311114</t>
+        <v>100</v>
+      </c>
+      <c r="F54" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>713121121</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -4303,7 +4288,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.013</t>
+          <t>260219_dum.HSV4.011</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -4328,7 +4313,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Suchá podlahová skladba — sádrovláknité dílce Fermacell tl. 25 mm (dva 12.5 mm vrstvy)</t>
+          <t>Protipožární SDK podhled zespodu trámového stropu (EI 30 dle PBŘ)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -4345,7 +4330,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>771421111</t>
+          <t>342213131</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -4355,7 +4340,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.014</t>
+          <t>260219_dum.HSV4.012</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
@@ -4370,52 +4355,87 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-5 Krov + střecha  (16 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
+      <c r="A56" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Suchá podlahová skladba 1.NP/2.NP — zásyp Liapor pro vyrovnání tl. 50 mm</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>100 m² × 0.05 m = 5</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>631311114</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.013</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
+          <t>Suchá podlahová skladba — sádrovláknité dílce Fermacell tl. 25 mm (dva 12.5 mm vrstvy)</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>762331911</t>
+        <v>100</v>
+      </c>
+      <c r="F57" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>771421111</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -4425,10 +4445,14 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.001</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV4.014</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4436,53 +4460,21 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>762331912</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.002</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr"/>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Krov + střecha  (16 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -4495,7 +4487,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
+          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -4504,16 +4496,16 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>19.4</v>
+        <v>156</v>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
+          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>762331923</t>
+          <t>762331911</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -4523,7 +4515,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.003</t>
+          <t>260219_dum.HSV5.001</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr"/>
@@ -4544,7 +4536,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
+          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -4553,16 +4545,16 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>19.2</v>
+        <v>110</v>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>24 krokví × 0.8 m námětek = 19.2</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>762331911</t>
+          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>762331912</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -4572,7 +4564,7 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.004</t>
+          <t>260219_dum.HSV5.002</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -4593,25 +4585,25 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
+          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>608</v>
+        <v>19.4</v>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -4621,7 +4613,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.005</t>
+          <t>260219_dum.HSV5.003</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
@@ -4642,25 +4634,25 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
+          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>176</v>
+        <v>19.2</v>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
+          <t>24 krokví × 0.8 m námětek = 19.2</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331911</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -4670,7 +4662,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.006</t>
+          <t>260219_dum.HSV5.004</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -4691,24 +4683,25 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
+          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F63" s="11">
-        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
-        <v/>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>762341711</t>
+        <v>608</v>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -4718,14 +4711,10 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.007</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.005</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4743,25 +4732,25 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
+          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>155.034</v>
+        <v>176</v>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>141 × 1.1 přesah = 155</t>
+          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -4771,14 +4760,10 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.008</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.006</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4796,7 +4781,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
+          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -4808,22 +4793,22 @@
         <v>140.94</v>
       </c>
       <c r="F65" s="11">
-        <f> 141 m² (plocha krytiny krov)</f>
+        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
         <v/>
       </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>713131811</t>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.009</t>
+          <t>260219_dum.HSV5.007</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
@@ -4848,7 +4833,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
+          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -4866,7 +4851,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>712311111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -4876,7 +4861,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.010</t>
+          <t>260219_dum.HSV5.008</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -4901,7 +4886,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
+          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -4913,22 +4898,22 @@
         <v>140.94</v>
       </c>
       <c r="F67" s="11">
-        <f> 141 m²</f>
+        <f> 141 m² (plocha krytiny krov)</f>
         <v/>
       </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>762331923</t>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>713131811</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.011</t>
+          <t>260219_dum.HSV5.009</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
@@ -4953,7 +4938,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
+          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -4962,15 +4947,16 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F68" s="11">
-        <f> 141 m²</f>
-        <v/>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>762341711</t>
+        <v>155.034</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>712311111</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -4980,7 +4966,7 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.012</t>
+          <t>260219_dum.HSV5.010</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -5005,7 +4991,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
+          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -5017,12 +5003,12 @@
         <v>140.94</v>
       </c>
       <c r="F69" s="11">
-        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <f> 141 m²</f>
         <v/>
       </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>765791121</t>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -5032,7 +5018,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.013</t>
+          <t>260219_dum.HSV5.011</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
@@ -5057,7 +5043,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
+          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -5066,14 +5052,13 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>odhad — spací patro ~5 × 5 m</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
+        <v>140.94</v>
+      </c>
+      <c r="F70" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>762341711</t>
         </is>
@@ -5085,12 +5070,12 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.014</t>
+          <t>260219_dum.HSV5.012</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr">
@@ -5110,7 +5095,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -5119,16 +5104,15 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>4 vikýře × ~3 m² zděných čel = 12</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>311321411</t>
+        <v>140.94</v>
+      </c>
+      <c r="F71" s="11">
+        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <v/>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>765791121</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -5138,10 +5122,14 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.015</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.013</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5159,7 +5147,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
+          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -5168,16 +5156,16 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
+          <t>odhad — spací patro ~5 × 5 m</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>765791121</t>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -5187,12 +5175,12 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.016</t>
+          <t>260219_dum.HSV5.014</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>S12b</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
@@ -5202,52 +5190,84 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
+      <c r="A73" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>311321411</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.015</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
+          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
-        </is>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>962041141</t>
+          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>765791121</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -5257,10 +5277,14 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.001</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.016</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5268,48 +5292,21 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="n">
-        <v>68</v>
-      </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E75" s="19" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="F75" s="18">
-        <f> plocha krytiny ~141</f>
-        <v/>
-      </c>
-      <c r="G75" s="18" t="inlineStr"/>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.002</t>
-        </is>
-      </c>
-      <c r="J75" s="18" t="inlineStr"/>
-      <c r="K75" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="n"/>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="n">
@@ -5322,7 +5319,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -5331,16 +5328,16 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -5350,7 +5347,7 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.003</t>
+          <t>260219_dum.HSV6.001</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
@@ -5361,50 +5358,46 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="n">
+      <c r="A77" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B77" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F77" s="11">
-        <f> zastavěna 104.4 m²</f>
+      <c r="E77" s="19" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="F77" s="18">
+        <f> plocha krytiny ~141</f>
         <v/>
       </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.004</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="inlineStr"/>
-      <c r="K77" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="G77" s="18" t="inlineStr"/>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.002</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="inlineStr"/>
+      <c r="K77" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -5419,20 +5412,20 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -5447,7 +5440,7 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.005</t>
+          <t>260219_dum.HSV6.003</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr"/>
@@ -5468,25 +5461,24 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="F79" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -5496,7 +5488,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.006</t>
+          <t>260219_dum.HSV6.004</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -5517,7 +5509,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -5526,16 +5518,16 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
-        </is>
-      </c>
-      <c r="G80" s="13" t="inlineStr">
-        <is>
-          <t>781473810</t>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -5545,7 +5537,7 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.007</t>
+          <t>260219_dum.HSV6.005</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
@@ -5566,25 +5558,25 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>153.51</v>
+        <v>8</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -5594,7 +5586,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.008</t>
+          <t>260219_dum.HSV6.006</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -5615,25 +5607,25 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr">
-        <is>
-          <t>974041151</t>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>781473810</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -5643,7 +5635,7 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.009</t>
+          <t>260219_dum.HSV6.007</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
@@ -5664,25 +5656,25 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>25</v>
+        <v>153.51</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -5692,7 +5684,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.010</t>
+          <t>260219_dum.HSV6.008</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -5713,25 +5705,25 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -5741,7 +5733,7 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.011</t>
+          <t>260219_dum.HSV6.009</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
@@ -5762,25 +5754,25 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>56.5</v>
+        <v>25</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -5790,7 +5782,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.012</t>
+          <t>260219_dum.HSV6.010</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
@@ -5811,7 +5803,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -5820,26 +5812,26 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
-        </is>
-      </c>
-      <c r="G86" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>725900001</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.013</t>
+          <t>260219_dum.HSV6.011</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
@@ -5860,35 +5852,35 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>2</v>
+        <v>56.5</v>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
-        </is>
-      </c>
-      <c r="G87" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>997013501</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.014</t>
+          <t>260219_dum.HSV6.012</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
@@ -5909,7 +5901,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -5918,26 +5910,26 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
-        </is>
-      </c>
-      <c r="G88" s="11" t="inlineStr">
-        <is>
-          <t>968072456</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.013</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
@@ -5958,35 +5950,35 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³, × 10 m³ buffer pro suti + manipulace = 6.0 m³</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.016</t>
+          <t>260219_dum.HSV6.014</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
@@ -6007,25 +5999,25 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
-        </is>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>961044111</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -6035,7 +6027,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.017</t>
+          <t>260219_dum.HSV6.015</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
@@ -6046,176 +6038,170 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="n"/>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="9" t="n"/>
-      <c r="F91" s="9" t="n"/>
-      <c r="G91" s="9" t="n"/>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="9" t="n"/>
-      <c r="J91" s="9" t="n"/>
-      <c r="K91" s="9" t="n"/>
+      <c r="A91" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+        </is>
+      </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>962024141</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.016</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr"/>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.017</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E92" s="12" t="n">
+      <c r="E94" s="12" t="n">
         <v>276.7</v>
       </c>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
-      <c r="G92" s="11" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="J92" s="11" t="inlineStr">
+      <c r="J94" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F93" s="15">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G93" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002a</t>
-        </is>
-      </c>
-      <c r="J93" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K93" s="15" t="inlineStr">
-        <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="14" t="n">
-        <v>86</v>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
-        </is>
-      </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F94" s="15">
-        <f> HSV7.002 plocha 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G94" s="15" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002b</t>
-        </is>
-      </c>
-      <c r="J94" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K94" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6216,7 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
@@ -6239,10 +6225,10 @@
         </is>
       </c>
       <c r="E95" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F95" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
         <v/>
       </c>
       <c r="G95" s="15" t="inlineStr">
@@ -6257,17 +6243,17 @@
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
       <c r="J95" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6268,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -6291,15 +6277,15 @@
         </is>
       </c>
       <c r="E96" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F96" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha 276.7 m²</f>
         <v/>
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
@@ -6309,17 +6295,17 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+          <t>260219_dum.HSV7.002 → HSV7.002b</t>
         </is>
       </c>
       <c r="J96" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6334,24 +6320,24 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E97" s="16" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="F97" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr">
@@ -6361,17 +6347,17 @@
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6386,148 +6372,252 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F98" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+        </is>
+      </c>
+      <c r="J98" s="15" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F99" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+        </is>
+      </c>
+      <c r="J99" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr">
+        <is>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
           <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
-      <c r="D98" s="14" t="inlineStr">
+      <c r="D100" s="14" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E98" s="16" t="n">
+      <c r="E100" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F98" s="15">
+      <c r="F100" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G98" s="15" t="inlineStr">
+      <c r="G100" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr">
+      <c r="H100" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I98" s="15" t="inlineStr">
+      <c r="I100" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J98" s="15" t="inlineStr">
+      <c r="J100" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K98" s="15" t="inlineStr">
+      <c r="K100" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C99" s="11" t="inlineStr">
+      <c r="C101" s="11" t="inlineStr">
         <is>
           <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E101" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="11" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
         <is>
           <t>622221221</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.005</t>
         </is>
       </c>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="J101" s="11" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="n">
-        <v>92</v>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C100" s="11" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="E102" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F100" s="11" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G100" s="13" t="inlineStr">
+      <c r="G102" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J100" s="11" t="inlineStr">
+      <c r="J102" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K100" s="11" t="inlineStr">
+      <c r="K102" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6536,13 +6626,13 @@
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <mergeCells count="7">
-    <mergeCell ref="A91:K91"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A73:K73"/>
-    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6554,7 +6644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8953,7 +9043,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-76 Truhlář  (2 atomic operací) ━━</t>
+          <t>━━ PSV-76 Truhlář  (3 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B53" s="9" t="n"/>
@@ -9017,119 +9107,117 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>PSV-76 Truhlář</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>DXF dum_situace PLOT_DREVENY_04 = 57 INSERTs (timber pattern blocks) → odhad terasa ~30 m². NEPOUŽITELNÉ pro 3.NP biodeska (PLOT_DREVENY_04 v dum_DPZ = 0).</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV76.002</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr"/>
-      <c r="K55" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="F55" s="15">
+        <f> PSV76.002 plocha terasy 30 m²</f>
+        <v/>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.002 → PSV76.002a</t>
+        </is>
+      </c>
+      <c r="J55" s="15" t="inlineStr"/>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>ŘEZ C-C: dřevěný rošt z hranolů (NE hliníkový — oprava). Família 762 tesařské/truhlářské. Terče viz HSV1.005a.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>PSV-76 Truhlář</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F56" s="15">
+        <f> PSV76.002 plocha terasy 30 m²</f>
+        <v/>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.002 → PSV76.002b</t>
+        </is>
+      </c>
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>Pochozí dřevěná vrstva (garapa prkna 25 mm). Família 762. Kód 771474112 byl WRONG domain (dlaždice) — odstraněn (Pattern 26).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-76 Výplně otvorů  (12 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>PSV-76 Výplně otvorů</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>766621011</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV76.001</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr"/>
-      <c r="K57" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
@@ -9142,7 +9230,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -9151,14 +9239,14 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>766621011</t>
         </is>
@@ -9170,7 +9258,7 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.001</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
@@ -9191,7 +9279,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -9200,11 +9288,11 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -9219,7 +9307,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr"/>
@@ -9240,7 +9328,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -9249,11 +9337,11 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -9268,7 +9356,7 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.003</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -9289,7 +9377,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -9298,11 +9386,11 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -9317,7 +9405,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.005</t>
+          <t>260219_dum.PSV76.004</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
@@ -9338,7 +9426,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -9351,7 +9439,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -9366,7 +9454,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.006</t>
+          <t>260219_dum.PSV76.005</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -9387,7 +9475,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -9396,11 +9484,11 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -9415,7 +9503,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.007</t>
+          <t>260219_dum.PSV76.006</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr"/>
@@ -9436,7 +9524,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -9445,16 +9533,16 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -9464,7 +9552,7 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.008</t>
+          <t>260219_dum.PSV76.007</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr"/>
@@ -9485,7 +9573,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -9494,16 +9582,16 @@
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>TZ ARS — vstupní plastové dveře</t>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -9513,7 +9601,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.009</t>
+          <t>260219_dum.PSV76.008</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr"/>
@@ -9534,7 +9622,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -9543,16 +9631,16 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
+          <t>TZ ARS — vstupní plastové dveře</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -9562,7 +9650,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.010</t>
+          <t>260219_dum.PSV76.009</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr"/>
@@ -9583,7 +9671,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -9592,16 +9680,16 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -9611,7 +9699,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.013</t>
+          <t>260219_dum.PSV76.010</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr"/>
@@ -9632,7 +9720,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -9641,16 +9729,16 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -9660,7 +9748,7 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.014</t>
+          <t>260219_dum.PSV76.013</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr"/>
@@ -9671,70 +9759,70 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>764811112</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.014</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-76 Zámečnictví  (4 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>PSV-76 Zámečnictví</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>767531111</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV76.001</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr"/>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="n">
@@ -9747,7 +9835,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -9760,7 +9848,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>1 schodiště do podkroví (TZ ARS)</t>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -9775,7 +9863,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.001</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr"/>
@@ -9796,25 +9884,25 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>2 vstupy</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>767532111</t>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>767531111</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -9824,7 +9912,7 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr"/>
@@ -9845,25 +9933,25 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+          <t>2 vstupy</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -9873,7 +9961,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.003</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr"/>
@@ -9884,116 +9972,117 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnictví</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>767163115</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.004</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-77 Podlahy  (9 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="9" t="n"/>
-      <c r="I74" s="9" t="n"/>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="n"/>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>PSV-77 Podlahy</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="E76" s="12" t="n">
         <v>171.5</v>
       </c>
-      <c r="F75" s="11" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>776511820</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.001</t>
         </is>
       </c>
-      <c r="J75" s="11" t="inlineStr"/>
-      <c r="K75" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F76" s="15">
-        <f> PSV77.002 plocha 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G76" s="15" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV77.002 → PSV77.002a</t>
-        </is>
-      </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr">
-        <is>
-          <t>Dlažba lepená vč. lepidla (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10097,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
+          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -10035,13 +10124,13 @@
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002 → PSV77.002b</t>
+          <t>260219_dum.PSV77.002 → PSV77.002a</t>
         </is>
       </c>
       <c r="J77" s="15" t="inlineStr"/>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>Spárování (771 família) — často zahrnuto v kladení.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dlažba lepená vč. lepidla (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10145,7 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
+          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
@@ -10065,10 +10154,10 @@
         </is>
       </c>
       <c r="E78" s="16" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="F78" s="15">
-        <f> PSV77.003 plocha 32.4 m²</f>
+        <f> PSV77.002 plocha 13.5 m²</f>
         <v/>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -10083,13 +10172,13 @@
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003 → PSV77.003a</t>
+          <t>260219_dum.PSV77.002 → PSV77.002b</t>
         </is>
       </c>
       <c r="J78" s="15" t="inlineStr"/>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>Dlažba lepená (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Spárování (771 família) — často zahrnuto v kladení.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10193,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
@@ -10131,62 +10220,61 @@
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003 → PSV77.003b</t>
+          <t>260219_dum.PSV77.003 → PSV77.003a</t>
         </is>
       </c>
       <c r="J79" s="15" t="inlineStr"/>
       <c r="K79" s="15" t="inlineStr">
         <is>
+          <t>Dlažba lepená (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F80" s="15">
+        <f> PSV77.003 plocha 32.4 m²</f>
+        <v/>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.003 → PSV77.003b</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
           <t>Spárování (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr">
-        <is>
-          <t>766411111</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV77.004</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr"/>
-      <c r="K80" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10289,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -10210,16 +10298,16 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -10229,7 +10317,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.005</t>
+          <t>260219_dum.PSV77.004</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -10250,25 +10338,25 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -10278,7 +10366,7 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.006</t>
+          <t>260219_dum.PSV77.005</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
@@ -10299,7 +10387,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -10308,16 +10396,16 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -10327,7 +10415,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.007</t>
+          <t>260219_dum.PSV77.006</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -10338,69 +10426,70 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>771274107</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.007</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-78 Povrchové úpravy  (20 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="n"/>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>PSV-78 Povrchové úpravy</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="F85" s="15">
-        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
-        <v/>
-      </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="H85" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV78.001 → PSV78.001a</t>
-        </is>
-      </c>
-      <c r="J85" s="15" t="inlineStr"/>
-      <c r="K85" s="15" t="inlineStr">
-        <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="9" t="n"/>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
@@ -10413,7 +10502,7 @@
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -10425,7 +10514,7 @@
         <v>78.2</v>
       </c>
       <c r="F86" s="15">
-        <f> PSV78.001 plocha 78.2 m²</f>
+        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
         <v/>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -10440,13 +10529,13 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001 → PSV78.001b</t>
+          <t>260219_dum.PSV78.001 → PSV78.001a</t>
         </is>
       </c>
       <c r="J86" s="15" t="inlineStr"/>
       <c r="K86" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10550,7 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
+          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
@@ -10470,10 +10559,10 @@
         </is>
       </c>
       <c r="E87" s="16" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="F87" s="15">
-        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
+        <f> PSV78.001 plocha 78.2 m²</f>
         <v/>
       </c>
       <c r="G87" s="15" t="inlineStr">
@@ -10488,13 +10577,13 @@
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002 → PSV78.002a</t>
+          <t>260219_dum.PSV78.001 → PSV78.001b</t>
         </is>
       </c>
       <c r="J87" s="15" t="inlineStr"/>
       <c r="K87" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10598,7 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -10521,7 +10610,7 @@
         <v>208.4</v>
       </c>
       <c r="F88" s="15">
-        <f> PSV78.002 plocha 208.4 m²</f>
+        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
         <v/>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -10536,13 +10625,13 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002 → PSV78.002b</t>
+          <t>260219_dum.PSV78.002 → PSV78.002a</t>
         </is>
       </c>
       <c r="J88" s="15" t="inlineStr"/>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10646,7 @@
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -10566,10 +10655,10 @@
         </is>
       </c>
       <c r="E89" s="16" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="F89" s="15">
-        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
+        <f> PSV78.002 plocha 208.4 m²</f>
         <v/>
       </c>
       <c r="G89" s="15" t="inlineStr">
@@ -10584,13 +10673,13 @@
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003 → PSV78.003a</t>
+          <t>260219_dum.PSV78.002 → PSV78.002b</t>
         </is>
       </c>
       <c r="J89" s="15" t="inlineStr"/>
       <c r="K89" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10694,7 @@
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -10617,7 +10706,7 @@
         <v>201.6</v>
       </c>
       <c r="F90" s="15">
-        <f> PSV78.003 plocha 201.6 m²</f>
+        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
         <v/>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -10632,13 +10721,13 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003 → PSV78.003b</t>
+          <t>260219_dum.PSV78.003 → PSV78.003a</t>
         </is>
       </c>
       <c r="J90" s="15" t="inlineStr"/>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10742,7 @@
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -10662,10 +10751,10 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="F91" s="15">
-        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <f> PSV78.003 plocha 201.6 m²</f>
         <v/>
       </c>
       <c r="G91" s="15" t="inlineStr">
@@ -10680,13 +10769,13 @@
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004 → PSV78.004a</t>
+          <t>260219_dum.PSV78.003 → PSV78.003b</t>
         </is>
       </c>
       <c r="J91" s="15" t="inlineStr"/>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10790,7 @@
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -10713,77 +10802,76 @@
         <v>179.1</v>
       </c>
       <c r="F92" s="15">
+        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <v/>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV78.004 → PSV78.004a</t>
+        </is>
+      </c>
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>PSV-78 Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="F93" s="15">
         <f> PSV78.004 plocha 179.1 m²</f>
         <v/>
       </c>
-      <c r="G92" s="15" t="inlineStr">
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr">
+      <c r="H93" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.004 → PSV78.004b</t>
         </is>
       </c>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr">
+      <c r="J93" s="15" t="inlineStr"/>
+      <c r="K93" s="15" t="inlineStr">
         <is>
           <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>PSV-78 Povrchové úpravy</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>612471141</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV78.005</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr"/>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10886,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -10807,11 +10895,11 @@
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
@@ -10826,7 +10914,7 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.006</t>
+          <t>260219_dum.PSV78.005</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr"/>
@@ -10847,7 +10935,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -10856,11 +10944,11 @@
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -10875,7 +10963,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.007</t>
+          <t>260219_dum.PSV78.006</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
@@ -10896,7 +10984,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -10905,16 +10993,16 @@
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -10924,7 +11012,7 @@
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.008</t>
+          <t>260219_dum.PSV78.007</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr"/>
@@ -10945,7 +11033,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -10954,11 +11042,11 @@
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -10973,7 +11061,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.009</t>
+          <t>260219_dum.PSV78.008</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr"/>
@@ -10994,7 +11082,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -11003,11 +11091,11 @@
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -11022,7 +11110,7 @@
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.010</t>
+          <t>260219_dum.PSV78.009</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr"/>
@@ -11043,7 +11131,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -11052,11 +11140,11 @@
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -11071,7 +11159,7 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.011</t>
+          <t>260219_dum.PSV78.010</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
@@ -11092,7 +11180,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -11101,16 +11189,16 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -11120,7 +11208,7 @@
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012</t>
+          <t>260219_dum.PSV78.011</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr"/>
@@ -11141,7 +11229,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -11150,11 +11238,11 @@
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -11169,7 +11257,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.1_PP</t>
+          <t>260219_dum.PSV78.012</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
@@ -11190,7 +11278,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -11199,11 +11287,11 @@
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -11218,7 +11306,7 @@
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.1_NP</t>
+          <t>260219_dum.PSV78.012.1_PP</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr"/>
@@ -11239,7 +11327,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -11248,11 +11336,11 @@
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>247.5</v>
+        <v>254.5</v>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
@@ -11267,7 +11355,7 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.2_NP</t>
+          <t>260219_dum.PSV78.012.1_NP</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr"/>
@@ -11288,7 +11376,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -11297,11 +11385,11 @@
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -11316,7 +11404,7 @@
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.3_NP</t>
+          <t>260219_dum.PSV78.012.2_NP</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr"/>
@@ -11327,70 +11415,70 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>PSV-78 Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>784121011</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV78.012.3_NP</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-95 Detekce požární  (2 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
-      <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t>PSV-95 Detekce požární</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F106" s="11" t="inlineStr">
-        <is>
-          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
-        </is>
-      </c>
-      <c r="G106" s="13" t="inlineStr">
-        <is>
-          <t>375211101</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV95.001</t>
-        </is>
-      </c>
-      <c r="J106" s="11" t="inlineStr"/>
-      <c r="K106" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="n">
@@ -11403,7 +11491,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -11412,16 +11500,16 @@
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>TZ PBŘ — min. 1 ks 34A</t>
-        </is>
-      </c>
-      <c r="G107" s="11" t="inlineStr">
-        <is>
-          <t>966067121</t>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>375211101</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -11431,7 +11519,7 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV95.002</t>
+          <t>260219_dum.PSV95.001</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr"/>
@@ -11442,70 +11530,70 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>PSV-95 Detekce požární</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>966067121</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV95.002</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>━━ M-21 ELI silnoproud  (7 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n"/>
-      <c r="C108" s="9" t="n"/>
-      <c r="D108" s="9" t="n"/>
-      <c r="E108" s="9" t="n"/>
-      <c r="F108" s="9" t="n"/>
-      <c r="G108" s="9" t="n"/>
-      <c r="H108" s="9" t="n"/>
-      <c r="I108" s="9" t="n"/>
-      <c r="J108" s="9" t="n"/>
-      <c r="K108" s="9" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="n">
-        <v>96</v>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t>M-21 ELI silnoproud</t>
-        </is>
-      </c>
-      <c r="C109" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="11" t="inlineStr">
-        <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr">
-        <is>
-          <t>210010011</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.M21.001</t>
-        </is>
-      </c>
-      <c r="J109" s="11" t="inlineStr"/>
-      <c r="K109" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="9" t="n"/>
+      <c r="H109" s="9" t="n"/>
+      <c r="I109" s="9" t="n"/>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="n">
@@ -11518,25 +11606,25 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -11546,7 +11634,7 @@
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.002</t>
+          <t>260219_dum.M21.001</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr"/>
@@ -11567,25 +11655,25 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -11595,7 +11683,7 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.003</t>
+          <t>260219_dum.M21.002</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -11616,25 +11704,25 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -11644,7 +11732,7 @@
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.004</t>
+          <t>260219_dum.M21.003</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr"/>
@@ -11665,7 +11753,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -11674,16 +11762,16 @@
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -11693,7 +11781,7 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.005</t>
+          <t>260219_dum.M21.004</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -11714,25 +11802,25 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -11742,7 +11830,7 @@
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.006</t>
+          <t>260219_dum.M21.005</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr"/>
@@ -11763,7 +11851,7 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -11776,12 +11864,12 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -11791,11 +11879,60 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.007</t>
+          <t>260219_dum.M21.006</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
       <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>996019011</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.M21.007</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr"/>
+      <c r="K116" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11806,16 +11943,16 @@
   <mergeCells count="12">
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A74:K74"/>
-    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A57:K57"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A84:K84"/>
-    <mergeCell ref="A108:K108"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A106:K106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14670,7 +14807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14744,11 +14881,11 @@
         <v>30</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>HSV1.004a, HSV1.004b, HSV1.004c</t>
+          <t>HSV1.004a, HSV1.004b, HSV1.004c, HSV1.004d</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14902,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm +</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče vý</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
@@ -14777,11 +14914,11 @@
         <v>30</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>HSV1.005a, HSV1.005b, HSV1.005c, HSV1.005d</t>
+          <t>HSV1.005a, HSV1.005b, HSV1.005c, HSV1.005d, HSV1.005e</t>
         </is>
       </c>
     </row>
@@ -14920,17 +15057,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -14939,21 +15076,21 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>PSV77.002a, PSV77.002b</t>
+          <t>PSV76.002a, PSV76.002b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003</t>
+          <t>260219_dum.PSV77.002</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -14963,7 +15100,7 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -14972,31 +15109,31 @@
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>PSV77.003a, PSV77.003b</t>
+          <t>PSV77.002a, PSV77.002b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001</t>
+          <t>260219_dum.PSV77.003</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -15005,21 +15142,21 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>78.2</v>
+        <v>32.4</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>PSV78.001a, PSV78.001b</t>
+          <t>PSV77.003a, PSV77.003b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002</t>
+          <t>260219_dum.PSV78.001</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -15029,7 +15166,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -15038,21 +15175,21 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>PSV78.002a, PSV78.002b</t>
+          <t>PSV78.001a, PSV78.001b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003</t>
+          <t>260219_dum.PSV78.002</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -15062,7 +15199,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -15071,21 +15208,21 @@
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>PSV78.003a, PSV78.003b</t>
+          <t>PSV78.002a, PSV78.002b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004</t>
+          <t>260219_dum.PSV78.003</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -15095,7 +15232,7 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -15104,54 +15241,54 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>PSV78.004a, PSV78.004b</t>
+          <t>PSV78.003a, PSV78.003b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.004</t>
+          <t>260219_dum.PSV78.004</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0</v>
+        <v>179.1</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
+          <t>PSV78.004a, PSV78.004b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.005</t>
+          <t>260219_dum.PSV72.004</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -15161,7 +15298,7 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -15177,14 +15314,14 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
+          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.006</t>
+          <t>260219_dum.PSV72.005</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -15194,7 +15331,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -15210,14 +15347,14 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
+          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.008</t>
+          <t>260219_dum.PSV72.006</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -15227,54 +15364,87 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>set</t>
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>260219_dum.PSV72.008</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>260219_dum.HSV1.015</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>HSV-1 Zemní práce</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E19" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F19" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
         </is>
@@ -15291,7 +15461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15411,27 +15581,102 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Sklad — svislá hydroizolace + drenáž stěn pod terénem (skladby S03a/S04) — DSP nespecifikuje</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř u projektanta zda skladby S03a/S04 zahrnují svislou hydroizolaci + drenáž stěn skladu pod terénem. Pokud ano → doplníme (penetrace + 2× asfalt. pás + nopová fólie + drenáž DN100 za S04) dle ploch pod terénem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Sněhové zábrany / protisněhové prvky — falcovaná krytina, VII. sněhová oblast</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř u projektanta / dodavatele krytiny zda jsou pro falc. krytinu v VII. sněhové oblasti požadovány sněhové zábrany. Pokud ano → doplníme bm dle délky okapů (zejména nad vstupy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Lemování komína a střešních prostupů — klempířský detail</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř zda komín nebo VZT/ZTI prostupy procházejí novou střechou → pokud ano, doplníme klempířské lemování (ks dle počtu prostupů).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="260219_DUM_HSV" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="260219_DUM_PSV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="260219_DUM_VRN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="260217_SKLAD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composite_Decomposition_Map" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PENDING_DECISIONS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_HSV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_PSV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260219_DUM_VRN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="260217_SKLAD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Composite_Decomposition_Map" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PENDING_DECISIONS" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'260219_DUM_HSV'!$A$1:$K$1</definedName>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -1075,26 +1075,26 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
         <v>14</v>
       </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -1110,21 +1110,21 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -1170,17 +1170,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1190,7 +1190,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -1200,7 +1200,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -1210,7 +1210,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -1230,7 +1230,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -1240,7 +1240,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -1250,7 +1250,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -1260,17 +1260,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1280,7 +1280,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -1290,7 +1290,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -1300,17 +1300,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1320,7 +1320,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -1330,7 +1330,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -1340,7 +1340,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,74 +1590,64 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>996</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>1</v>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>METODIKA + PATTERN COMPLIANCE</t>
+        </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>METODIKA + PATTERN COMPLIANCE</t>
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>• Terasa A2 korekce: HSV1.005a = 636311 família (dlaždice NA TERČE, NE 762 carpentry)</t>
         </is>
@@ -1666,6 +1656,7 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A112:C112"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A117:C117"/>
@@ -1673,7 +1664,6 @@
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A4:C4"/>
@@ -1691,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1767,7 +1757,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-1 Zemní práce  (16 atomic operací) ━━</t>
+          <t>━━ HSV-1 Zemní práce  (18 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -1939,7 +1929,7 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Kladení betonové dlažby tl. 50 mm do kladecího lože z kamenné drti 4-8 mm tl. 40 mm — anglický dvorek</t>
+          <t>Kladení betonové dlažby tl. 50 mm — anglický dvorek</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1991,7 +1981,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Podkladní nosná vrstva z kamenné drti frakce 4-8 mm tl. 150 mm + zhutnění — anglický dvorek</t>
+          <t>Kladecí vrstva z kamenné drti frakce 4-8 mm tl. 40 mm — anglický dvorek</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -2003,7 +1993,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="15">
-        <f> HSV1.004 plocha 30 m²</f>
+        <f> HSV1.004 plocha dvorku 30 m²</f>
         <v/>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -2028,7 +2018,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Podklad ze štěrkodrti (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Kladecí lože pod dlažbu (564 família) — řez C-C, dříve sloučeno s dlažbou (op a).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2033,7 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Úprava + zhutnění zemní pláně na Edef ≥ 30 MPa — anglický dvorek</t>
+          <t>Podkladní nosná vrstva z kamenné drti frakce 4-8 mm tl. 150 mm + zhutnění — anglický dvorek</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -2060,7 +2050,7 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -2080,7 +2070,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Podklad ze štěrkodrti (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2085,7 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Kladení betonových dlaždic tl. 50 mm na rektifikovatelné terče výšky ~50 mm — terasa za opěrnou stěnou</t>
+          <t>Úprava + zhutnění zemní pláně na Edef ≥ 30 MPa — anglický dvorek</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -2107,84 +2097,80 @@
         <v>30</v>
       </c>
       <c r="F9" s="15">
+        <f> HSV1.004 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.004 → HSV1.004d</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>Anglický dvorek</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Úprava pláně (181 família) — případně zahrnuto v zemních pracích.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Osazení rektifikovatelných terčů výšky ~50 mm na betonové dlaždice — terasa za opěrnou stěnou (nesou dřevěnou pochozí vrstvu PSV76.002)</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="18">
         <f> HSV1.005 plocha terasy 30 m²</f>
         <v/>
       </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>636311</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.005 → HSV1.005a</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>A2 KOREKCE: dlaždice NA TERČE → 636311 família (NE 762 carpentry — stará dřevěná kompozice nahrazena betonovými dlaždicemi na terče per Alexander Phase 5).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>HSV-1 Zemní práce</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Štěrkový podsyp frakce 16/32 mm tl. 100 mm — terasa</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
-        <v/>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.005 → HSV1.005b</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Terasa</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>Podklad štěrkopísek (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>Rektifikovatelné terče — spec systém (família needs_lookup). Nesou dřevěný rošt + prkna (PSV76.002 Truhlář, 762).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2185,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Hrubý podsyp z kamenné drti frakce 4/8 mm tl. 150 mm — terasa</t>
+          <t>Betonové dlaždice tl. 50 mm jako roznášecí (nosná) vrstva POD rektifikovatelné terče — terasa</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -2211,7 +2197,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
+        <f> HSV1.005 plocha terasy 30 m²</f>
         <v/>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -2226,7 +2212,7 @@
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.005 → HSV1.005c</t>
+          <t>260219_dum.HSV1.005 → HSV1.005b</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
@@ -2236,7 +2222,7 @@
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>Podklad štěrkodrť (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>ŘEZ C-C OPRAVA: dlaždice = roznášecí vrstva POD terče (NE 636311 'na terče' — to byla chyba). Roznášecí betonová dlaždice na podsypu → 564/596 família. Leaf Stage 3.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2237,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Geotextilie separační pod podsyp terasy</t>
+          <t>Štěrkový podsyp frakce 16/32 mm tl. 100 mm — terasa</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -2268,120 +2254,131 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.005 → HSV1.005c</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>Terasa</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Podklad štěrkopísek (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Hrubý podsyp z kamenné drti frakce 4/8 mm tl. 150 mm — terasa</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.005 → HSV1.005d</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>Terasa</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Podklad štěrkodrť (564 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Geotextilie separační pod podsyp terasy</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="15">
+        <f> HSV1.005 plocha 30 m²</f>
+        <v/>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.005 → HSV1.005d</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.005 → HSV1.005e</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>Terasa</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Geotextilie (693 família) nebo zahrnuto v 564.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>HSV-1 Zemní práce</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Pažení a rozepření dočasných výkopů příložné, hl. do 2 m, v zemině třídy 3</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>obvod rýh BV 2×(10+1.2) × hloubka 1.6</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>151101101</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.006</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>HSV-1 Zemní práce</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Vodorovné přemístění výkopku — odvoz na deponii do 8 km vč. skládkovného (zemina F4)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F14" s="18">
-        <f> V hloubení rýh BV + figura dvorek (12.6 + 6.0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.007</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr"/>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -2396,35 +2393,35 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Zhutněný štěrkopískový zásyp + lože pod ŽB deskou 1.NP, Edef2 ≥ 30 MPa na pláni / 45 MPa na štěrku</t>
+          <t>Pažení a rozepření dočasných výkopů příložné, hl. do 2 m, v zemině třídy 3</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha_1NP × 0.15 m štěrkové lože (uvažovat 83 m² × 0.15)</t>
+          <t>obvod rýh BV 2×(10+1.2) × hloubka 1.6</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>151101101</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.008</t>
+          <t>260219_dum.HSV1.006</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr"/>
@@ -2435,98 +2432,95 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>HSV-1 Zemní práce</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F16" s="15">
-        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Vodorovné přemístění výkopku — odvoz na deponii do 8 km vč. skládkovného (zemina F4)</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F16" s="18">
+        <f> V hloubení rýh BV + figura dvorek (12.6 + 6.0)</f>
         <v/>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.015 → HSV1.015a</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="G16" s="18" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.007</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr"/>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>HSV-1 Zemní práce</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F17" s="15">
-        <f> HSV1.015 délka drenáže 12 m</f>
-        <v/>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV1.015 → HSV1.015b</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr"/>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>Obsyp drenáže (212/174 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Zhutněný štěrkopískový zásyp + lože pod ŽB deskou 1.NP, Edef2 ≥ 30 MPa na pláni / 45 MPa na štěrku</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>podlahova_plocha_1NP × 0.15 m štěrkové lože (uvažovat 83 m² × 0.15)</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.008</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2535,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -2553,188 +2547,190 @@
         <v>12</v>
       </c>
       <c r="F18" s="15">
+        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <v/>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.015 → HSV1.015a</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>Drenáž trubní (212 família URS zemní) NEBO 8xx ZTI vnější (items.json má 877315111 cross-discipline).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="15">
+        <f> HSV1.015 délka drenáže 12 m</f>
+        <v/>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.015 → HSV1.015b</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>Obsyp drenáže (212/174 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="15">
         <f> HSV1.015 délka 12 m</f>
         <v/>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>693</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV1.015 → HSV1.015c</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr"/>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Geotextilie obal + napojení (693 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-2 Základové a ŽB  (13 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Bílá vana ČBS 02 — pata úhlové opěrné stěny 250×1200 mm × L=10 m, C25/30 XC3 XF1 XA1 CL0.4 Dmax22 S3</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>0.25 × 1.20 × 10 = 3.0</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>274321321</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.001</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Bílá vana ČBS 02 — stěna úhlová tl. 250 mm × výška 2050 mm × L=10 m, beton C25/30 XC3 XF1 XA1 (trhliny max 0.20 mm)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>0.25 × 2.05 × 10 = 5.13</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>274321321</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.002</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Systémové oboustranné bednění bílé vany — DOKA Framax / PERI MAXIMO, vč. těsnění pracovních spár bobtnavý pásek bentonit (TZ §5.5)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>65</v>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr"/>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2749,25 +2745,25 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Výztuž bílé vany B500B 120 kg/m³ (empirická sazba Methvin pro úhlové opěrné stěny W0)</t>
+          <t>Bílá vana ČBS 02 — stěna úhlová tl. 250 mm × výška 2050 mm × L=10 m, beton C25/30 XC3 XF1 XA1 (trhliny max 0.20 mm)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>975</v>
+        <v>5.12</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>(3.0+5.13) × 120 = 976</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>273361821</t>
+          <t>0.25 × 2.05 × 10 = 5.13</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>274321321</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -2777,7 +2773,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.004</t>
+          <t>260219_dum.HSV2.002</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
@@ -2798,7 +2794,7 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Separační PE fólie pod základovou patou bílé vany (povinná dle ČBS 02)</t>
+          <t>Systémové oboustranné bednění bílé vany — DOKA Framax / PERI MAXIMO, vč. těsnění pracovních spár bobtnavý pásek bentonit (TZ §5.5)</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -2807,11 +2803,11 @@
         </is>
       </c>
       <c r="E24" s="19" t="n">
-        <v>13.2</v>
+        <v>65</v>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>1.20 × 10 × 1.10 přesah = 13.2</t>
+          <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr"/>
@@ -2822,7 +2818,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.005</t>
+          <t>260219_dum.HSV2.003</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr"/>
@@ -2843,25 +2839,25 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Mokré ošetřování betonu bílé vany min. 7 dní dle ČSN EN 13670 + ČBS 02 (kontrola trhlin max 0.20 mm)</t>
+          <t>Výztuž bílé vany B500B 120 kg/m³ (empirická sazba Methvin pro úhlové opěrné stěny W0)</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>53</v>
+        <v>975</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>viditelná plocha BV pro ošetřování ~53</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>279351102</t>
+          <t>(3.0+5.13) × 120 = 976</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.006</t>
+          <t>260219_dum.HSV2.004</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
@@ -2882,96 +2878,96 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>ŽB pozední věnec 300×250 mm po obvodu nadezdívky 3.NP, beton C25/30 XC1 + výztuž 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>274321311</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.007</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Separační PE fólie pod základovou patou bílé vany (povinná dle ČBS 02)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>1.20 × 10 × 1.10 přesah = 13.2</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.005</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr"/>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n">
+      <c r="A27" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Bednění pozedního věnce systémové oboustranné</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Mokré ošetřování betonu bílé vany min. 7 dní dle ČSN EN 13670 + ČBS 02 (kontrola trhlin max 0.20 mm)</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.008</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr"/>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="E27" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>viditelná plocha BV pro ošetřování ~53</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>279351102</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.006</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2986,25 +2982,25 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Výztuž B500B věnce 100 kg/m³ (Methvin sazba pro pozední věnce)</t>
+          <t>ŽB pozední věnec 300×250 mm po obvodu nadezdívky 3.NP, beton C25/30 XC1 + výztuž 100 kg/m³</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>310</v>
+        <v>2.9</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>3.1 × 100 = 310</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>273361821</t>
+          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>274321311</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -3014,7 +3010,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.009</t>
+          <t>260219_dum.HSV2.007</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
@@ -3025,55 +3021,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Nabetonávka stropu 2.NP/3.NP — beton C25/30 XC1 tl. 60 mm nad vlnu trapézového plechu 40S/160</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>104.4 m² × 0.06 m = 6.26</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>274321111</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.010</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Bednění pozedního věnce systémové oboustranné</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.008</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr"/>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3076,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Výztuž nabetonávky kari síť 5/100/100 (cca 4.4 kg/m²)</t>
+          <t>Výztuž B500B věnce 100 kg/m³ (Methvin sazba pro pozední věnce)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -3097,16 +3085,16 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>459</v>
+        <v>310</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>104.4 m² × 4.4 kg/m² = 459</t>
+          <t>3.1 × 100 = 310</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>273362441</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -3116,14 +3104,10 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.011</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV2.009</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3141,7 +3125,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>ŽB deska podlahy 1.NP na terénu tl. 150 mm, C25/30 XC2 + vyztužení kari 6/150/150 + okrajové pruty</t>
+          <t>Nabetonávka stropu 2.NP/3.NP — beton C25/30 XC1 tl. 60 mm nad vlnu trapézového plechu 40S/160</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -3150,16 +3134,16 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>10.96</v>
+        <v>6.26</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
+          <t>104.4 m² × 0.06 m = 6.26</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>273321311</t>
+          <t>274321111</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -3169,12 +3153,12 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.012</t>
+          <t>260219_dum.HSV2.010</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
@@ -3194,7 +3178,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Výztuž ŽB desky 1.NP — kari 6/150/150 + B500B okrajové pruty (~75 kg/m³ Methvin)</t>
+          <t>Výztuž nabetonávky kari síť 5/100/100 (cca 4.4 kg/m²)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -3203,16 +3187,16 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>825</v>
+        <v>459</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>11.0 × 75 = 825</t>
+          <t>104.4 m² × 4.4 kg/m² = 459</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273362441</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -3222,67 +3206,103 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.013</t>
+          <t>260219_dum.HSV2.011</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>ŽB deska podlahy 1.NP na terénu tl. 150 mm, C25/30 XC2 + vyztužení kari 6/150/150 + okrajové pruty</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>273321311</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.012</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-3 Svislé konstrukce  (7 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Lokální dozdívky a přizdívky z cihel plných pálených P10 na MVC M10 (uvedeno v TZ statika §4)</t>
+          <t>Výztuž ŽB desky 1.NP — kari 6/150/150 + B500B okrajové pruty (~75 kg/m³ Methvin)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>4</v>
+        <v>825</v>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
+          <t>11.0 × 75 = 825</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>311232511</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -3292,12 +3312,12 @@
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.001</t>
+          <t>260219_dum.HSV2.013</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>S01, S02</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -3307,57 +3327,21 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Nadezdívka 3.NP a čela vikýřů — Porotherm 30 Profi P10 na maltu pro tenké spáry, výška 2.65 m</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>311321411</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-3 Svislé konstrukce  (7 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3370,25 +3354,25 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Ocelové překlady IPN160 ve dvojici nad otvory pro nové dveře/okna v 1.NP a 2.NP (8 otvorů odhad)</t>
+          <t>Lokální dozdívky a přizdívky z cihel plných pálených P10 na MVC M10 (uvedeno v TZ statika §4)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>317143112</t>
+          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>311232511</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -3398,12 +3382,12 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.003</t>
+          <t>260219_dum.HSV3.001</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S02</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
@@ -3423,40 +3407,40 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maltové uložení překladů IPN160 — MC25 tl. 50 mm + kari 5/100/100 (po obou stranách otvoru)</t>
+          <t>Nadezdívka 3.NP a čela vikýřů — Porotherm 30 Profi P10 na maltu pro tenké spáry, výška 2.65 m</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>16</v>
+        <v>71.8</v>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>8 otvorů × 2 strany = 16 uložení</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>317242421</t>
+          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>311321411</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.004</t>
+          <t>260219_dum.HSV3.002</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -3476,7 +3460,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Zesílení ostění úhelníky L100/10 dvojicí u otvoru u komínového tělesa (statická limitace)</t>
+          <t>Ocelové překlady IPN160 ve dvojici nad otvory pro nové dveře/okna v 1.NP a 2.NP (8 otvorů odhad)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -3485,26 +3469,26 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>767131120</t>
+          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>317143112</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.005</t>
+          <t>260219_dum.HSV3.003</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -3529,7 +3513,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Dočasné podstojkování stávajících přiléhajících stropů při osazování IPN překladů (8 otvorů)</t>
+          <t>Maltové uložení překladů IPN160 — MC25 tl. 50 mm + kari 5/100/100 (po obou stranách otvoru)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -3538,15 +3522,16 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" s="11">
-        <f> počet překladů (po jednom podstojkování per otvor)</f>
-        <v/>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>962081120</t>
+        <v>16</v>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>8 otvorů × 2 strany = 16 uložení</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>317242421</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -3556,10 +3541,14 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.006</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV3.004</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3577,40 +3566,40 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Nové příčky z pórobetonových tvárnic 150 mm na lepidlo + dilatovány od stropu</t>
+          <t>Zesílení ostění úhelníky L100/10 dvojicí u otvoru u komínového tělesa (statická limitace)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>87.7</v>
+        <v>4</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha × 0.4 (typický rozsah příček 30-50%)</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>342241211</t>
+          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>767131120</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.007</t>
+          <t>260219_dum.HSV3.005</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
@@ -3620,52 +3609,83 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-4 Vodorovné  (14 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
+      <c r="A41" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Dočasné podstojkování stávajících přiléhajících stropů při osazování IPN překladů (8 otvorů)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="11">
+        <f> počet překladů (po jednom podstojkování per otvor)</f>
+        <v/>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>962081120</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV3.006</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Ocelová stropnice IPE180 1.NP v pozici nové příčky 2.NP — dodávka + montáž (1 ks × ~5 m)</t>
+          <t>Nové příčky z pórobetonových tvárnic 150 mm na lepidlo + dilatovány od stropu</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>94</v>
+        <v>87.7</v>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
+          <t>podlahova_plocha × 0.4 (typický rozsah příček 30-50%)</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>342241211</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -3675,10 +3695,14 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV3.007</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3686,57 +3710,21 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Ocelobetonový strop 2.NP/3.NP — stropnice IPE180 á 1000 mm × rozpon ~8 m × ~8 ks</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>1203</v>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV4.002</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="K43" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-4 Vodorovné  (14 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -3749,7 +3737,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop — výztuha 2×HEA180 trakt do ulice (Fibichova), dl. ~10 m</t>
+          <t>Ocelová stropnice IPE180 1.NP v pozici nové příčky 2.NP — dodávka + montáž (1 ks × ~5 m)</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -3758,11 +3746,11 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>710</v>
+        <v>94</v>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -3777,14 +3765,10 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV4.001</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3802,7 +3786,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop — výztuha HEA200 dvorní trakt, dl. ~10 m</t>
+          <t>Ocelobetonový strop 2.NP/3.NP — stropnice IPE180 á 1000 mm × rozpon ~8 m × ~8 ks</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -3811,14 +3795,14 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>423</v>
+        <v>1203</v>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
+          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>411321414</t>
         </is>
@@ -3830,7 +3814,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.004</t>
+          <t>260219_dum.HSV4.002</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
@@ -3855,20 +3839,21 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trapézový plech 40S/160 tl. 0.75 mm — dodávka + montáž na stropnice IPE180</t>
+          <t>Ocelobetonový strop — výztuha 2×HEA180 trakt do ulice (Fibichova), dl. ~10 m</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F46" s="11">
-        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
-        <v/>
+        <v>710</v>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+        </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3867,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.005</t>
+          <t>260219_dum.HSV4.003</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -3907,24 +3892,25 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Protipožární SDK podhled pod trapézovým plechem (EI 30 dle PBŘ — ocelobeton + SDK)</t>
+          <t>Ocelobetonový strop — výztuha HEA200 dvorní trakt, dl. ~10 m</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F47" s="11">
-        <f> plocha trapézu 104.4 m²</f>
-        <v/>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>342213131</t>
+        <v>423</v>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -3934,7 +3920,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.006</t>
+          <t>260219_dum.HSV4.004</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
@@ -3959,40 +3945,39 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Vyvezení původního zásypu z cihelné klenby 1.PP/1.NP — manuálně + odvoz</t>
+          <t>Trapézový plech 40S/160 tl. 0.75 mm — dodávka + montáž na stropnice IPE180</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>974031150</t>
+        <v>104.4</v>
+      </c>
+      <c r="F48" s="11">
+        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.007</t>
+          <t>260219_dum.HSV4.005</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
@@ -4012,25 +3997,24 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Nový zásyp klenby 1.PP/1.NP — perlitbeton (lehký zásyp) tl. 100 mm</t>
+          <t>Protipožární SDK podhled pod trapézovým plechem (EI 30 dle PBŘ — ocelobeton + SDK)</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>271223111</t>
+        <v>104.4</v>
+      </c>
+      <c r="F49" s="11">
+        <f> plocha trapézu 104.4 m²</f>
+        <v/>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>342213131</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -4040,12 +4024,12 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.008</t>
+          <t>260219_dum.HSV4.006</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -4065,35 +4049,35 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Plastická perlitbetonová roznášecí vrstva tl. 50 mm nad zásypem klenby</t>
+          <t>Vyvezení původního zásypu z cihelné klenby 1.PP/1.NP — manuálně + odvoz</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
+          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>974031150</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.009</t>
+          <t>260219_dum.HSV4.007</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
@@ -4118,25 +4102,25 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Strop trámový 1.NP/2.NP — sejmutí podlah, demontáž záklopu a zásypu shora (zachovat prkenný záklop na trámech)</t>
+          <t>Nový zásyp klenby 1.PP/1.NP — perlitbeton (lehký zásyp) tl. 100 mm</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>974041141</t>
+          <t>271223111</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -4146,12 +4130,12 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.010</t>
+          <t>260219_dum.HSV4.008</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
@@ -4171,7 +4155,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Tepelná izolace minerální vata mezi trámy stropu 1.NP/2.NP, tl. 180 mm (= trám 60/180)</t>
+          <t>Plastická perlitbetonová roznášecí vrstva tl. 50 mm nad zásypem klenby</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -4180,15 +4164,16 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="F52" s="11">
-        <f> plocha stropu</f>
-        <v/>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>713121121</t>
+        <v>50</v>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>631321311</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -4198,12 +4183,12 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.011</t>
+          <t>260219_dum.HSV4.009</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
@@ -4223,7 +4208,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Protipožární SDK podhled zespodu trámového stropu (EI 30 dle PBŘ)</t>
+          <t>Strop trámový 1.NP/2.NP — sejmutí podlah, demontáž záklopu a zásypu shora (zachovat prkenný záklop na trámech)</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -4234,13 +4219,14 @@
       <c r="E53" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F53" s="11">
-        <f> plocha stropu</f>
-        <v/>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+        </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>342213131</t>
+          <t>974041141</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -4250,7 +4236,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.012</t>
+          <t>260219_dum.HSV4.010</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
@@ -4275,25 +4261,24 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Suchá podlahová skladba 1.NP/2.NP — zásyp Liapor pro vyrovnání tl. 50 mm</t>
+          <t>Tepelná izolace minerální vata mezi trámy stropu 1.NP/2.NP, tl. 180 mm (= trám 60/180)</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>100 m² × 0.05 m = 5</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>631311114</t>
+        <v>100</v>
+      </c>
+      <c r="F54" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>713121121</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -4303,7 +4288,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.013</t>
+          <t>260219_dum.HSV4.011</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -4328,7 +4313,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Suchá podlahová skladba — sádrovláknité dílce Fermacell tl. 25 mm (dva 12.5 mm vrstvy)</t>
+          <t>Protipožární SDK podhled zespodu trámového stropu (EI 30 dle PBŘ)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -4345,7 +4330,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>771421111</t>
+          <t>342213131</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -4355,7 +4340,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.014</t>
+          <t>260219_dum.HSV4.012</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
@@ -4370,52 +4355,87 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-5 Krov + střecha  (16 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
+      <c r="A56" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Suchá podlahová skladba 1.NP/2.NP — zásyp Liapor pro vyrovnání tl. 50 mm</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>100 m² × 0.05 m = 5</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>631311114</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.013</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
+          <t>Suchá podlahová skladba — sádrovláknité dílce Fermacell tl. 25 mm (dva 12.5 mm vrstvy)</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>762331911</t>
+        <v>100</v>
+      </c>
+      <c r="F57" s="11">
+        <f> plocha stropu</f>
+        <v/>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>771421111</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -4425,10 +4445,14 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.001</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV4.014</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4436,53 +4460,21 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>762331912</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.002</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr"/>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Krov + střecha  (16 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -4495,7 +4487,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
+          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -4504,16 +4496,16 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>19.4</v>
+        <v>156</v>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
+          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>762331923</t>
+          <t>762331911</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -4523,7 +4515,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.003</t>
+          <t>260219_dum.HSV5.001</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr"/>
@@ -4544,7 +4536,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
+          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -4553,16 +4545,16 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>19.2</v>
+        <v>110</v>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>24 krokví × 0.8 m námětek = 19.2</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>762331911</t>
+          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>762331912</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -4572,7 +4564,7 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.004</t>
+          <t>260219_dum.HSV5.002</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -4593,25 +4585,25 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
+          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>608</v>
+        <v>19.4</v>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -4621,7 +4613,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.005</t>
+          <t>260219_dum.HSV5.003</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
@@ -4642,25 +4634,25 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
+          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>176</v>
+        <v>19.2</v>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
+          <t>24 krokví × 0.8 m námětek = 19.2</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331911</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -4670,7 +4662,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.006</t>
+          <t>260219_dum.HSV5.004</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -4691,24 +4683,25 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
+          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F63" s="11">
-        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
-        <v/>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>762341711</t>
+        <v>608</v>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -4718,14 +4711,10 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.007</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.005</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4743,25 +4732,25 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
+          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>155.034</v>
+        <v>176</v>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>141 × 1.1 přesah = 155</t>
+          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -4771,14 +4760,10 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.008</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.006</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4796,7 +4781,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
+          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -4808,22 +4793,22 @@
         <v>140.94</v>
       </c>
       <c r="F65" s="11">
-        <f> 141 m² (plocha krytiny krov)</f>
+        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
         <v/>
       </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>713131811</t>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.009</t>
+          <t>260219_dum.HSV5.007</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
@@ -4848,7 +4833,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
+          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -4866,7 +4851,7 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>712311111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -4876,7 +4861,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.010</t>
+          <t>260219_dum.HSV5.008</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -4901,7 +4886,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
+          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -4913,22 +4898,22 @@
         <v>140.94</v>
       </c>
       <c r="F67" s="11">
-        <f> 141 m²</f>
+        <f> 141 m² (plocha krytiny krov)</f>
         <v/>
       </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>762331923</t>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>713131811</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.011</t>
+          <t>260219_dum.HSV5.009</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
@@ -4953,7 +4938,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
+          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -4962,15 +4947,16 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F68" s="11">
-        <f> 141 m²</f>
-        <v/>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>762341711</t>
+        <v>155.034</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>712311111</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -4980,7 +4966,7 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.012</t>
+          <t>260219_dum.HSV5.010</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -5005,7 +4991,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
+          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -5017,12 +5003,12 @@
         <v>140.94</v>
       </c>
       <c r="F69" s="11">
-        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <f> 141 m²</f>
         <v/>
       </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>765791121</t>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -5032,7 +5018,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.013</t>
+          <t>260219_dum.HSV5.011</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
@@ -5057,7 +5043,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
+          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -5066,14 +5052,13 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>odhad — spací patro ~5 × 5 m</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
+        <v>140.94</v>
+      </c>
+      <c r="F70" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>762341711</t>
         </is>
@@ -5085,12 +5070,12 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.014</t>
+          <t>260219_dum.HSV5.012</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="K70" s="11" t="inlineStr">
@@ -5110,7 +5095,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -5119,16 +5104,15 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>4 vikýře × ~3 m² zděných čel = 12</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>311321411</t>
+        <v>140.94</v>
+      </c>
+      <c r="F71" s="11">
+        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <v/>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>765791121</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -5138,10 +5122,14 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.015</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.013</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5159,7 +5147,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
+          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -5168,16 +5156,16 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
+          <t>odhad — spací patro ~5 × 5 m</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>765791121</t>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -5187,12 +5175,12 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.016</t>
+          <t>260219_dum.HSV5.014</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>S12b</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
@@ -5202,52 +5190,84 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
+      <c r="A73" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>311321411</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.015</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
+          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
-        </is>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>962041141</t>
+          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>765791121</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -5257,10 +5277,14 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.001</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.016</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5268,48 +5292,21 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="n">
-        <v>68</v>
-      </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E75" s="19" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="F75" s="18">
-        <f> plocha krytiny ~141</f>
-        <v/>
-      </c>
-      <c r="G75" s="18" t="inlineStr"/>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.002</t>
-        </is>
-      </c>
-      <c r="J75" s="18" t="inlineStr"/>
-      <c r="K75" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="n"/>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="n">
@@ -5322,7 +5319,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -5331,16 +5328,16 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -5350,7 +5347,7 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.003</t>
+          <t>260219_dum.HSV6.001</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr"/>
@@ -5361,50 +5358,46 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="n">
+      <c r="A77" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B77" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F77" s="11">
-        <f> zastavěna 104.4 m²</f>
+      <c r="E77" s="19" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="F77" s="18">
+        <f> plocha krytiny ~141</f>
         <v/>
       </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.004</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="inlineStr"/>
-      <c r="K77" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="G77" s="18" t="inlineStr"/>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.002</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="inlineStr"/>
+      <c r="K77" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -5419,20 +5412,20 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -5447,7 +5440,7 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.005</t>
+          <t>260219_dum.HSV6.003</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr"/>
@@ -5468,25 +5461,24 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="F79" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -5496,7 +5488,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.006</t>
+          <t>260219_dum.HSV6.004</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -5517,7 +5509,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -5526,16 +5518,16 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
-        </is>
-      </c>
-      <c r="G80" s="13" t="inlineStr">
-        <is>
-          <t>781473810</t>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -5545,7 +5537,7 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.007</t>
+          <t>260219_dum.HSV6.005</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
@@ -5566,25 +5558,25 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>153.51</v>
+        <v>8</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -5594,7 +5586,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.008</t>
+          <t>260219_dum.HSV6.006</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -5615,25 +5607,25 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr">
-        <is>
-          <t>974041151</t>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>781473810</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -5643,7 +5635,7 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.009</t>
+          <t>260219_dum.HSV6.007</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
@@ -5664,25 +5656,25 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>25</v>
+        <v>153.51</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -5692,7 +5684,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.010</t>
+          <t>260219_dum.HSV6.008</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -5713,25 +5705,25 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -5741,7 +5733,7 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.011</t>
+          <t>260219_dum.HSV6.009</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
@@ -5762,25 +5754,25 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>56.5</v>
+        <v>25</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -5790,7 +5782,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.012</t>
+          <t>260219_dum.HSV6.010</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
@@ -5811,7 +5803,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -5820,26 +5812,26 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
-        </is>
-      </c>
-      <c r="G86" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>725900001</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.013</t>
+          <t>260219_dum.HSV6.011</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
@@ -5860,35 +5852,35 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>2</v>
+        <v>56.5</v>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
-        </is>
-      </c>
-      <c r="G87" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>997013501</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.014</t>
+          <t>260219_dum.HSV6.012</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
@@ -5909,7 +5901,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -5918,26 +5910,26 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
-        </is>
-      </c>
-      <c r="G88" s="11" t="inlineStr">
-        <is>
-          <t>968072456</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.013</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
@@ -5958,35 +5950,35 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³, × 10 m³ buffer pro suti + manipulace = 6.0 m³</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.016</t>
+          <t>260219_dum.HSV6.014</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
@@ -6007,25 +5999,25 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
-        </is>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>961044111</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -6035,7 +6027,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.017</t>
+          <t>260219_dum.HSV6.015</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
@@ -6046,176 +6038,170 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="n"/>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="9" t="n"/>
-      <c r="F91" s="9" t="n"/>
-      <c r="G91" s="9" t="n"/>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="9" t="n"/>
-      <c r="J91" s="9" t="n"/>
-      <c r="K91" s="9" t="n"/>
+      <c r="A91" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+        </is>
+      </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>962024141</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.016</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr"/>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.017</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E92" s="12" t="n">
+      <c r="E94" s="12" t="n">
         <v>276.7</v>
       </c>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
-      <c r="G92" s="11" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="J92" s="11" t="inlineStr">
+      <c r="J94" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F93" s="15">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G93" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002a</t>
-        </is>
-      </c>
-      <c r="J93" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K93" s="15" t="inlineStr">
-        <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="14" t="n">
-        <v>86</v>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
-        </is>
-      </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F94" s="15">
-        <f> HSV7.002 plocha 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G94" s="15" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002b</t>
-        </is>
-      </c>
-      <c r="J94" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K94" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6216,7 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
@@ -6239,10 +6225,10 @@
         </is>
       </c>
       <c r="E95" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F95" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
         <v/>
       </c>
       <c r="G95" s="15" t="inlineStr">
@@ -6257,17 +6243,17 @@
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
       <c r="J95" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6268,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -6291,15 +6277,15 @@
         </is>
       </c>
       <c r="E96" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F96" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha 276.7 m²</f>
         <v/>
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
@@ -6309,17 +6295,17 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+          <t>260219_dum.HSV7.002 → HSV7.002b</t>
         </is>
       </c>
       <c r="J96" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6334,24 +6320,24 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E97" s="16" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="F97" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr">
@@ -6361,17 +6347,17 @@
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6386,148 +6372,252 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F98" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+        </is>
+      </c>
+      <c r="J98" s="15" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F99" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+        </is>
+      </c>
+      <c r="J99" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr">
+        <is>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
           <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
-      <c r="D98" s="14" t="inlineStr">
+      <c r="D100" s="14" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E98" s="16" t="n">
+      <c r="E100" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F98" s="15">
+      <c r="F100" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G98" s="15" t="inlineStr">
+      <c r="G100" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr">
+      <c r="H100" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I98" s="15" t="inlineStr">
+      <c r="I100" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J98" s="15" t="inlineStr">
+      <c r="J100" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K98" s="15" t="inlineStr">
+      <c r="K100" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C99" s="11" t="inlineStr">
+      <c r="C101" s="11" t="inlineStr">
         <is>
           <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E101" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="11" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
         <is>
           <t>622221221</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.005</t>
         </is>
       </c>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="J101" s="11" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="n">
-        <v>92</v>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C100" s="11" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="E102" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F100" s="11" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G100" s="13" t="inlineStr">
+      <c r="G102" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J100" s="11" t="inlineStr">
+      <c r="J102" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K100" s="11" t="inlineStr">
+      <c r="K102" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6536,13 +6626,13 @@
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <mergeCells count="7">
-    <mergeCell ref="A91:K91"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A73:K73"/>
-    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6554,7 +6644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8953,7 +9043,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-76 Truhlář  (2 atomic operací) ━━</t>
+          <t>━━ PSV-76 Truhlář  (3 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B53" s="9" t="n"/>
@@ -9017,119 +9107,117 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>PSV-76 Truhlář</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>DXF dum_situace PLOT_DREVENY_04 = 57 INSERTs (timber pattern blocks) → odhad terasa ~30 m². NEPOUŽITELNÉ pro 3.NP biodeska (PLOT_DREVENY_04 v dum_DPZ = 0).</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV76.002</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="inlineStr"/>
-      <c r="K55" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="F55" s="15">
+        <f> PSV76.002 plocha terasy 30 m²</f>
+        <v/>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.002 → PSV76.002a</t>
+        </is>
+      </c>
+      <c r="J55" s="15" t="inlineStr"/>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>ŘEZ C-C: dřevěný rošt z hranolů (NE hliníkový — oprava). Família 762 tesařské/truhlářské. Terče viz HSV1.005a.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>PSV-76 Truhlář</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F56" s="15">
+        <f> PSV76.002 plocha terasy 30 m²</f>
+        <v/>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.002 → PSV76.002b</t>
+        </is>
+      </c>
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>Pochozí dřevěná vrstva (garapa prkna 25 mm). Família 762. Kód 771474112 byl WRONG domain (dlaždice) — odstraněn (Pattern 26).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-76 Výplně otvorů  (12 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>PSV-76 Výplně otvorů</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>766621011</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV76.001</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr"/>
-      <c r="K57" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
@@ -9142,7 +9230,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -9151,14 +9239,14 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>766621011</t>
         </is>
@@ -9170,7 +9258,7 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.001</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr"/>
@@ -9191,7 +9279,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -9200,11 +9288,11 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -9219,7 +9307,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr"/>
@@ -9240,7 +9328,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -9249,11 +9337,11 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -9268,7 +9356,7 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.003</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -9289,7 +9377,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -9298,11 +9386,11 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -9317,7 +9405,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.005</t>
+          <t>260219_dum.PSV76.004</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
@@ -9338,7 +9426,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -9351,7 +9439,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -9366,7 +9454,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.006</t>
+          <t>260219_dum.PSV76.005</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -9387,7 +9475,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -9396,11 +9484,11 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -9415,7 +9503,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.007</t>
+          <t>260219_dum.PSV76.006</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr"/>
@@ -9436,7 +9524,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -9445,16 +9533,16 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -9464,7 +9552,7 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.008</t>
+          <t>260219_dum.PSV76.007</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr"/>
@@ -9485,7 +9573,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -9494,16 +9582,16 @@
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>TZ ARS — vstupní plastové dveře</t>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -9513,7 +9601,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.009</t>
+          <t>260219_dum.PSV76.008</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr"/>
@@ -9534,7 +9622,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -9543,16 +9631,16 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
+          <t>TZ ARS — vstupní plastové dveře</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -9562,7 +9650,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.010</t>
+          <t>260219_dum.PSV76.009</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr"/>
@@ -9583,7 +9671,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -9592,16 +9680,16 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -9611,7 +9699,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.013</t>
+          <t>260219_dum.PSV76.010</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr"/>
@@ -9632,7 +9720,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -9641,16 +9729,16 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -9660,7 +9748,7 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.014</t>
+          <t>260219_dum.PSV76.013</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr"/>
@@ -9671,70 +9759,70 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>764811112</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.014</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-76 Zámečnictví  (4 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>PSV-76 Zámečnictví</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>767531111</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV76.001</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr"/>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="n">
@@ -9747,7 +9835,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -9760,7 +9848,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>1 schodiště do podkroví (TZ ARS)</t>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -9775,7 +9863,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.001</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr"/>
@@ -9796,25 +9884,25 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>2 vstupy</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>767532111</t>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>767531111</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -9824,7 +9912,7 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr"/>
@@ -9845,25 +9933,25 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+          <t>2 vstupy</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -9873,7 +9961,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.003</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr"/>
@@ -9884,116 +9972,117 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnictví</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>767163115</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV76.004</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-77 Podlahy  (9 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="9" t="n"/>
-      <c r="I74" s="9" t="n"/>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="n"/>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>PSV-77 Podlahy</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="E76" s="12" t="n">
         <v>171.5</v>
       </c>
-      <c r="F75" s="11" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>776511820</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>260219_dum.PSV77.001</t>
         </is>
       </c>
-      <c r="J75" s="11" t="inlineStr"/>
-      <c r="K75" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F76" s="15">
-        <f> PSV77.002 plocha 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G76" s="15" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV77.002 → PSV77.002a</t>
-        </is>
-      </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr">
-        <is>
-          <t>Dlažba lepená vč. lepidla (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10097,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
+          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -10035,13 +10124,13 @@
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002 → PSV77.002b</t>
+          <t>260219_dum.PSV77.002 → PSV77.002a</t>
         </is>
       </c>
       <c r="J77" s="15" t="inlineStr"/>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>Spárování (771 família) — často zahrnuto v kladení.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dlažba lepená vč. lepidla (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10145,7 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
+          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
@@ -10065,10 +10154,10 @@
         </is>
       </c>
       <c r="E78" s="16" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="F78" s="15">
-        <f> PSV77.003 plocha 32.4 m²</f>
+        <f> PSV77.002 plocha 13.5 m²</f>
         <v/>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -10083,13 +10172,13 @@
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003 → PSV77.003a</t>
+          <t>260219_dum.PSV77.002 → PSV77.002b</t>
         </is>
       </c>
       <c r="J78" s="15" t="inlineStr"/>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>Dlažba lepená (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Spárování (771 família) — často zahrnuto v kladení.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10193,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
@@ -10131,62 +10220,61 @@
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003 → PSV77.003b</t>
+          <t>260219_dum.PSV77.003 → PSV77.003a</t>
         </is>
       </c>
       <c r="J79" s="15" t="inlineStr"/>
       <c r="K79" s="15" t="inlineStr">
         <is>
+          <t>Dlažba lepená (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F80" s="15">
+        <f> PSV77.003 plocha 32.4 m²</f>
+        <v/>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.003 → PSV77.003b</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
           <t>Spárování (771 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr">
-        <is>
-          <t>766411111</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV77.004</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr"/>
-      <c r="K80" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10289,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -10210,16 +10298,16 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -10229,7 +10317,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.005</t>
+          <t>260219_dum.PSV77.004</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -10250,25 +10338,25 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -10278,7 +10366,7 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.006</t>
+          <t>260219_dum.PSV77.005</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
@@ -10299,7 +10387,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -10308,16 +10396,16 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -10327,7 +10415,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.007</t>
+          <t>260219_dum.PSV77.006</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -10338,69 +10426,70 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>771274107</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.007</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-78 Povrchové úpravy  (20 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="n"/>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>PSV-78 Povrchové úpravy</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="F85" s="15">
-        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
-        <v/>
-      </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="H85" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV78.001 → PSV78.001a</t>
-        </is>
-      </c>
-      <c r="J85" s="15" t="inlineStr"/>
-      <c r="K85" s="15" t="inlineStr">
-        <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="9" t="n"/>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
@@ -10413,7 +10502,7 @@
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -10425,7 +10514,7 @@
         <v>78.2</v>
       </c>
       <c r="F86" s="15">
-        <f> PSV78.001 plocha 78.2 m²</f>
+        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
         <v/>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -10440,13 +10529,13 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001 → PSV78.001b</t>
+          <t>260219_dum.PSV78.001 → PSV78.001a</t>
         </is>
       </c>
       <c r="J86" s="15" t="inlineStr"/>
       <c r="K86" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10550,7 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
+          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
@@ -10470,10 +10559,10 @@
         </is>
       </c>
       <c r="E87" s="16" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="F87" s="15">
-        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
+        <f> PSV78.001 plocha 78.2 m²</f>
         <v/>
       </c>
       <c r="G87" s="15" t="inlineStr">
@@ -10488,13 +10577,13 @@
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002 → PSV78.002a</t>
+          <t>260219_dum.PSV78.001 → PSV78.001b</t>
         </is>
       </c>
       <c r="J87" s="15" t="inlineStr"/>
       <c r="K87" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10598,7 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -10521,7 +10610,7 @@
         <v>208.4</v>
       </c>
       <c r="F88" s="15">
-        <f> PSV78.002 plocha 208.4 m²</f>
+        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
         <v/>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -10536,13 +10625,13 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002 → PSV78.002b</t>
+          <t>260219_dum.PSV78.002 → PSV78.002a</t>
         </is>
       </c>
       <c r="J88" s="15" t="inlineStr"/>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10646,7 @@
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -10566,10 +10655,10 @@
         </is>
       </c>
       <c r="E89" s="16" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="F89" s="15">
-        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
+        <f> PSV78.002 plocha 208.4 m²</f>
         <v/>
       </c>
       <c r="G89" s="15" t="inlineStr">
@@ -10584,13 +10673,13 @@
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003 → PSV78.003a</t>
+          <t>260219_dum.PSV78.002 → PSV78.002b</t>
         </is>
       </c>
       <c r="J89" s="15" t="inlineStr"/>
       <c r="K89" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10694,7 @@
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -10617,7 +10706,7 @@
         <v>201.6</v>
       </c>
       <c r="F90" s="15">
-        <f> PSV78.003 plocha 201.6 m²</f>
+        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
         <v/>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -10632,13 +10721,13 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003 → PSV78.003b</t>
+          <t>260219_dum.PSV78.003 → PSV78.003a</t>
         </is>
       </c>
       <c r="J90" s="15" t="inlineStr"/>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10742,7 @@
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -10662,10 +10751,10 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="F91" s="15">
-        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <f> PSV78.003 plocha 201.6 m²</f>
         <v/>
       </c>
       <c r="G91" s="15" t="inlineStr">
@@ -10680,13 +10769,13 @@
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004 → PSV78.004a</t>
+          <t>260219_dum.PSV78.003 → PSV78.003b</t>
         </is>
       </c>
       <c r="J91" s="15" t="inlineStr"/>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10790,7 @@
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -10713,77 +10802,76 @@
         <v>179.1</v>
       </c>
       <c r="F92" s="15">
+        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <v/>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV78.004 → PSV78.004a</t>
+        </is>
+      </c>
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>Jádrová omítka VC (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>PSV-78 Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="F93" s="15">
         <f> PSV78.004 plocha 179.1 m²</f>
         <v/>
       </c>
-      <c r="G92" s="15" t="inlineStr">
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr">
+      <c r="H93" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>260219_dum.PSV78.004 → PSV78.004b</t>
         </is>
       </c>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr">
+      <c r="J93" s="15" t="inlineStr"/>
+      <c r="K93" s="15" t="inlineStr">
         <is>
           <t>Štuková omítka (612 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>PSV-78 Povrchové úpravy</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>612471141</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV78.005</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr"/>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10886,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -10807,11 +10895,11 @@
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
@@ -10826,7 +10914,7 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.006</t>
+          <t>260219_dum.PSV78.005</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr"/>
@@ -10847,7 +10935,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -10856,11 +10944,11 @@
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -10875,7 +10963,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.007</t>
+          <t>260219_dum.PSV78.006</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
@@ -10896,7 +10984,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -10905,16 +10993,16 @@
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -10924,7 +11012,7 @@
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.008</t>
+          <t>260219_dum.PSV78.007</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr"/>
@@ -10945,7 +11033,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -10954,11 +11042,11 @@
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -10973,7 +11061,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.009</t>
+          <t>260219_dum.PSV78.008</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr"/>
@@ -10994,7 +11082,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -11003,11 +11091,11 @@
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -11022,7 +11110,7 @@
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.010</t>
+          <t>260219_dum.PSV78.009</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr"/>
@@ -11043,7 +11131,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -11052,11 +11140,11 @@
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -11071,7 +11159,7 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.011</t>
+          <t>260219_dum.PSV78.010</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
@@ -11092,7 +11180,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -11101,16 +11189,16 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -11120,7 +11208,7 @@
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012</t>
+          <t>260219_dum.PSV78.011</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr"/>
@@ -11141,7 +11229,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -11150,11 +11238,11 @@
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -11169,7 +11257,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.1_PP</t>
+          <t>260219_dum.PSV78.012</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
@@ -11190,7 +11278,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -11199,11 +11287,11 @@
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -11218,7 +11306,7 @@
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.1_NP</t>
+          <t>260219_dum.PSV78.012.1_PP</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr"/>
@@ -11239,7 +11327,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -11248,11 +11336,11 @@
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>247.5</v>
+        <v>254.5</v>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
@@ -11267,7 +11355,7 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.2_NP</t>
+          <t>260219_dum.PSV78.012.1_NP</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr"/>
@@ -11288,7 +11376,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -11297,11 +11385,11 @@
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -11316,7 +11404,7 @@
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.012.3_NP</t>
+          <t>260219_dum.PSV78.012.2_NP</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr"/>
@@ -11327,70 +11415,70 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>PSV-78 Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>784121011</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV78.012.3_NP</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-95 Detekce požární  (2 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
-      <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t>PSV-95 Detekce požární</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F106" s="11" t="inlineStr">
-        <is>
-          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
-        </is>
-      </c>
-      <c r="G106" s="13" t="inlineStr">
-        <is>
-          <t>375211101</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV95.001</t>
-        </is>
-      </c>
-      <c r="J106" s="11" t="inlineStr"/>
-      <c r="K106" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="n">
@@ -11403,7 +11491,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -11412,16 +11500,16 @@
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>TZ PBŘ — min. 1 ks 34A</t>
-        </is>
-      </c>
-      <c r="G107" s="11" t="inlineStr">
-        <is>
-          <t>966067121</t>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>375211101</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -11431,7 +11519,7 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV95.002</t>
+          <t>260219_dum.PSV95.001</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr"/>
@@ -11442,70 +11530,70 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>PSV-95 Detekce požární</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>966067121</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV95.002</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>━━ M-21 ELI silnoproud  (7 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n"/>
-      <c r="C108" s="9" t="n"/>
-      <c r="D108" s="9" t="n"/>
-      <c r="E108" s="9" t="n"/>
-      <c r="F108" s="9" t="n"/>
-      <c r="G108" s="9" t="n"/>
-      <c r="H108" s="9" t="n"/>
-      <c r="I108" s="9" t="n"/>
-      <c r="J108" s="9" t="n"/>
-      <c r="K108" s="9" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="n">
-        <v>96</v>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t>M-21 ELI silnoproud</t>
-        </is>
-      </c>
-      <c r="C109" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="11" t="inlineStr">
-        <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr">
-        <is>
-          <t>210010011</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.M21.001</t>
-        </is>
-      </c>
-      <c r="J109" s="11" t="inlineStr"/>
-      <c r="K109" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="9" t="n"/>
+      <c r="H109" s="9" t="n"/>
+      <c r="I109" s="9" t="n"/>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="n">
@@ -11518,25 +11606,25 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -11546,7 +11634,7 @@
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.002</t>
+          <t>260219_dum.M21.001</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr"/>
@@ -11567,25 +11655,25 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -11595,7 +11683,7 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.003</t>
+          <t>260219_dum.M21.002</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -11616,25 +11704,25 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -11644,7 +11732,7 @@
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.004</t>
+          <t>260219_dum.M21.003</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr"/>
@@ -11665,7 +11753,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -11674,16 +11762,16 @@
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -11693,7 +11781,7 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.005</t>
+          <t>260219_dum.M21.004</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -11714,25 +11802,25 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -11742,7 +11830,7 @@
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.006</t>
+          <t>260219_dum.M21.005</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr"/>
@@ -11763,7 +11851,7 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -11776,12 +11864,12 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -11791,11 +11879,60 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.007</t>
+          <t>260219_dum.M21.006</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
       <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>996019011</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.M21.007</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr"/>
+      <c r="K116" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -11806,16 +11943,16 @@
   <mergeCells count="12">
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A74:K74"/>
-    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A57:K57"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A84:K84"/>
-    <mergeCell ref="A108:K108"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A106:K106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14670,7 +14807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14744,11 +14881,11 @@
         <v>30</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>HSV1.004a, HSV1.004b, HSV1.004c</t>
+          <t>HSV1.004a, HSV1.004b, HSV1.004c, HSV1.004d</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14902,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm +</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče vý</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
@@ -14777,11 +14914,11 @@
         <v>30</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>HSV1.005a, HSV1.005b, HSV1.005c, HSV1.005d</t>
+          <t>HSV1.005a, HSV1.005b, HSV1.005c, HSV1.005d, HSV1.005e</t>
         </is>
       </c>
     </row>
@@ -14920,17 +15057,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -14939,21 +15076,21 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>PSV77.002a, PSV77.002b</t>
+          <t>PSV76.002a, PSV76.002b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003</t>
+          <t>260219_dum.PSV77.002</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -14963,7 +15100,7 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -14972,31 +15109,31 @@
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>PSV77.003a, PSV77.003b</t>
+          <t>PSV77.002a, PSV77.002b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001</t>
+          <t>260219_dum.PSV77.003</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -15005,21 +15142,21 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>78.2</v>
+        <v>32.4</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>PSV78.001a, PSV78.001b</t>
+          <t>PSV77.003a, PSV77.003b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002</t>
+          <t>260219_dum.PSV78.001</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -15029,7 +15166,7 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -15038,21 +15175,21 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>PSV78.002a, PSV78.002b</t>
+          <t>PSV78.001a, PSV78.001b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003</t>
+          <t>260219_dum.PSV78.002</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -15062,7 +15199,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -15071,21 +15208,21 @@
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>PSV78.003a, PSV78.003b</t>
+          <t>PSV78.002a, PSV78.002b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004</t>
+          <t>260219_dum.PSV78.003</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -15095,7 +15232,7 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -15104,54 +15241,54 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>PSV78.004a, PSV78.004b</t>
+          <t>PSV78.003a, PSV78.003b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.004</t>
+          <t>260219_dum.PSV78.004</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0</v>
+        <v>179.1</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
+          <t>PSV78.004a, PSV78.004b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.005</t>
+          <t>260219_dum.PSV72.004</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -15161,7 +15298,7 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -15177,14 +15314,14 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
+          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.006</t>
+          <t>260219_dum.PSV72.005</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -15194,7 +15331,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -15210,14 +15347,14 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
+          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.008</t>
+          <t>260219_dum.PSV72.006</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -15227,54 +15364,87 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>set</t>
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>260219_dum.PSV72.008</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>260219_dum.HSV1.015</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>HSV-1 Zemní práce</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E19" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F19" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
         </is>
@@ -15291,7 +15461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15411,27 +15581,102 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Sklad — svislá hydroizolace + drenáž stěn pod terénem (skladby S03a/S04) — DSP nespecifikuje</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř u projektanta zda skladby S03a/S04 zahrnují svislou hydroizolaci + drenáž stěn skladu pod terénem. Pokud ano → doplníme (penetrace + 2× asfalt. pás + nopová fólie + drenáž DN100 za S04) dle ploch pod terénem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Sněhové zábrany / protisněhové prvky — falcovaná krytina, VII. sněhová oblast</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř u projektanta / dodavatele krytiny zda jsou pro falc. krytinu v VII. sněhové oblasti požadovány sněhové zábrany. Pokud ano → doplníme bm dle délky okapů (zejména nad vstupy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Lemování komína a střešních prostupů — klempířský detail</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Karle, ověř zda komín nebo VZT/ZTI prostupy procházejí novou střechou → pokud ano, doplníme klempířské lemování (ks dle počtu prostupů).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1757,7 +1757,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-1 Zemní práce  (18 atomic operací) ━━</t>
+          <t>━━ HSV-1 Zemní práce  (19 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>30</v>
+        <v>16.54</v>
       </c>
       <c r="F6" s="15">
-        <f> HSV1.004 plocha dvorku 30 m²</f>
+        <f> HSV1.004 plocha dvorku 16.54 m² (situace 12.46 + 4.08, dlažba = brick-hatch)</f>
         <v/>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>30</v>
+        <v>16.54</v>
       </c>
       <c r="F7" s="15">
-        <f> HSV1.004 plocha dvorku 30 m²</f>
+        <f> HSV1.004 plocha dvorku 16.54 m² (situace 12.46 + 4.08)</f>
         <v/>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>30</v>
+        <v>16.54</v>
       </c>
       <c r="F8" s="15">
-        <f> HSV1.004 plocha 30 m²</f>
+        <f> HSV1.004 plocha 16.54 m²</f>
         <v/>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>30</v>
+        <v>16.54</v>
       </c>
       <c r="F9" s="15">
-        <f> HSV1.004 plocha 30 m²</f>
+        <f> HSV1.004 plocha 16.54 m²</f>
         <v/>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="E10" s="19" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F10" s="18">
-        <f> HSV1.005 plocha terasy 30 m²</f>
+        <f> HSV1.005 plocha terasy 9.23 m² (situace měření, terasa = line-hatch)</f>
         <v/>
       </c>
       <c r="G10" s="18" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F11" s="15">
-        <f> HSV1.005 plocha terasy 30 m²</f>
+        <f> HSV1.005 plocha terasy 9.23 m² (situace měření)</f>
         <v/>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F12" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
+        <f> HSV1.005 plocha 9.23 m²</f>
         <v/>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F13" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
+        <f> HSV1.005 plocha 9.23 m²</f>
         <v/>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F14" s="15">
-        <f> HSV1.005 plocha 30 m²</f>
+        <f> HSV1.005 plocha 9.23 m²</f>
         <v/>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -2669,70 +2669,70 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.016</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>Venkovní schody na terénu</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-2 Základové a ŽB  (13 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Bílá vana ČBS 02 — pata úhlové opěrné stěny 250×1200 mm × L=10 m, C25/30 XC3 XF1 XA1 CL0.4 Dmax22 S3</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>0.25 × 1.20 × 10 = 3.0</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>274321321</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.001</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Bílá vana ČBS 02 — stěna úhlová tl. 250 mm × výška 2050 mm × L=10 m, beton C25/30 XC3 XF1 XA1 (trhliny max 0.20 mm)</t>
+          <t>Bílá vana ČBS 02 — pata úhlové opěrné stěny 250×1200 mm × L=10 m, C25/30 XC3 XF1 XA1 CL0.4 Dmax22 S3</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -2754,14 +2754,14 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>5.12</v>
+        <v>3</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>0.25 × 2.05 × 10 = 5.13</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
+          <t>0.25 × 1.20 × 10 = 3.0</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>274321321</t>
         </is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.002</t>
+          <t>260219_dum.HSV2.001</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
@@ -2784,190 +2784,190 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n">
+      <c r="A24" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Bílá vana ČBS 02 — stěna úhlová tl. 250 mm × výška 2050 mm × L=10 m, beton C25/30 XC3 XF1 XA1 (trhliny max 0.20 mm)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>0.25 × 2.05 × 10 = 5.13</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>274321321</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.002</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>Systémové oboustranné bednění bílé vany — DOKA Framax / PERI MAXIMO, vč. těsnění pracovních spár bobtnavý pásek bentonit (TZ §5.5)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E25" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>2×2.05×10 (svislé) + 2×1.20×10 (pata) = 41 + 24 = 65</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr"/>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.003</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr"/>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="J25" s="18" t="inlineStr"/>
+      <c r="K25" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Výztuž bílé vany B500B 120 kg/m³ (empirická sazba Methvin pro úhlové opěrné stěny W0)</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>975</v>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>(3.0+5.13) × 120 = 976</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.004</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Separační PE fólie pod základovou patou bílé vany (povinná dle ČBS 02)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E27" s="19" t="n">
         <v>13.2</v>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>1.20 × 10 × 1.10 přesah = 13.2</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr"/>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I26" s="18" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.005</t>
         </is>
       </c>
-      <c r="J26" s="18" t="inlineStr"/>
-      <c r="K26" s="18" t="inlineStr">
+      <c r="J27" s="18" t="inlineStr"/>
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Mokré ošetřování betonu bílé vany min. 7 dní dle ČSN EN 13670 + ČBS 02 (kontrola trhlin max 0.20 mm)</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>viditelná plocha BV pro ošetřování ~53</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>279351102</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.006</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -2982,25 +2982,25 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>ŽB pozední věnec 300×250 mm po obvodu nadezdívky 3.NP, beton C25/30 XC1 + výztuž 100 kg/m³</t>
+          <t>Mokré ošetřování betonu bílé vany min. 7 dní dle ČSN EN 13670 + ČBS 02 (kontrola trhlin max 0.20 mm)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2.9</v>
+        <v>53</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>274321311</t>
+          <t>viditelná plocha BV pro ošetřování ~53</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>279351102</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.007</t>
+          <t>260219_dum.HSV2.006</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
@@ -3021,96 +3021,96 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n">
+      <c r="A29" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>ŽB pozední věnec 300×250 mm po obvodu nadezdívky 3.NP, beton C25/30 XC1 + výztuž 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>0.30 × 0.25 × obvod 38.7 m (DXF km_R_návrh_tlustá 2 closed polygon area 91.28 m²) = 2.9 m³</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>274321311</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.007</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>Bednění pozedního věnce systémové oboustranné</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E30" s="19" t="n">
         <v>19.4</v>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>2 (oboustranné) × 0.25 m výška × obvod 38.7 m (DXF) = 19.4 m²</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr"/>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I29" s="18" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.008</t>
         </is>
       </c>
-      <c r="J29" s="18" t="inlineStr"/>
-      <c r="K29" s="18" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr"/>
+      <c r="K30" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Výztuž B500B věnce 100 kg/m³ (Methvin sazba pro pozední věnce)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>310</v>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>3.1 × 100 = 310</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>273361821</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV2.009</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr"/>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -3125,25 +3125,25 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Nabetonávka stropu 2.NP/3.NP — beton C25/30 XC1 tl. 60 mm nad vlnu trapézového plechu 40S/160</t>
+          <t>Výztuž B500B věnce 100 kg/m³ (Methvin sazba pro pozední věnce)</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>6.26</v>
+        <v>310</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>104.4 m² × 0.06 m = 6.26</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>274321111</t>
+          <t>3.1 × 100 = 310</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>273361821</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -3153,14 +3153,10 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.010</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV2.009</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3178,25 +3174,25 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Výztuž nabetonávky kari síť 5/100/100 (cca 4.4 kg/m²)</t>
+          <t>Nabetonávka stropu 2.NP/3.NP — beton C25/30 XC1 tl. 60 mm nad vlnu trapézového plechu 40S/160</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>459</v>
+        <v>6.26</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>104.4 m² × 4.4 kg/m² = 459</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>273362441</t>
+          <t>104.4 m² × 0.06 m = 6.26</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>274321111</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -3206,7 +3202,7 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.011</t>
+          <t>260219_dum.HSV2.010</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -3231,25 +3227,25 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>ŽB deska podlahy 1.NP na terénu tl. 150 mm, C25/30 XC2 + vyztužení kari 6/150/150 + okrajové pruty</t>
+          <t>Výztuž nabetonávky kari síť 5/100/100 (cca 4.4 kg/m²)</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>10.96</v>
+        <v>459</v>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
-        </is>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>273321311</t>
+          <t>104.4 m² × 4.4 kg/m² = 459</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>273362441</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -3259,12 +3255,12 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV2.012</t>
+          <t>260219_dum.HSV2.011</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
@@ -3284,117 +3280,117 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>ŽB deska podlahy 1.NP na terénu tl. 150 mm, C25/30 XC2 + vyztužení kari 6/150/150 + okrajové pruty</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>104.4 × 0.7 (rozsah 1.NP) × 0.15 = ~11.0</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>273321311</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV2.012</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
           <t>Výztuž ŽB desky 1.NP — kari 6/150/150 + B500B okrajové pruty (~75 kg/m³ Methvin)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>825</v>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>11.0 × 75 = 825</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>273361821</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV2.013</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-3 Svislé konstrukce  (7 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Lokální dozdívky a přizdívky z cihel plných pálených P10 na MVC M10 (uvedeno v TZ statika §4)</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>311232511</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV3.001</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>S01, S02</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -3407,40 +3403,40 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Nadezdívka 3.NP a čela vikýřů — Porotherm 30 Profi P10 na maltu pro tenké spáry, výška 2.65 m</t>
+          <t>Lokální dozdívky a přizdívky z cihel plných pálených P10 na MVC M10 (uvedeno v TZ statika §4)</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>71.8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
-        </is>
-      </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>311321411</t>
+          <t>odhad — drobné dozdívky kolem nových otvorů 1.NP/2.NP</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>311232511</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.002</t>
+          <t>260219_dum.HSV3.001</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S01, S02</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -3460,40 +3456,40 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Ocelové překlady IPN160 ve dvojici nad otvory pro nové dveře/okna v 1.NP a 2.NP (8 otvorů odhad)</t>
+          <t>Nadezdívka 3.NP a čela vikýřů — Porotherm 30 Profi P10 na maltu pro tenké spáry, výška 2.65 m</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>8</v>
+        <v>71.8</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
+          <t>obvod 38.7 m (DXF km_R_návrh_tlustá 2) × výška 2.65 m × 0.7 (sníženo o štíty zachované — řadovka) = 71.8 m²</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>317143112</t>
+          <t>311321411</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.003</t>
+          <t>260219_dum.HSV3.002</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
@@ -3513,25 +3509,25 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maltové uložení překladů IPN160 — MC25 tl. 50 mm + kari 5/100/100 (po obou stranách otvoru)</t>
+          <t>Ocelové překlady IPN160 ve dvojici nad otvory pro nové dveře/okna v 1.NP a 2.NP (8 otvorů odhad)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>8 otvorů × 2 strany = 16 uložení</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>317242421</t>
+          <t>odhad 8 nových otvorů × 2 IPN160 (dvojice)</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>317143112</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -3541,7 +3537,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.004</t>
+          <t>260219_dum.HSV3.003</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
@@ -3566,35 +3562,35 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Zesílení ostění úhelníky L100/10 dvojicí u otvoru u komínového tělesa (statická limitace)</t>
+          <t>Maltové uložení překladů IPN160 — MC25 tl. 50 mm + kari 5/100/100 (po obou stranách otvoru)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
+          <t>8 otvorů × 2 strany = 16 uložení</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>767131120</t>
+          <t>317242421</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.005</t>
+          <t>260219_dum.HSV3.004</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -3619,37 +3615,42 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Dočasné podstojkování stávajících přiléhajících stropů při osazování IPN překladů (8 otvorů)</t>
+          <t>Zesílení ostění úhelníky L100/10 dvojicí u otvoru u komínového tělesa (statická limitace)</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="11">
-        <f> počet překladů (po jednom podstojkování per otvor)</f>
-        <v/>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>962081120</t>
+        <v>4</v>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>TZ statika §4 — 2× L100/10 (dvojice) na 2 strany otvoru = 4 ks</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>767131120</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV3.006</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV3.005</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="K41" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3667,113 +3668,112 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
+          <t>Dočasné podstojkování stávajících přiléhajících stropů při osazování IPN překladů (8 otvorů)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="11">
+        <f> počet překladů (po jednom podstojkování per otvor)</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>962081120</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV3.006</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
           <t>Nové příčky z pórobetonových tvárnic 150 mm na lepidlo + dilatovány od stropu</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>87.7</v>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>podlahova_plocha × 0.4 (typický rozsah příček 30-50%)</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>342241211</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV3.007</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-4 Vodorovné  (14 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>Ocelová stropnice IPE180 1.NP v pozici nové příčky 2.NP — dodávka + montáž (1 ks × ~5 m)</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr"/>
-      <c r="K44" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop 2.NP/3.NP — stropnice IPE180 á 1000 mm × rozpon ~8 m × ~8 ks</t>
+          <t>Ocelová stropnice IPE180 1.NP v pozici nové příčky 2.NP — dodávka + montáž (1 ks × ~5 m)</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -3795,11 +3795,11 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>1203</v>
+        <v>94</v>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
+          <t>1 ks × 5 m × 18.8 kg/m (IPE180 hmotnost) = 94</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -3814,14 +3814,10 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.002</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV4.001</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -3839,7 +3835,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop — výztuha 2×HEA180 trakt do ulice (Fibichova), dl. ~10 m</t>
+          <t>Ocelobetonový strop 2.NP/3.NP — stropnice IPE180 á 1000 mm × rozpon ~8 m × ~8 ks</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -3848,11 +3844,11 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>710</v>
+        <v>1203</v>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+          <t>8 ks × 8 m × 18.8 kg/m = 1203</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -3867,7 +3863,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.003</t>
+          <t>260219_dum.HSV4.002</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -3892,7 +3888,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Ocelobetonový strop — výztuha HEA200 dvorní trakt, dl. ~10 m</t>
+          <t>Ocelobetonový strop — výztuha 2×HEA180 trakt do ulice (Fibichova), dl. ~10 m</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -3901,14 +3897,14 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>423</v>
+        <v>710</v>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
-        </is>
-      </c>
-      <c r="G47" s="11" t="inlineStr">
+          <t>2 ks × 10 m × 35.5 kg/m (HEA180) = 710</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>411321414</t>
         </is>
@@ -3920,7 +3916,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.004</t>
+          <t>260219_dum.HSV4.003</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
@@ -3945,22 +3941,23 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trapézový plech 40S/160 tl. 0.75 mm — dodávka + montáž na stropnice IPE180</t>
+          <t>Ocelobetonový strop — výztuha HEA200 dvorní trakt, dl. ~10 m</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F48" s="11">
-        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
-        <v/>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
+        <v>423</v>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>1 ks × 10 m × 42.3 kg/m (HEA200) = 423</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>411321414</t>
         </is>
@@ -3972,7 +3969,7 @@
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.005</t>
+          <t>260219_dum.HSV4.004</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -3997,7 +3994,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Protipožární SDK podhled pod trapézovým plechem (EI 30 dle PBŘ — ocelobeton + SDK)</t>
+          <t>Trapézový plech 40S/160 tl. 0.75 mm — dodávka + montáž na stropnice IPE180</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -4009,12 +4006,12 @@
         <v>104.4</v>
       </c>
       <c r="F49" s="11">
-        <f> plocha trapézu 104.4 m²</f>
+        <f> zastavěna plocha 104.4 m² (celý strop 2.NP/3.NP)</f>
         <v/>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>342213131</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -4024,7 +4021,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.006</t>
+          <t>260219_dum.HSV4.005</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
@@ -4049,40 +4046,39 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Vyvezení původního zásypu z cihelné klenby 1.PP/1.NP — manuálně + odvoz</t>
+          <t>Protipožární SDK podhled pod trapézovým plechem (EI 30 dle PBŘ — ocelobeton + SDK)</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>974031150</t>
+        <v>104.4</v>
+      </c>
+      <c r="F50" s="11">
+        <f> plocha trapézu 104.4 m²</f>
+        <v/>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>342213131</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.007</t>
+          <t>260219_dum.HSV4.006</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -4102,7 +4098,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Nový zásyp klenby 1.PP/1.NP — perlitbeton (lehký zásyp) tl. 100 mm</t>
+          <t>Vyvezení původního zásypu z cihelné klenby 1.PP/1.NP — manuálně + odvoz</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -4111,26 +4107,26 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
+          <t>klenba ~50 m² × tl. zásypu 0.15 m = 7.5 (round 8)</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>271223111</t>
+          <t>974031150</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.008</t>
+          <t>260219_dum.HSV4.007</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
@@ -4155,25 +4151,25 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Plastická perlitbetonová roznášecí vrstva tl. 50 mm nad zásypem klenby</t>
+          <t>Nový zásyp klenby 1.PP/1.NP — perlitbeton (lehký zásyp) tl. 100 mm</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
+          <t>klenba 50 m² × 0.10 m perlitbeton = 5.0</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>271223111</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -4183,7 +4179,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.009</t>
+          <t>260219_dum.HSV4.008</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -4208,7 +4204,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Strop trámový 1.NP/2.NP — sejmutí podlah, demontáž záklopu a zásypu shora (zachovat prkenný záklop na trámech)</t>
+          <t>Plastická perlitbetonová roznášecí vrstva tl. 50 mm nad zásypem klenby</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -4217,16 +4213,16 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+          <t>klenba 1.PP/1.NP plocha ~50 m²</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>974041141</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -4236,12 +4232,12 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.010</t>
+          <t>260219_dum.HSV4.009</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
@@ -4261,7 +4257,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Tepelná izolace minerální vata mezi trámy stropu 1.NP/2.NP, tl. 180 mm (= trám 60/180)</t>
+          <t>Strop trámový 1.NP/2.NP — sejmutí podlah, demontáž záklopu a zásypu shora (zachovat prkenný záklop na trámech)</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -4272,13 +4268,14 @@
       <c r="E54" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F54" s="11">
-        <f> plocha stropu</f>
-        <v/>
-      </c>
-      <c r="G54" s="13" t="inlineStr">
-        <is>
-          <t>713121121</t>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>podlahova_plocha_1NP+2NP ~100 m²</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>974041141</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -4288,7 +4285,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.011</t>
+          <t>260219_dum.HSV4.010</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -4313,7 +4310,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Protipožární SDK podhled zespodu trámového stropu (EI 30 dle PBŘ)</t>
+          <t>Tepelná izolace minerální vata mezi trámy stropu 1.NP/2.NP, tl. 180 mm (= trám 60/180)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -4328,9 +4325,9 @@
         <f> plocha stropu</f>
         <v/>
       </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>342213131</t>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>713121121</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -4340,7 +4337,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.012</t>
+          <t>260219_dum.HSV4.011</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
@@ -4365,25 +4362,24 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Suchá podlahová skladba 1.NP/2.NP — zásyp Liapor pro vyrovnání tl. 50 mm</t>
+          <t>Protipožární SDK podhled zespodu trámového stropu (EI 30 dle PBŘ)</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>100 m² × 0.05 m = 5</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="F56" s="11">
+        <f> plocha stropu</f>
+        <v/>
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>631311114</t>
+          <t>342213131</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -4393,7 +4389,7 @@
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.013</t>
+          <t>260219_dum.HSV4.012</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
@@ -4418,112 +4414,116 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
+          <t>Suchá podlahová skladba 1.NP/2.NP — zásyp Liapor pro vyrovnání tl. 50 mm</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>100 m² × 0.05 m = 5</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>631311114</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.013</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
           <t>Suchá podlahová skladba — sádrovláknité dílce Fermacell tl. 25 mm (dva 12.5 mm vrstvy)</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="E58" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F58" s="11">
         <f> plocha stropu</f>
         <v/>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>771421111</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV4.014</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="K57" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-5 Krov + střecha  (16 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
-      <c r="H58" s="9" t="n"/>
-      <c r="I58" s="9" t="n"/>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
-        <is>
-          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>762331911</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.001</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="inlineStr"/>
-      <c r="K59" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
+          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -4545,16 +4545,16 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
+          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>762331912</t>
+          <t>762331911</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.002</t>
+          <t>260219_dum.HSV5.001</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
+          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -4594,16 +4594,16 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>19.4</v>
+        <v>110</v>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
+          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>762331923</t>
+          <t>762331912</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.003</t>
+          <t>260219_dum.HSV5.002</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
+          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -4643,16 +4643,16 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>24 krokví × 0.8 m námětek = 19.2</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>762331911</t>
+          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.004</t>
+          <t>260219_dum.HSV5.003</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr"/>
@@ -4683,25 +4683,25 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
+          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>608</v>
+        <v>19.2</v>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>411321414</t>
+          <t>24 krokví × 0.8 m námětek = 19.2</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>762331911</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.005</t>
+          <t>260219_dum.HSV5.004</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
+          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -4741,14 +4741,14 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>176</v>
+        <v>608</v>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
+          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>411321414</t>
         </is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.006</t>
+          <t>260219_dum.HSV5.005</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr"/>
@@ -4781,24 +4781,25 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
+          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F65" s="11">
-        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
-        <v/>
+        <v>176</v>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
+        </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>762341711</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -4808,14 +4809,10 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.007</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.006</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr"/>
       <c r="K65" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4833,7 +4830,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
+          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -4842,16 +4839,15 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>155.034</v>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>141 × 1.1 přesah = 155</t>
-        </is>
+        <v>140.94</v>
+      </c>
+      <c r="F66" s="11">
+        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
+        <v/>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -4861,7 +4857,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.008</t>
+          <t>260219_dum.HSV5.007</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -4886,7 +4882,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
+          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -4895,25 +4891,26 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F67" s="11">
-        <f> 141 m² (plocha krytiny krov)</f>
-        <v/>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>713131811</t>
+        <v>155.034</v>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>712311101</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.009</t>
+          <t>260219_dum.HSV5.008</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
@@ -4938,7 +4935,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
+          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -4947,26 +4944,25 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>155.034</v>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>141 × 1.1 přesah = 155</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>712311111</t>
+        <v>140.94</v>
+      </c>
+      <c r="F68" s="11">
+        <f> 141 m² (plocha krytiny krov)</f>
+        <v/>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>713131811</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.010</t>
+          <t>260219_dum.HSV5.009</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -4991,7 +4987,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
+          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -5000,15 +4996,16 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F69" s="11">
-        <f> 141 m²</f>
-        <v/>
+        <v>155.034</v>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>762331923</t>
+          <t>712311111</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -5018,7 +5015,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.011</t>
+          <t>260219_dum.HSV5.010</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
@@ -5043,7 +5040,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
+          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -5058,9 +5055,9 @@
         <f> 141 m²</f>
         <v/>
       </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>762341711</t>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
@@ -5070,7 +5067,7 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.012</t>
+          <t>260219_dum.HSV5.011</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
@@ -5095,7 +5092,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
+          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -5107,12 +5104,12 @@
         <v>140.94</v>
       </c>
       <c r="F71" s="11">
-        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <f> 141 m²</f>
         <v/>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>765791121</t>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -5122,7 +5119,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.013</t>
+          <t>260219_dum.HSV5.012</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
@@ -5147,7 +5144,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
+          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -5156,16 +5153,15 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F72" s="11" t="inlineStr">
-        <is>
-          <t>odhad — spací patro ~5 × 5 m</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>762341711</t>
+        <v>140.94</v>
+      </c>
+      <c r="F72" s="11">
+        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <v/>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>765791121</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -5175,12 +5171,12 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.014</t>
+          <t>260219_dum.HSV5.013</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
@@ -5200,7 +5196,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -5209,16 +5205,16 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+          <t>odhad — spací patro ~5 × 5 m</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>311321411</t>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -5228,10 +5224,14 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.015</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.014</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5249,204 +5249,204 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
+          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>311321411</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.015</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
           <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="E75" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>4 vikýře × 2 strany × ~3 m² = 24</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
         <is>
           <t>765791121</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.016</t>
         </is>
       </c>
-      <c r="J74" s="11" t="inlineStr">
+      <c r="J75" s="11" t="inlineStr">
         <is>
           <t>S12b</t>
         </is>
       </c>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="n"/>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="E77" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F76" s="11" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
         </is>
       </c>
-      <c r="G76" s="13" t="inlineStr">
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>962041141</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.001</t>
         </is>
       </c>
-      <c r="J76" s="11" t="inlineStr"/>
-      <c r="K76" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="B77" s="18" t="inlineStr">
+      <c r="J77" s="11" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E77" s="19" t="n">
+      <c r="E78" s="19" t="n">
         <v>140.9</v>
       </c>
-      <c r="F77" s="18">
+      <c r="F78" s="18">
         <f> plocha krytiny ~141</f>
         <v/>
       </c>
-      <c r="G77" s="18" t="inlineStr"/>
-      <c r="H77" s="17" t="inlineStr">
+      <c r="G78" s="18" t="inlineStr"/>
+      <c r="H78" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I77" s="18" t="inlineStr">
+      <c r="I78" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.002</t>
         </is>
       </c>
-      <c r="J77" s="18" t="inlineStr"/>
-      <c r="K77" s="18" t="inlineStr">
+      <c r="J78" s="18" t="inlineStr"/>
+      <c r="K78" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.003</t>
-        </is>
-      </c>
-      <c r="J78" s="11" t="inlineStr"/>
-      <c r="K78" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -5461,24 +5461,25 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F79" s="11">
-        <f> zastavěna 104.4 m²</f>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+        </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -5488,7 +5489,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.004</t>
+          <t>260219_dum.HSV6.003</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr"/>
@@ -5509,7 +5510,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -5518,16 +5519,15 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="F80" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.005</t>
+          <t>260219_dum.HSV6.004</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr"/>
@@ -5558,20 +5558,20 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.006</t>
+          <t>260219_dum.HSV6.005</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
-        </is>
-      </c>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>781473810</t>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.007</t>
+          <t>260219_dum.HSV6.006</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -5665,16 +5665,16 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>153.51</v>
+        <v>60</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
-        </is>
-      </c>
-      <c r="G83" s="11" t="inlineStr">
-        <is>
-          <t>974031132</t>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>781473810</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.008</t>
+          <t>260219_dum.HSV6.007</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>5</v>
+        <v>153.51</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.009</t>
+          <t>260219_dum.HSV6.008</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
@@ -5754,25 +5754,25 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.010</t>
+          <t>260219_dum.HSV6.009</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -5812,16 +5812,16 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.011</t>
+          <t>260219_dum.HSV6.010</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
@@ -5852,25 +5852,25 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>56.5</v>
+        <v>12</v>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.012</t>
+          <t>260219_dum.HSV6.011</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
@@ -5901,35 +5901,35 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>16</v>
+        <v>56.5</v>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
-        </is>
-      </c>
-      <c r="G88" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>997013501</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.013</t>
+          <t>260219_dum.HSV6.012</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -5959,11 +5959,11 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.014</t>
+          <t>260219_dum.HSV6.013</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -6008,26 +6008,26 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="inlineStr">
-        <is>
-          <t>968072456</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.014</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
@@ -6048,25 +6048,25 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0.6</v>
+        <v>15</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
-        </is>
-      </c>
-      <c r="G91" s="13" t="inlineStr">
-        <is>
-          <t>962024141</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.016</t>
+          <t>260219_dum.HSV6.015</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr"/>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -6106,16 +6106,16 @@
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.017</t>
+          <t>260219_dum.HSV6.016</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr"/>
@@ -6136,124 +6136,121 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.017</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr"/>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B93" s="9" t="n"/>
-      <c r="C93" s="9" t="n"/>
-      <c r="D93" s="9" t="n"/>
-      <c r="E93" s="9" t="n"/>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="9" t="n"/>
-      <c r="H93" s="9" t="n"/>
-      <c r="I93" s="9" t="n"/>
-      <c r="J93" s="9" t="n"/>
-      <c r="K93" s="9" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="n">
-        <v>86</v>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E94" s="12" t="n">
+      <c r="E95" s="12" t="n">
         <v>276.7</v>
       </c>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
-      <c r="G94" s="11" t="inlineStr">
+      <c r="G95" s="11" t="inlineStr">
         <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="J94" s="11" t="inlineStr">
+      <c r="J95" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="14" t="n">
-        <v>87</v>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F95" s="15">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G95" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H95" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002a</t>
-        </is>
-      </c>
-      <c r="J95" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K95" s="15" t="inlineStr">
-        <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6265,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -6280,12 +6277,12 @@
         <v>276.7</v>
       </c>
       <c r="F96" s="15">
-        <f> HSV7.002 plocha 276.7 m²</f>
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
         <v/>
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
@@ -6295,7 +6292,7 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.002 → HSV7.002b</t>
+          <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
       <c r="J96" s="15" t="inlineStr">
@@ -6305,7 +6302,7 @@
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6317,7 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
@@ -6329,15 +6326,15 @@
         </is>
       </c>
       <c r="E97" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F97" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha 276.7 m²</f>
         <v/>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr">
@@ -6347,17 +6344,17 @@
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002b</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6369,7 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
@@ -6389,7 +6386,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr">
@@ -6399,7 +6396,7 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
       <c r="J98" s="15" t="inlineStr">
@@ -6409,7 +6406,7 @@
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6424,24 +6421,24 @@
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E99" s="16" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="F99" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="G99" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>781</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr">
@@ -6451,17 +6448,17 @@
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
         </is>
       </c>
       <c r="J99" s="15" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6473,7 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -6488,85 +6485,84 @@
         <v>82.2</v>
       </c>
       <c r="F100" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+        </is>
+      </c>
+      <c r="J100" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="inlineStr">
+        <is>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F101" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G100" s="15" t="inlineStr">
+      <c r="G101" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr">
+      <c r="H101" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I100" s="15" t="inlineStr">
+      <c r="I101" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J100" s="15" t="inlineStr">
+      <c r="J101" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K100" s="15" t="inlineStr">
+      <c r="K101" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="n">
-        <v>93</v>
-      </c>
-      <c r="B101" s="11" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C101" s="11" t="inlineStr">
-        <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="11" t="inlineStr">
-        <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
-        </is>
-      </c>
-      <c r="G101" s="11" t="inlineStr">
-        <is>
-          <t>622221221</t>
-        </is>
-      </c>
-      <c r="H101" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.005</t>
-        </is>
-      </c>
-      <c r="J101" s="11" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K101" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -6581,43 +6577,96 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>622221221</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.005</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E102" s="12" t="n">
+      <c r="E103" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F102" s="11" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G102" s="13" t="inlineStr">
+      <c r="G103" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="J103" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K102" s="11" t="inlineStr">
+      <c r="K103" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6626,13 +6675,13 @@
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <mergeCells count="7">
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A94:K94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9126,10 +9175,10 @@
         </is>
       </c>
       <c r="E55" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F55" s="15">
-        <f> PSV76.002 plocha terasy 30 m²</f>
+        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
         <v/>
       </c>
       <c r="G55" s="15" t="inlineStr">
@@ -9174,10 +9223,10 @@
         </is>
       </c>
       <c r="E56" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F56" s="15">
-        <f> PSV76.002 plocha terasy 30 m²</f>
+        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
         <v/>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -14878,7 +14927,7 @@
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>30</v>
+        <v>16.54</v>
       </c>
       <c r="F2" s="14" t="n">
         <v>4</v>
@@ -14911,7 +14960,7 @@
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F3" s="14" t="n">
         <v>5</v>
@@ -15076,7 +15125,7 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>30</v>
+        <v>9.23</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>2</v>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -1032,7 +1032,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa 636311 (na terče, NE 762) · HSV2.003/008 bednění 274.</t>
+          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>• Terasa A2 korekce: HSV1.005a = 636311 família (dlaždice NA TERČE, NE 762 carpentry)</t>
+          <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -1280,7 +1280,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -1290,7 +1290,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -1300,7 +1300,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -1310,17 +1310,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -1330,7 +1330,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -1340,7 +1340,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1350,7 +1350,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -1360,17 +1360,17 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
@@ -1380,7 +1380,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -1390,7 +1390,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -1400,7 +1400,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -1410,7 +1410,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -1420,7 +1420,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -1430,7 +1430,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1440,7 +1440,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1450,7 +1450,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -1460,7 +1460,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -1470,17 +1470,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -1490,7 +1490,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -1500,7 +1500,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -1510,7 +1510,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -1520,7 +1520,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -1530,7 +1530,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,64 +1590,74 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
@@ -1656,7 +1666,6 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A112:C112"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A117:C117"/>
@@ -1664,6 +1673,7 @@
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A4:C4"/>
@@ -1681,7 +1691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4511,7 +4521,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-5 Krov + střecha  (16 atomic operací) ━━</t>
+          <t>━━ HSV-5 Krov + střecha  (20 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B59" s="9" t="n"/>
@@ -4526,401 +4536,386 @@
       <c r="K59" s="9" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="n">
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Montáž krokví 100/180 mm — vázaná konstrukce krovu pomocí ocelových spojek, hraněné řezivo (průřez 180 cm², přes 120 do 224)</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="n">
         <v>156</v>
       </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>(2 sklony × 12 krokví × 6.5 m délka) = 156</t>
-        </is>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>762331911</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.001</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr"/>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="F60" s="15">
+        <f> HSV5.001 délka krokví 156 bm</f>
+        <v/>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>762332122</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.001 → HSV5.001a</t>
+        </is>
+      </c>
+      <c r="J60" s="15" t="inlineStr"/>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t>Montáž 762332122 (266 Kč/m, KROS). Materiál = op b.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
+      <c r="A61" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="n">
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>Dodávka hranolového řeziva C24 pro krokve 100/180 mm vč. 10 % prořezu (fungicidní + protihmyzí impregnace)</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F61" s="15">
+        <f> 156 × 0.10 × 0.18 × 1.10 = 3.09 m³</f>
+        <v/>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>60512136</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.001 → HSV5.001b</t>
+        </is>
+      </c>
+      <c r="J61" s="15" t="inlineStr"/>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>Hranol řezivo do 288 cm² (60512136). Impregnace dle TZ statika §6.2.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Montáž kleštin 2×60/180 mm — vázaná konstrukce krovu pomocí ocelových spojek (průřez 216 cm², přes 120 do 224)</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>11 pozic × 2 ks × ~5 m délka = 110</t>
-        </is>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>762331912</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.002</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr"/>
-      <c r="K61" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="F62" s="15">
+        <f> HSV5.002 délka kleštin 110 bm</f>
+        <v/>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>762332122</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.002 → HSV5.002a</t>
+        </is>
+      </c>
+      <c r="J62" s="15" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr">
+        <is>
+          <t>Montáž 762332122 (266 Kč/m). Materiál = op b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="n">
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Dodávka hranolového řeziva C24 pro kleštiny 2×60/180 mm vč. 10 % prořezu + impregnace</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F63" s="15">
+        <f> 110 × 0.06 × 0.18 × 1.10 = 1.31 m³</f>
+        <v/>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>60512136</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.002 → HSV5.002b</t>
+        </is>
+      </c>
+      <c r="J63" s="15" t="inlineStr"/>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>Hranol řezivo (60512136).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Montáž pozednic 140/160 mm — vázaná konstrukce krovu pomocí ocelových spojek (průřez 224 cm², přes 120 do 224)</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="n">
         <v>19.4</v>
       </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>polovina obvodu (2 dlouhé strany) = ~20</t>
-        </is>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>762331923</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.003</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr"/>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="F64" s="15">
+        <f> HSV5.003 délka pozednic ~19.4 bm</f>
+        <v/>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>762332122</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.003 → HSV5.003a</t>
+        </is>
+      </c>
+      <c r="J64" s="15" t="inlineStr"/>
+      <c r="K64" s="15" t="inlineStr">
+        <is>
+          <t>Montáž 762332122. Kotvení do ŽB věnce = samostatně (CHYBÍ DETAIL — závitové tyče/kotvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="n">
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Dodávka hranolového řeziva C24 pro pozednice 140/160 mm vč. 10 % prořezu + impregnace</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F65" s="15">
+        <f> 19.4 × 0.14 × 0.16 × 1.10 = 0.48 m³</f>
+        <v/>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>60512136</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.003 → HSV5.003b</t>
+        </is>
+      </c>
+      <c r="J65" s="15" t="inlineStr"/>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>Hranol řezivo (60512136).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>Montáž námětků 60/100 mm — vázaná konstrukce krovu pomocí ocelových spojek (průřez 60 cm², přes 50 do 120)</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="n">
         <v>19.2</v>
       </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>24 krokví × 0.8 m námětek = 19.2</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>762331911</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.004</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr"/>
-      <c r="K63" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="F66" s="15">
+        <f> HSV5.004 délka námětků 19.2 bm</f>
+        <v/>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>762332121</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.004 → HSV5.004a</t>
+        </is>
+      </c>
+      <c r="J66" s="15" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>Montáž 762332121 (206 Kč/m, KROS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="n">
-        <v>608</v>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.005</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr"/>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
-        </is>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.006</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr"/>
-      <c r="K65" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F66" s="11">
-        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Dodávka hranolového řeziva C24 pro námětky 60/100 mm vč. 10 % prořezu + impregnace</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="F67" s="15">
+        <f> 19.2 × 0.06 × 0.10 × 1.10 = 0.127 m³</f>
         <v/>
       </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>762341711</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.007</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>155.034</v>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
-        <is>
-          <t>141 × 1.1 přesah = 155</t>
-        </is>
-      </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>712311101</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.008</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.004 → HSV5.004b</t>
+        </is>
+      </c>
+      <c r="J67" s="15" t="inlineStr"/>
+      <c r="K67" s="15" t="inlineStr">
+        <is>
+          <t>Hranol řezivo 605 família — leaf dle krátké délky &lt;6 m (60512136 je 6-8 m). Verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -4935,41 +4930,38 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
+          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F68" s="11">
-        <f> 141 m² (plocha krytiny krov)</f>
-        <v/>
+        <v>608</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+        </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>713131811</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.009</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.005</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
       <c r="K68" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -4987,25 +4979,25 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
+          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>155.034</v>
+        <v>176</v>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>141 × 1.1 přesah = 155</t>
+          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>712311111</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -5015,14 +5007,10 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.010</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.006</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
       <c r="K69" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5040,7 +5028,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
+          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -5052,12 +5040,12 @@
         <v>140.94</v>
       </c>
       <c r="F70" s="11">
-        <f> 141 m²</f>
+        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
         <v/>
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>762331923</t>
+          <t>762341711</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
@@ -5067,7 +5055,7 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.011</t>
+          <t>260219_dum.HSV5.007</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
@@ -5092,7 +5080,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
+          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -5101,15 +5089,16 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F71" s="11">
-        <f> 141 m²</f>
-        <v/>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>762341711</t>
+        <v>155.034</v>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>712311101</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -5119,7 +5108,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.012</t>
+          <t>260219_dum.HSV5.008</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
@@ -5144,7 +5133,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
+          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -5156,22 +5145,22 @@
         <v>140.94</v>
       </c>
       <c r="F72" s="11">
-        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <f> 141 m² (plocha krytiny krov)</f>
         <v/>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>765791121</t>
+          <t>713131811</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.013</t>
+          <t>260219_dum.HSV5.009</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
@@ -5196,7 +5185,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
+          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -5205,16 +5194,16 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>25</v>
+        <v>155.034</v>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>odhad — spací patro ~5 × 5 m</t>
+          <t>141 × 1.1 přesah = 155</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>762341711</t>
+          <t>712311111</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -5224,12 +5213,12 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.014</t>
+          <t>260219_dum.HSV5.010</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="K73" s="11" t="inlineStr">
@@ -5249,7 +5238,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -5258,16 +5247,15 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F74" s="11" t="inlineStr">
-        <is>
-          <t>4 vikýře × ~3 m² zděných čel = 12</t>
-        </is>
+        <v>140.94</v>
+      </c>
+      <c r="F74" s="11">
+        <f> 141 m²</f>
+        <v/>
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>311321411</t>
+          <t>762331923</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -5277,10 +5265,14 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.015</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.011</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5298,7 +5290,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
+          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -5307,179 +5299,222 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="F75" s="11" t="inlineStr">
-        <is>
-          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="inlineStr">
+        <v>140.94</v>
+      </c>
+      <c r="F75" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>762341711</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.012</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F76" s="11">
+        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <v/>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>765791121</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.016</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="inlineStr">
-        <is>
-          <t>S12b</t>
-        </is>
-      </c>
-      <c r="K75" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="n"/>
-      <c r="C76" s="9" t="n"/>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
-      <c r="H76" s="9" t="n"/>
-      <c r="I76" s="9" t="n"/>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.013</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
+          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>odhad — spací patro ~5 × 5 m</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>762341711</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.014</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
-        </is>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.001</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="inlineStr"/>
-      <c r="K77" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="17" t="n">
-        <v>71</v>
-      </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E78" s="19" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="F78" s="18">
-        <f> plocha krytiny ~141</f>
-        <v/>
-      </c>
-      <c r="G78" s="18" t="inlineStr"/>
-      <c r="H78" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I78" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.002</t>
-        </is>
-      </c>
-      <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>311321411</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.015</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>765791121</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -5489,10 +5524,14 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.003</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="inlineStr"/>
+          <t>260219_dum.HSV5.016</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5500,52 +5539,21 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F80" s="11">
-        <f> zastavěna 104.4 m²</f>
-        <v/>
-      </c>
-      <c r="G80" s="11" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.004</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr"/>
-      <c r="K80" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="9" t="n"/>
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="9" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="n">
@@ -5558,25 +5566,25 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
-        </is>
-      </c>
-      <c r="G81" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -5586,7 +5594,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.005</t>
+          <t>260219_dum.HSV6.001</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr"/>
@@ -5597,51 +5605,46 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="n">
+      <c r="A82" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B82" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.006</t>
-        </is>
-      </c>
-      <c r="J82" s="11" t="inlineStr"/>
-      <c r="K82" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="F82" s="18">
+        <f> plocha krytiny ~141</f>
+        <v/>
+      </c>
+      <c r="G82" s="18" t="inlineStr"/>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.002</t>
+        </is>
+      </c>
+      <c r="J82" s="18" t="inlineStr"/>
+      <c r="K82" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -5656,25 +5659,25 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
-        </is>
-      </c>
-      <c r="G83" s="13" t="inlineStr">
-        <is>
-          <t>781473810</t>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -5684,7 +5687,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.007</t>
+          <t>260219_dum.HSV6.003</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr"/>
@@ -5705,7 +5708,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -5714,16 +5717,15 @@
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>153.51</v>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
-        <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="F84" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -5733,7 +5735,7 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.008</t>
+          <t>260219_dum.HSV6.004</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr"/>
@@ -5754,25 +5756,25 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -5782,7 +5784,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.009</t>
+          <t>260219_dum.HSV6.005</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
@@ -5803,7 +5805,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -5812,16 +5814,16 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -5831,7 +5833,7 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.010</t>
+          <t>260219_dum.HSV6.006</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr"/>
@@ -5852,25 +5854,25 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
-        </is>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>725900001</t>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>781473810</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -5880,7 +5882,7 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.011</t>
+          <t>260219_dum.HSV6.007</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
@@ -5901,25 +5903,25 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>56.5</v>
+        <v>153.51</v>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -5929,7 +5931,7 @@
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.012</t>
+          <t>260219_dum.HSV6.008</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
@@ -5950,35 +5952,35 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>974041151</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.013</t>
+          <t>260219_dum.HSV6.009</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
@@ -5999,7 +6001,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -6008,26 +6010,26 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
-        </is>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>968071120</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.014</t>
+          <t>260219_dum.HSV6.010</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
@@ -6048,7 +6050,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -6057,16 +6059,16 @@
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -6076,7 +6078,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.011</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr"/>
@@ -6097,25 +6099,25 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0.6</v>
+        <v>56.5</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
-        </is>
-      </c>
-      <c r="G92" s="13" t="inlineStr">
-        <is>
-          <t>962024141</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr">
+        <is>
+          <t>997013501</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -6125,7 +6127,7 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.016</t>
+          <t>260219_dum.HSV6.012</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr"/>
@@ -6146,35 +6148,35 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.017</t>
+          <t>260219_dum.HSV6.013</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr"/>
@@ -6185,280 +6187,268 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="n"/>
-      <c r="C94" s="9" t="n"/>
-      <c r="D94" s="9" t="n"/>
-      <c r="E94" s="9" t="n"/>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="9" t="n"/>
-      <c r="H94" s="9" t="n"/>
-      <c r="I94" s="9" t="n"/>
-      <c r="J94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+      <c r="A94" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.014</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.015</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+        </is>
+      </c>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>962024141</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.016</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.017</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr"/>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="n"/>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C99" s="11" t="inlineStr">
         <is>
           <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E95" s="12" t="n">
+      <c r="E99" s="12" t="n">
         <v>276.7</v>
       </c>
-      <c r="F95" s="11" t="inlineStr">
+      <c r="F99" s="11" t="inlineStr">
         <is>
           <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
-      <c r="G95" s="11" t="inlineStr">
+      <c r="G99" s="11" t="inlineStr">
         <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="J95" s="11" t="inlineStr">
+      <c r="J99" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K95" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="14" t="n">
-        <v>88</v>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
-        </is>
-      </c>
-      <c r="D96" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F96" s="15">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G96" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H96" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002a</t>
-        </is>
-      </c>
-      <c r="J96" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K96" s="15" t="inlineStr">
-        <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="n">
-        <v>89</v>
-      </c>
-      <c r="B97" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F97" s="15">
-        <f> HSV7.002 plocha 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G97" s="15" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="H97" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002b</t>
-        </is>
-      </c>
-      <c r="J97" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K97" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
-        </is>
-      </c>
-      <c r="D98" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F98" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G98" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H98" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
-        </is>
-      </c>
-      <c r="J98" s="15" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="K98" s="15" t="inlineStr">
-        <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="n">
-        <v>91</v>
-      </c>
-      <c r="B99" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C99" s="15" t="inlineStr">
-        <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F99" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G99" s="15" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="H99" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I99" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
-        </is>
-      </c>
-      <c r="J99" s="15" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="K99" s="15" t="inlineStr">
-        <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -6473,24 +6463,24 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E100" s="16" t="n">
-        <v>82.2</v>
+        <v>276.7</v>
       </c>
       <c r="F100" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
         <v/>
       </c>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr">
@@ -6500,7 +6490,7 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
       <c r="J100" s="15" t="inlineStr">
@@ -6510,7 +6500,7 @@
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6525,148 +6515,356 @@
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F101" s="15">
+        <f> HSV7.002 plocha 276.7 m²</f>
+        <v/>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H101" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.002 → HSV7.002b</t>
+        </is>
+      </c>
+      <c r="J101" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="inlineStr">
+        <is>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F102" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+        </is>
+      </c>
+      <c r="J102" s="15" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F103" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+        </is>
+      </c>
+      <c r="J103" s="15" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K103" s="15" t="inlineStr">
+        <is>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F104" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+        </is>
+      </c>
+      <c r="J104" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K104" s="15" t="inlineStr">
+        <is>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
           <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
-      <c r="D101" s="14" t="inlineStr">
+      <c r="D105" s="14" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E101" s="16" t="n">
+      <c r="E105" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F101" s="15">
+      <c r="F105" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G101" s="15" t="inlineStr">
+      <c r="G105" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H101" s="14" t="inlineStr">
+      <c r="H105" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I101" s="15" t="inlineStr">
+      <c r="I105" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J101" s="15" t="inlineStr">
+      <c r="J105" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K101" s="15" t="inlineStr">
+      <c r="K105" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C102" s="11" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E102" s="12" t="n">
+      <c r="E106" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="11" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
         <is>
           <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
-      <c r="G102" s="11" t="inlineStr">
+      <c r="G106" s="11" t="inlineStr">
         <is>
           <t>622221221</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="inlineStr">
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.005</t>
         </is>
       </c>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="J106" s="11" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K102" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C103" s="11" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
         <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="E107" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F103" s="11" t="inlineStr">
+      <c r="F107" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G103" s="13" t="inlineStr">
+      <c r="G107" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H103" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I103" s="11" t="inlineStr">
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J103" s="11" t="inlineStr">
+      <c r="J107" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K103" s="11" t="inlineStr">
+      <c r="K107" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6678,10 +6876,10 @@
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A98:K98"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A94:K94"/>
+    <mergeCell ref="A80:K80"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14856,7 +15054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14974,83 +15172,83 @@
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.002</t>
+          <t>260219_dum.HSV5.001</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, </t>
+          <t>Tesařský krov — krokve 100/180 mm á 800 mm, rezivo C24 fungicidní + protihmyzí (cca 2×12 krokví × ~6.5 m)</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>276.7</v>
+        <v>156</v>
       </c>
       <c r="F4" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>HSV7.002a, HSV7.002b</t>
+          <t>HSV5.001a, HSV5.001b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003</t>
+          <t>260219_dum.HSV5.002</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Tesařský krov — kleštiny dvojfošny 60/180 mm probíhající v oblasti spací části</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>13.5</v>
+        <v>110</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>HSV7.003a, HSV7.003b</t>
+          <t>HSV5.002a, HSV5.002b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004</t>
+          <t>260219_dum.HSV5.003</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Tesařský krov — pozednice 140/160 mm kotvená do ŽB věnce 3.NP</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -15059,31 +15257,31 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>82.2</v>
+        <v>19.4</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>HSV7.004a, HSV7.004b</t>
+          <t>HSV5.003a, HSV5.003b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.HSV5.004</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Tesařský krov — námětky 60/100 v dolní koncové části pro přesah střechy ~500 mm</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -15092,31 +15290,31 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>43.5</v>
+        <v>19.2</v>
       </c>
       <c r="F7" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>PSV76.003a, PSV76.003b</t>
+          <t>HSV5.004a, HSV5.004b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.HSV7.002</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
+          <t xml:space="preserve">ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, </t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -15125,31 +15323,31 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>9.23</v>
+        <v>276.7</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>PSV76.002a, PSV76.002b</t>
+          <t>HSV7.002a, HSV7.002b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002</t>
+          <t>260219_dum.HSV7.003</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -15165,90 +15363,90 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>PSV77.002a, PSV77.002b</t>
+          <t>HSV7.003a, HSV7.003b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003</t>
+          <t>260219_dum.HSV7.004</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>32.4</v>
+        <v>82.2</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>PSV77.003a, PSV77.003b</t>
+          <t>HSV7.004a, HSV7.004b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001</t>
+          <t>260219_dum.PSV76.003</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>78.2</v>
+        <v>43.5</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>PSV78.001a, PSV78.001b</t>
+          <t>PSV76.003a, PSV76.003b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -15257,31 +15455,31 @@
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>208.4</v>
+        <v>9.23</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>PSV78.002a, PSV78.002b</t>
+          <t>PSV76.002a, PSV76.002b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003</t>
+          <t>260219_dum.PSV77.002</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -15290,31 +15488,31 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>201.6</v>
+        <v>13.5</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>PSV78.003a, PSV78.003b</t>
+          <t>PSV77.002a, PSV77.002b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004</t>
+          <t>260219_dum.PSV77.003</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -15323,177 +15521,309 @@
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>179.1</v>
+        <v>32.4</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>PSV78.004a, PSV78.004b</t>
+          <t>PSV77.003a, PSV77.003b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.004</t>
+          <t>260219_dum.PSV78.001</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
+          <t>PSV78.001a, PSV78.001b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.005</t>
+          <t>260219_dum.PSV78.002</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0</v>
+        <v>208.4</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
+          <t>PSV78.002a, PSV78.002b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.006</t>
+          <t>260219_dum.PSV78.003</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0</v>
+        <v>201.6</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
+          <t>PSV78.003a, PSV78.003b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.008</t>
+          <t>260219_dum.PSV78.004</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>15</v>
+        <v>179.1</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+          <t>PSV78.004a, PSV78.004b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.015</t>
+          <t>260219_dum.PSV72.004</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>set</t>
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV72.005</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV72.006</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV72.008</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV1.015</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -1140,7 +1140,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -1150,37 +1150,37 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1691,7 +1691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4521,7 +4521,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-5 Krov + střecha  (20 atomic operací) ━━</t>
+          <t>━━ HSV-5 Krov + střecha  (24 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B59" s="9" t="n"/>
@@ -5539,211 +5539,229 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F80" s="15">
+        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
+        <v/>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>762085112</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017 → HSV5.017a</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>Montáž 762085112. OVĚŘIT M12/M16 + délku dle statiky/tesařského detailu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" s="15">
+        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
+        <v/>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>31197004</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017 → HSV5.017b</t>
+        </is>
+      </c>
+      <c r="J81" s="15" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>Materiál svorníku (31197004).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>100 ks</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="15">
+        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
+        <v/>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>3111006</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017 → HSV5.017c</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>Matice (3111006), 2 na svorník.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>100 ks</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="15">
+        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
+        <v/>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>31121004</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017 → HSV5.017d</t>
+        </is>
+      </c>
+      <c r="J83" s="15" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>Podložka (31121004), 2 na svorník.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="9" t="n"/>
-      <c r="I80" s="9" t="n"/>
-      <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
-        </is>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.001</t>
-        </is>
-      </c>
-      <c r="J81" s="11" t="inlineStr"/>
-      <c r="K81" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="17" t="n">
-        <v>75</v>
-      </c>
-      <c r="B82" s="18" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="inlineStr">
-        <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E82" s="19" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="F82" s="18">
-        <f> plocha krytiny ~141</f>
-        <v/>
-      </c>
-      <c r="G82" s="18" t="inlineStr"/>
-      <c r="H82" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I82" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.002</t>
-        </is>
-      </c>
-      <c r="J82" s="18" t="inlineStr"/>
-      <c r="K82" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="inlineStr">
-        <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
-        </is>
-      </c>
-      <c r="G83" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.003</t>
-        </is>
-      </c>
-      <c r="J83" s="11" t="inlineStr"/>
-      <c r="K83" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F84" s="11">
-        <f> zastavěna 104.4 m²</f>
-        <v/>
-      </c>
-      <c r="G84" s="11" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.004</t>
-        </is>
-      </c>
-      <c r="J84" s="11" t="inlineStr"/>
-      <c r="K84" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="9" t="n"/>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="n">
@@ -5756,25 +5774,25 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
-        </is>
-      </c>
-      <c r="G85" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -5784,7 +5802,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.005</t>
+          <t>260219_dum.HSV6.001</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr"/>
@@ -5795,51 +5813,46 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="n">
+      <c r="A86" s="17" t="n">
         <v>79</v>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B86" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
-        </is>
-      </c>
-      <c r="G86" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.006</t>
-        </is>
-      </c>
-      <c r="J86" s="11" t="inlineStr"/>
-      <c r="K86" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="F86" s="18">
+        <f> plocha krytiny ~141</f>
+        <v/>
+      </c>
+      <c r="G86" s="18" t="inlineStr"/>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.002</t>
+        </is>
+      </c>
+      <c r="J86" s="18" t="inlineStr"/>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -5854,25 +5867,25 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
-        </is>
-      </c>
-      <c r="G87" s="13" t="inlineStr">
-        <is>
-          <t>781473810</t>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -5882,7 +5895,7 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.007</t>
+          <t>260219_dum.HSV6.003</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr"/>
@@ -5903,7 +5916,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -5912,16 +5925,15 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>153.51</v>
-      </c>
-      <c r="F88" s="11" t="inlineStr">
-        <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="F88" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -5931,7 +5943,7 @@
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.008</t>
+          <t>260219_dum.HSV6.004</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr"/>
@@ -5952,25 +5964,25 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -5980,7 +5992,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.009</t>
+          <t>260219_dum.HSV6.005</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr"/>
@@ -6001,7 +6013,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -6010,16 +6022,16 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -6029,7 +6041,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.010</t>
+          <t>260219_dum.HSV6.006</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr"/>
@@ -6050,25 +6062,25 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="inlineStr">
-        <is>
-          <t>725900001</t>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>781473810</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -6078,7 +6090,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.011</t>
+          <t>260219_dum.HSV6.007</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr"/>
@@ -6099,25 +6111,25 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>56.5</v>
+        <v>153.51</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -6127,7 +6139,7 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.012</t>
+          <t>260219_dum.HSV6.008</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr"/>
@@ -6148,35 +6160,35 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
-        </is>
-      </c>
-      <c r="G93" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>974041151</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.013</t>
+          <t>260219_dum.HSV6.009</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr"/>
@@ -6197,7 +6209,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -6206,26 +6218,26 @@
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
-        </is>
-      </c>
-      <c r="G94" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>968071120</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.014</t>
+          <t>260219_dum.HSV6.010</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr"/>
@@ -6246,7 +6258,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -6255,16 +6267,16 @@
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -6274,7 +6286,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.011</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr"/>
@@ -6295,25 +6307,25 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0.6</v>
+        <v>56.5</v>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
-        </is>
-      </c>
-      <c r="G96" s="13" t="inlineStr">
-        <is>
-          <t>962024141</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>997013501</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -6323,7 +6335,7 @@
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.016</t>
+          <t>260219_dum.HSV6.012</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr"/>
@@ -6344,35 +6356,35 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.017</t>
+          <t>260219_dum.HSV6.013</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr"/>
@@ -6383,280 +6395,268 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="n"/>
-      <c r="C98" s="9" t="n"/>
-      <c r="D98" s="9" t="n"/>
-      <c r="E98" s="9" t="n"/>
-      <c r="F98" s="9" t="n"/>
-      <c r="G98" s="9" t="n"/>
-      <c r="H98" s="9" t="n"/>
-      <c r="I98" s="9" t="n"/>
-      <c r="J98" s="9" t="n"/>
-      <c r="K98" s="9" t="n"/>
+      <c r="A98" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.014</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.015</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>962024141</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.016</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.017</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C99" s="11" t="inlineStr">
+      <c r="C103" s="11" t="inlineStr">
         <is>
           <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E103" s="12" t="n">
         <v>276.7</v>
       </c>
-      <c r="F99" s="11" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
         <is>
           <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G103" s="11" t="inlineStr">
         <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="J99" s="11" t="inlineStr">
+      <c r="J103" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="14" t="n">
-        <v>92</v>
-      </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
-        </is>
-      </c>
-      <c r="D100" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F100" s="15">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G100" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H100" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002a</t>
-        </is>
-      </c>
-      <c r="J100" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K100" s="15" t="inlineStr">
-        <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="14" t="n">
-        <v>93</v>
-      </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C101" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
-        </is>
-      </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="F101" s="15">
-        <f> HSV7.002 plocha 276.7 m²</f>
-        <v/>
-      </c>
-      <c r="G101" s="15" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="H101" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.002 → HSV7.002b</t>
-        </is>
-      </c>
-      <c r="J101" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K101" s="15" t="inlineStr">
-        <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="14" t="n">
-        <v>94</v>
-      </c>
-      <c r="B102" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="inlineStr">
-        <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
-        </is>
-      </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F102" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G102" s="15" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="H102" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I102" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
-        </is>
-      </c>
-      <c r="J102" s="15" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="K102" s="15" t="inlineStr">
-        <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="B103" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C103" s="15" t="inlineStr">
-        <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F103" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G103" s="15" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="H103" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
-        </is>
-      </c>
-      <c r="J103" s="15" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="K103" s="15" t="inlineStr">
-        <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -6671,24 +6671,24 @@
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E104" s="16" t="n">
-        <v>82.2</v>
+        <v>276.7</v>
       </c>
       <c r="F104" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
         <v/>
       </c>
       <c r="G104" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
       <c r="J104" s="15" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K104" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6723,148 +6723,356 @@
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F105" s="15">
+        <f> HSV7.002 plocha 276.7 m²</f>
+        <v/>
+      </c>
+      <c r="G105" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.002 → HSV7.002b</t>
+        </is>
+      </c>
+      <c r="J105" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K105" s="15" t="inlineStr">
+        <is>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F106" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+        </is>
+      </c>
+      <c r="J106" s="15" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K106" s="15" t="inlineStr">
+        <is>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F107" s="15">
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <v/>
+      </c>
+      <c r="G107" s="15" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H107" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+        </is>
+      </c>
+      <c r="J107" s="15" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K107" s="15" t="inlineStr">
+        <is>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F108" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+        </is>
+      </c>
+      <c r="J108" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
           <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
-      <c r="D105" s="14" t="inlineStr">
+      <c r="D109" s="14" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E105" s="16" t="n">
+      <c r="E109" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F105" s="15">
+      <c r="F109" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G105" s="15" t="inlineStr">
+      <c r="G109" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H105" s="14" t="inlineStr">
+      <c r="H109" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I105" s="15" t="inlineStr">
+      <c r="I109" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J105" s="15" t="inlineStr">
+      <c r="J109" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K105" s="15" t="inlineStr">
+      <c r="K109" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>98</v>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C106" s="11" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E106" s="12" t="n">
+      <c r="E110" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F106" s="11" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G110" s="11" t="inlineStr">
         <is>
           <t>622221221</t>
         </is>
       </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="inlineStr">
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.005</t>
         </is>
       </c>
-      <c r="J106" s="11" t="inlineStr">
+      <c r="J110" s="11" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K106" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C107" s="11" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D107" s="10" t="inlineStr">
+      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E107" s="12" t="n">
+      <c r="E111" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F107" s="11" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G107" s="13" t="inlineStr">
+      <c r="G111" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I107" s="11" t="inlineStr">
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J107" s="11" t="inlineStr">
+      <c r="J111" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K107" s="11" t="inlineStr">
+      <c r="K111" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
@@ -6876,10 +7084,10 @@
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A84:K84"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="A102:K102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15054,7 +15262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15826,6 +16034,39 @@
       <c r="G23" s="15" t="inlineStr">
         <is>
           <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorn</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>HSV5.017a, HSV5.017b, HSV5.017c, HSV5.017d</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -722,153 +722,153 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -878,37 +878,37 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -918,17 +918,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -938,17 +938,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -958,7 +958,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -968,108 +968,108 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B45" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>✓ verified (leaf ověřen)</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
+          <t>✓ verified (leaf ověřen)</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>167</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>⚠ família ??? (leaf z ÚRS online)</t>
+          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>53</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>⚠ família ??? (leaf z ÚRS online)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
+      <c r="B51" s="5" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>• PRÁCE JE KOMPLETNÍ bez ohledu na stav kódu — seznam (postup prací) = primary deliverable. Code = secondary, doplní se v ÚRS online / KROS.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Família</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Počet ops</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -1090,27 +1090,27 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -1120,27 +1120,27 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -1150,7 +1150,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -1160,57 +1160,57 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -1220,7 +1220,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1230,27 +1230,27 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -1260,7 +1260,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -1270,27 +1270,27 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -1300,7 +1300,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -1310,7 +1310,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1320,17 +1320,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -1340,7 +1340,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1350,7 +1350,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -1360,7 +1360,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -1370,17 +1370,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -1390,7 +1390,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -1400,7 +1400,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -1410,7 +1410,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -1420,7 +1420,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -1430,7 +1430,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1440,7 +1440,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,7 +1590,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -1600,64 +1600,74 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
@@ -1667,19 +1677,19 @@
   <mergeCells count="15">
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A121:C121"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1691,7 +1701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3771,7 +3781,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-4 Vodorovné  (14 atomic operací) ━━</t>
+          <t>━━ HSV-4 Vodorovné  (23 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B44" s="9" t="n"/>
@@ -4519,867 +4529,843 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-5 Krov + střecha  (24 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="n"/>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
+      <c r="A59" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F59" s="15">
+        <f> plocha stropu S07</f>
+        <v/>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>713191</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.015 → HSV4.015a</t>
+        </is>
+      </c>
+      <c r="J59" s="15" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>Montáž izolace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="n">
-        <v>54</v>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="A60" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F60" s="18">
+        <f> 59.5 × 1.05 prořez</f>
+        <v/>
+      </c>
+      <c r="G60" s="18" t="inlineStr"/>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.015 → HSV4.015b</t>
+        </is>
+      </c>
+      <c r="J60" s="18" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="K60" s="18" t="inlineStr">
+        <is>
+          <t>Materiál izolace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F61" s="18">
+        <f> 59.5 × 1.10 přesahy</f>
+        <v/>
+      </c>
+      <c r="G61" s="18" t="inlineStr"/>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.016 → HSV4.016a</t>
+        </is>
+      </c>
+      <c r="J61" s="18" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="K61" s="18" t="inlineStr">
+        <is>
+          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F62" s="15">
+        <f> plocha stropu S09</f>
+        <v/>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>713121</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.017 → HSV4.017a</t>
+        </is>
+      </c>
+      <c r="J62" s="15" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="K62" s="15" t="inlineStr">
+        <is>
+          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>Minerální vata 180/200 mm — materiál</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="F63" s="18">
+        <f> 104.4 × 1.05</f>
+        <v/>
+      </c>
+      <c r="G63" s="18" t="inlineStr"/>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.017 → HSV4.017b</t>
+        </is>
+      </c>
+      <c r="J63" s="18" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="K63" s="18" t="inlineStr">
+        <is>
+          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr"/>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.018 → HSV4.018a</t>
+        </is>
+      </c>
+      <c r="J64" s="18" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>VYJASNĚNÍ V1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>713191</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.019 → HSV4.019a</t>
+        </is>
+      </c>
+      <c r="J65" s="15" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>VYJASNĚNÍ V1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr"/>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.020 → HSV4.020a</t>
+        </is>
+      </c>
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>VYJASNĚNÍ V1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>Separační vrstva — S08 (neurčeno)</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr"/>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.021 → HSV4.021a</t>
+        </is>
+      </c>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="K67" s="18" t="inlineStr">
+        <is>
+          <t>VYJASNĚNÍ V1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Krov + střecha  (29 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="n"/>
+      <c r="H68" s="9" t="n"/>
+      <c r="I68" s="9" t="n"/>
+      <c r="J68" s="9" t="n"/>
+      <c r="K68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>Montáž krokví 100/180 mm — vázaná konstrukce krovu pomocí ocelových spojek, hraněné řezivo (průřez 180 cm², přes 120 do 224)</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E60" s="16" t="n">
+      <c r="E69" s="16" t="n">
         <v>156</v>
       </c>
-      <c r="F60" s="15">
+      <c r="F69" s="15">
         <f> HSV5.001 délka krokví 156 bm</f>
         <v/>
       </c>
-      <c r="G60" s="15" t="inlineStr">
+      <c r="G69" s="15" t="inlineStr">
         <is>
           <t>762332122</t>
         </is>
       </c>
-      <c r="H60" s="14" t="inlineStr">
+      <c r="H69" s="14" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr">
+      <c r="I69" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.001 → HSV5.001a</t>
         </is>
       </c>
-      <c r="J60" s="15" t="inlineStr"/>
-      <c r="K60" s="15" t="inlineStr">
+      <c r="J69" s="15" t="inlineStr"/>
+      <c r="K69" s="15" t="inlineStr">
         <is>
           <t>Montáž 762332122 (266 Kč/m, KROS). Materiál = op b.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="n">
-        <v>55</v>
-      </c>
-      <c r="B61" s="15" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>Dodávka hranolového řeziva C24 pro krokve 100/180 mm vč. 10 % prořezu (fungicidní + protihmyzí impregnace)</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E61" s="16" t="n">
+      <c r="E70" s="16" t="n">
         <v>3.09</v>
       </c>
-      <c r="F61" s="15">
+      <c r="F70" s="15">
         <f> 156 × 0.10 × 0.18 × 1.10 = 3.09 m³</f>
         <v/>
       </c>
-      <c r="G61" s="15" t="inlineStr">
+      <c r="G70" s="15" t="inlineStr">
         <is>
           <t>60512136</t>
         </is>
       </c>
-      <c r="H61" s="14" t="inlineStr">
+      <c r="H70" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I61" s="15" t="inlineStr">
+      <c r="I70" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.001 → HSV5.001b</t>
         </is>
       </c>
-      <c r="J61" s="15" t="inlineStr"/>
-      <c r="K61" s="15" t="inlineStr">
+      <c r="J70" s="15" t="inlineStr"/>
+      <c r="K70" s="15" t="inlineStr">
         <is>
           <t>Hranol řezivo do 288 cm² (60512136). Impregnace dle TZ statika §6.2.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="14" t="n">
-        <v>56</v>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>Montáž kleštin 2×60/180 mm — vázaná konstrukce krovu pomocí ocelových spojek (průřez 216 cm², přes 120 do 224)</t>
         </is>
       </c>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E62" s="16" t="n">
+      <c r="E71" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="F62" s="15">
+      <c r="F71" s="15">
         <f> HSV5.002 délka kleštin 110 bm</f>
         <v/>
       </c>
-      <c r="G62" s="15" t="inlineStr">
+      <c r="G71" s="15" t="inlineStr">
         <is>
           <t>762332122</t>
         </is>
       </c>
-      <c r="H62" s="14" t="inlineStr">
+      <c r="H71" s="14" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.002 → HSV5.002a</t>
         </is>
       </c>
-      <c r="J62" s="15" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr">
+      <c r="J71" s="15" t="inlineStr"/>
+      <c r="K71" s="15" t="inlineStr">
         <is>
           <t>Montáž 762332122 (266 Kč/m). Materiál = op b.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="n">
-        <v>57</v>
-      </c>
-      <c r="B63" s="15" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>Dodávka hranolového řeziva C24 pro kleštiny 2×60/180 mm vč. 10 % prořezu + impregnace</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E63" s="16" t="n">
+      <c r="E72" s="16" t="n">
         <v>1.31</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F72" s="15">
         <f> 110 × 0.06 × 0.18 × 1.10 = 1.31 m³</f>
         <v/>
       </c>
-      <c r="G63" s="15" t="inlineStr">
+      <c r="G72" s="15" t="inlineStr">
         <is>
           <t>60512136</t>
         </is>
       </c>
-      <c r="H63" s="14" t="inlineStr">
+      <c r="H72" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.002 → HSV5.002b</t>
         </is>
       </c>
-      <c r="J63" s="15" t="inlineStr"/>
-      <c r="K63" s="15" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr">
         <is>
           <t>Hranol řezivo (60512136).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="n">
-        <v>58</v>
-      </c>
-      <c r="B64" s="15" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>Montáž pozednic 140/160 mm — vázaná konstrukce krovu pomocí ocelových spojek (průřez 224 cm², přes 120 do 224)</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E64" s="16" t="n">
+      <c r="E73" s="16" t="n">
         <v>19.4</v>
       </c>
-      <c r="F64" s="15">
+      <c r="F73" s="15">
         <f> HSV5.003 délka pozednic ~19.4 bm</f>
         <v/>
       </c>
-      <c r="G64" s="15" t="inlineStr">
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>762332122</t>
         </is>
       </c>
-      <c r="H64" s="14" t="inlineStr">
+      <c r="H73" s="14" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I73" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.003 → HSV5.003a</t>
         </is>
       </c>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="15" t="inlineStr">
+      <c r="J73" s="15" t="inlineStr"/>
+      <c r="K73" s="15" t="inlineStr">
         <is>
           <t>Montáž 762332122. Kotvení do ŽB věnce = samostatně (CHYBÍ DETAIL — závitové tyče/kotvy).</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="14" t="n">
-        <v>59</v>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t>Dodávka hranolového řeziva C24 pro pozednice 140/160 mm vč. 10 % prořezu + impregnace</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E65" s="16" t="n">
+      <c r="E74" s="16" t="n">
         <v>0.48</v>
       </c>
-      <c r="F65" s="15">
+      <c r="F74" s="15">
         <f> 19.4 × 0.14 × 0.16 × 1.10 = 0.48 m³</f>
         <v/>
       </c>
-      <c r="G65" s="15" t="inlineStr">
+      <c r="G74" s="15" t="inlineStr">
         <is>
           <t>60512136</t>
         </is>
       </c>
-      <c r="H65" s="14" t="inlineStr">
+      <c r="H74" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.003 → HSV5.003b</t>
         </is>
       </c>
-      <c r="J65" s="15" t="inlineStr"/>
-      <c r="K65" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr">
         <is>
           <t>Hranol řezivo (60512136).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C75" s="15" t="inlineStr">
         <is>
           <t>Montáž námětků 60/100 mm — vázaná konstrukce krovu pomocí ocelových spojek (průřez 60 cm², přes 50 do 120)</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E66" s="16" t="n">
+      <c r="E75" s="16" t="n">
         <v>19.2</v>
       </c>
-      <c r="F66" s="15">
+      <c r="F75" s="15">
         <f> HSV5.004 délka námětků 19.2 bm</f>
         <v/>
       </c>
-      <c r="G66" s="15" t="inlineStr">
+      <c r="G75" s="15" t="inlineStr">
         <is>
           <t>762332121</t>
         </is>
       </c>
-      <c r="H66" s="14" t="inlineStr">
+      <c r="H75" s="14" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="I75" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.004 → HSV5.004a</t>
         </is>
       </c>
-      <c r="J66" s="15" t="inlineStr"/>
-      <c r="K66" s="15" t="inlineStr">
+      <c r="J75" s="15" t="inlineStr"/>
+      <c r="K75" s="15" t="inlineStr">
         <is>
           <t>Montáž 762332121 (206 Kč/m, KROS).</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="14" t="n">
-        <v>61</v>
-      </c>
-      <c r="B67" s="15" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C76" s="15" t="inlineStr">
         <is>
           <t>Dodávka hranolového řeziva C24 pro námětky 60/100 mm vč. 10 % prořezu + impregnace</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D76" s="14" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E67" s="16" t="n">
+      <c r="E76" s="16" t="n">
         <v>0.127</v>
       </c>
-      <c r="F67" s="15">
+      <c r="F76" s="15">
         <f> 19.2 × 0.06 × 0.10 × 1.10 = 0.127 m³</f>
         <v/>
       </c>
-      <c r="G67" s="15" t="inlineStr">
+      <c r="G76" s="15" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr">
+      <c r="H76" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.004 → HSV5.004b</t>
         </is>
       </c>
-      <c r="J67" s="15" t="inlineStr"/>
-      <c r="K67" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr">
         <is>
           <t>Hranol řezivo 605 família — leaf dle krátké délky &lt;6 m (60512136 je 6-8 m). Verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="n">
-        <v>608</v>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
-        </is>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.005</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
-        </is>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.006</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr"/>
-      <c r="K69" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F70" s="11">
-        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
-        <v/>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>762341711</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.007</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="n">
-        <v>155.034</v>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>141 × 1.1 přesah = 155</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>712311101</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.008</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K71" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F72" s="11">
-        <f> 141 m² (plocha krytiny krov)</f>
-        <v/>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>713131811</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.009</t>
-        </is>
-      </c>
-      <c r="J72" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="n">
-        <v>155.034</v>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>141 × 1.1 přesah = 155</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>712311111</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.010</t>
-        </is>
-      </c>
-      <c r="J73" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F74" s="11">
-        <f> 141 m²</f>
-        <v/>
-      </c>
-      <c r="G74" s="11" t="inlineStr">
-        <is>
-          <t>762331923</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.011</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F75" s="11">
-        <f> 141 m²</f>
-        <v/>
-      </c>
-      <c r="G75" s="13" t="inlineStr">
-        <is>
-          <t>762341711</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.012</t>
-        </is>
-      </c>
-      <c r="J75" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K75" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Krov + střecha</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="n">
-        <v>140.94</v>
-      </c>
-      <c r="F76" s="11">
-        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
-        <v/>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>765791121</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.013</t>
-        </is>
-      </c>
-      <c r="J76" s="11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="K76" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -5394,25 +5380,25 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
+          <t>Ocelová středová vaznice HEA160 — 2 ks × cca 10 m délka</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>25</v>
+        <v>608</v>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>odhad — spací patro ~5 × 5 m</t>
-        </is>
-      </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>762341711</t>
+          <t>2 × 10 × 30.4 kg/m (HEA160) = 608</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
@@ -5422,14 +5408,10 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.014</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="inlineStr">
-        <is>
-          <t>S11</t>
-        </is>
-      </c>
+          <t>260219_dum.HSV5.005</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr"/>
       <c r="K77" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
@@ -5447,25 +5429,25 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+          <t>Ocelové sloupky uzavřený profil 100×100×4 mm pod vaznice HEA160 (~6 ks × ~2.5 m výška)</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+          <t>6 × 2.5 × 11.7 kg/m (RHS 100×100×4) = 176</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>311321411</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -5475,7 +5457,7 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.015</t>
+          <t>260219_dum.HSV5.006</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr"/>
@@ -5496,7 +5478,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
+          <t>Bednění z prken tl. 20 mm pod nadkrokevní PIR (biodeska/palubka)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -5505,943 +5487,970 @@
         </is>
       </c>
       <c r="E79" s="12" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F79" s="11">
+        <f> 141 m² (plocha střechy včetně sklonu + přesahy)</f>
+        <v/>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>762341711</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.007</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Parotěsná folie nad bedněním pod nadkrokevní PIR (např. Isover Vario nebo Tyvek Air guard)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>155.034</v>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>712311101</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.008</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Nadkrokevní tepelná izolace PIR (polyisokyanurát) tl. 160 mm (λ=0,022 W/mK) — řez A-A S10 explicit</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F81" s="11">
+        <f> 141 m² (plocha krytiny krov)</f>
+        <v/>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>713131811</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.009</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Doplňková hydroizolační difuzně otevřená folie nad PIR pod kontralatě</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="n">
+        <v>155.034</v>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>141 × 1.1 přesah = 155</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>712311111</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.010</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Distanční kontralatě 40×60 mm pro vzduchovou mezeru nad PIR</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F83" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>762331923</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.011</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Bednění z prken tl. 25 mm pod plechovou hliníkovou krytinu (rozsah dle technologie krytiny)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F84" s="11">
+        <f> 141 m²</f>
+        <v/>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>762341711</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.012</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Plechová falcovaná HLINÍKOVÁ krytina (např. PREFA, Rheinzink, Lindab) + tlumící podložka</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F85" s="11">
+        <f> 141 m² (vč. vikýřů přidat ~10%)</f>
+        <v/>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>765791121</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.013</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>Patro pro přespání v krovu — biodeska / OSB desky tl. 22 mm nad kleštinami</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>odhad — spací patro ~5 × 5 m</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>762341711</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.014</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Vikýře — zděná čela z Porotherm 30 (odhad 4 ks × ~3 m² stěna)</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>4 vikýře × ~3 m² zděných čel = 12</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>311321411</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.015</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Fasádní minerální izolace λ0.035 180 mm + kotvy fasády — vikýře S12b</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>4 vikýře × 2 strany × ~3 m² = 24</t>
-        </is>
-      </c>
-      <c r="G79" s="11" t="inlineStr">
-        <is>
-          <t>765791121</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV5.016</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="inlineStr">
+      <c r="F88" s="15">
+        <f> 4 vikýře × ~6 m²</f>
+        <v/>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.016 → HSV5.016a</t>
+        </is>
+      </c>
+      <c r="J88" s="15" t="inlineStr">
         <is>
           <t>S12b</t>
         </is>
       </c>
-      <c r="K79" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="K88" s="15" t="inlineStr">
+        <is>
+          <t>Vrstva 1 izolace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C80" s="15" t="inlineStr">
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>Paropropustná fasádní folie s UV odolností — vikýře</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="F89" s="18">
+        <f> 24 × 1.10</f>
+        <v/>
+      </c>
+      <c r="G89" s="18" t="inlineStr"/>
+      <c r="H89" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.016 → HSV5.016b</t>
+        </is>
+      </c>
+      <c r="J89" s="18" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>Vrstva 2 folie.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Svislý nosný rastr 40×60 mm + ochranný nátěr — vikýře</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" s="18">
+        <f> plocha fasády vikýřů</f>
+        <v/>
+      </c>
+      <c r="G90" s="18" t="inlineStr"/>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.016 → HSV5.016c</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>Vrstva 3 rastr.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>Celoplošné bednění prkna 25 mm — vikýře</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" s="18">
+        <f> plocha fasády vikýřů</f>
+        <v/>
+      </c>
+      <c r="G91" s="18" t="inlineStr"/>
+      <c r="H91" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.016 → HSV5.016d</t>
+        </is>
+      </c>
+      <c r="J91" s="18" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
+      <c r="K91" s="18" t="inlineStr">
+        <is>
+          <t>Vrstva 4 bednění.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>Falcovaný hliníkový plech — krycí vrstva vikýře</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="F92" s="18">
+        <f> 24 × 1.10</f>
+        <v/>
+      </c>
+      <c r="G92" s="18" t="inlineStr"/>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.016 → HSV5.016e</t>
+        </is>
+      </c>
+      <c r="J92" s="18" t="inlineStr">
+        <is>
+          <t>S12b</t>
+        </is>
+      </c>
+      <c r="K92" s="18" t="inlineStr">
+        <is>
+          <t>Vrstva 5 plech.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
         </is>
       </c>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="D93" s="14" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E80" s="16" t="n">
+      <c r="E93" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F80" s="15">
+      <c r="F93" s="15">
         <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
         <v/>
       </c>
-      <c r="G80" s="15" t="inlineStr">
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>762085112</t>
         </is>
       </c>
-      <c r="H80" s="14" t="inlineStr">
+      <c r="H93" s="14" t="inlineStr">
         <is>
           <t>✓ verified</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.017 → HSV5.017a</t>
         </is>
       </c>
-      <c r="J80" s="15" t="inlineStr">
+      <c r="J93" s="15" t="inlineStr">
         <is>
           <t>Krov — spojovací prostředky</t>
         </is>
       </c>
-      <c r="K80" s="15" t="inlineStr">
+      <c r="K93" s="15" t="inlineStr">
         <is>
           <t>Montáž 762085112. OVĚŘIT M12/M16 + délku dle statiky/tesařského detailu.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C81" s="15" t="inlineStr">
+      <c r="C94" s="15" t="inlineStr">
         <is>
           <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="D94" s="14" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E81" s="16" t="n">
+      <c r="E94" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="F81" s="15">
+      <c r="F94" s="15">
         <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
         <v/>
       </c>
-      <c r="G81" s="15" t="inlineStr">
+      <c r="G94" s="15" t="inlineStr">
         <is>
           <t>31197004</t>
         </is>
       </c>
-      <c r="H81" s="14" t="inlineStr">
+      <c r="H94" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I81" s="15" t="inlineStr">
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.017 → HSV5.017b</t>
         </is>
       </c>
-      <c r="J81" s="15" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr">
         <is>
           <t>Krov — spojovací prostředky</t>
         </is>
       </c>
-      <c r="K81" s="15" t="inlineStr">
+      <c r="K94" s="15" t="inlineStr">
         <is>
           <t>Materiál svorníku (31197004).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="14" t="n">
-        <v>76</v>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C95" s="15" t="inlineStr">
         <is>
           <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
+      <c r="D95" s="14" t="inlineStr">
         <is>
           <t>100 ks</t>
         </is>
       </c>
-      <c r="E82" s="16" t="n">
+      <c r="E95" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="15">
+      <c r="F95" s="15">
         <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
         <v/>
       </c>
-      <c r="G82" s="15" t="inlineStr">
+      <c r="G95" s="15" t="inlineStr">
         <is>
           <t>3111006</t>
         </is>
       </c>
-      <c r="H82" s="14" t="inlineStr">
+      <c r="H95" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="I95" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.017 → HSV5.017c</t>
         </is>
       </c>
-      <c r="J82" s="15" t="inlineStr">
+      <c r="J95" s="15" t="inlineStr">
         <is>
           <t>Krov — spojovací prostředky</t>
         </is>
       </c>
-      <c r="K82" s="15" t="inlineStr">
+      <c r="K95" s="15" t="inlineStr">
         <is>
           <t>Matice (3111006), 2 na svorník.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="14" t="n">
-        <v>77</v>
-      </c>
-      <c r="B83" s="15" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C96" s="15" t="inlineStr">
         <is>
           <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D96" s="14" t="inlineStr">
         <is>
           <t>100 ks</t>
         </is>
       </c>
-      <c r="E83" s="16" t="n">
+      <c r="E96" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="15">
+      <c r="F96" s="15">
         <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
         <v/>
       </c>
-      <c r="G83" s="15" t="inlineStr">
+      <c r="G96" s="15" t="inlineStr">
         <is>
           <t>31121004</t>
         </is>
       </c>
-      <c r="H83" s="14" t="inlineStr">
+      <c r="H96" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I83" s="15" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV5.017 → HSV5.017d</t>
         </is>
       </c>
-      <c r="J83" s="15" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr">
         <is>
           <t>Krov — spojovací prostředky</t>
         </is>
       </c>
-      <c r="K83" s="15" t="inlineStr">
+      <c r="K96" s="15" t="inlineStr">
         <is>
           <t>Podložka (31121004), 2 na svorník.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="n"/>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr">
-        <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
-        </is>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.001</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr"/>
-      <c r="K85" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="n">
-        <v>79</v>
-      </c>
-      <c r="B86" s="18" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
-        </is>
-      </c>
-      <c r="D86" s="17" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E86" s="19" t="n">
-        <v>140.9</v>
-      </c>
-      <c r="F86" s="18">
-        <f> plocha krytiny ~141</f>
+      <c r="E97" s="19" t="n">
+        <v>155</v>
+      </c>
+      <c r="F97" s="18">
+        <f> 140.94 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="G86" s="18" t="inlineStr"/>
-      <c r="H86" s="17" t="inlineStr">
+      <c r="G97" s="18" t="inlineStr"/>
+      <c r="H97" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I86" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.002</t>
-        </is>
-      </c>
-      <c r="J86" s="18" t="inlineStr"/>
-      <c r="K86" s="18" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F87" s="11" t="inlineStr">
-        <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
-        </is>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.003</t>
-        </is>
-      </c>
-      <c r="J87" s="11" t="inlineStr"/>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C88" s="11" t="inlineStr">
-        <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="F88" s="11">
-        <f> zastavěna 104.4 m²</f>
-        <v/>
-      </c>
-      <c r="G88" s="11" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.004</t>
-        </is>
-      </c>
-      <c r="J88" s="11" t="inlineStr"/>
-      <c r="K88" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr">
-        <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
-        </is>
-      </c>
-      <c r="G89" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.005</t>
-        </is>
-      </c>
-      <c r="J89" s="11" t="inlineStr"/>
-      <c r="K89" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C90" s="11" t="inlineStr">
-        <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F90" s="11" t="inlineStr">
-        <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.006</t>
-        </is>
-      </c>
-      <c r="J90" s="11" t="inlineStr"/>
-      <c r="K90" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
-        </is>
-      </c>
-      <c r="G91" s="13" t="inlineStr">
-        <is>
-          <t>781473810</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.007</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr"/>
-      <c r="K91" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="B92" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C92" s="11" t="inlineStr">
-        <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
-        </is>
-      </c>
-      <c r="D92" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>153.51</v>
-      </c>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr">
-        <is>
-          <t>974031132</t>
-        </is>
-      </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.008</t>
-        </is>
-      </c>
-      <c r="J92" s="11" t="inlineStr"/>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="n">
-        <v>86</v>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>974041151</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.009</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr"/>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr">
-        <is>
-          <t>968071120</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.010</t>
-        </is>
-      </c>
-      <c r="J94" s="11" t="inlineStr"/>
-      <c r="K94" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="B95" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C95" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr">
-        <is>
-          <t>725900001</t>
-        </is>
-      </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.011</t>
-        </is>
-      </c>
-      <c r="J95" s="11" t="inlineStr"/>
-      <c r="K95" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
-        </is>
-      </c>
-      <c r="G96" s="11" t="inlineStr">
-        <is>
-          <t>997013501</t>
-        </is>
-      </c>
-      <c r="H96" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.012</t>
-        </is>
-      </c>
-      <c r="J96" s="11" t="inlineStr"/>
-      <c r="K96" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="F97" s="11" t="inlineStr">
-        <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
-        </is>
-      </c>
-      <c r="G97" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.013</t>
-        </is>
-      </c>
-      <c r="J97" s="11" t="inlineStr"/>
-      <c r="K97" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.018 → HSV5.018a</t>
+        </is>
+      </c>
+      <c r="J97" s="18" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="K97" s="18" t="inlineStr">
+        <is>
+          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
-        </is>
-      </c>
-      <c r="G98" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
-        </is>
-      </c>
-      <c r="H98" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.014</t>
-        </is>
-      </c>
-      <c r="J98" s="11" t="inlineStr"/>
-      <c r="K98" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-6 Bourací práce  (18 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="n"/>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="n">
@@ -6454,25 +6463,25 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
-        </is>
-      </c>
-      <c r="G99" s="11" t="inlineStr">
-        <is>
-          <t>968072456</t>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -6482,7 +6491,7 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.001</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr"/>
@@ -6493,51 +6502,46 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="n">
+      <c r="A100" s="17" t="n">
         <v>93</v>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B100" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F100" s="11" t="inlineStr">
-        <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
-        </is>
-      </c>
-      <c r="G100" s="13" t="inlineStr">
-        <is>
-          <t>962024141</t>
-        </is>
-      </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.016</t>
-        </is>
-      </c>
-      <c r="J100" s="11" t="inlineStr"/>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="F100" s="18">
+        <f> plocha krytiny ~141</f>
+        <v/>
+      </c>
+      <c r="G100" s="18" t="inlineStr"/>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.002</t>
+        </is>
+      </c>
+      <c r="J100" s="18" t="inlineStr"/>
+      <c r="K100" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6556,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -6561,16 +6565,16 @@
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
-        </is>
-      </c>
-      <c r="G101" s="13" t="inlineStr">
-        <is>
-          <t>961044111</t>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -6580,7 +6584,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.017</t>
+          <t>260219_dum.HSV6.003</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr"/>
@@ -6591,503 +6595,1498 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="n"/>
-      <c r="C102" s="9" t="n"/>
-      <c r="D102" s="9" t="n"/>
-      <c r="E102" s="9" t="n"/>
-      <c r="F102" s="9" t="n"/>
-      <c r="G102" s="9" t="n"/>
-      <c r="H102" s="9" t="n"/>
-      <c r="I102" s="9" t="n"/>
-      <c r="J102" s="9" t="n"/>
-      <c r="K102" s="9" t="n"/>
+      <c r="A102" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F102" s="11">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>962041141</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.004</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.005</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr"/>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>962031132</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.006</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>781473810</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.007</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>153.51</v>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>974031132</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.008</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>974041151</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.009</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr"/>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>968071120</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.010</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>725900001</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.011</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr"/>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>997013501</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.012</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+        </is>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.013</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr"/>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.014</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr"/>
+      <c r="K112" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.015</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr"/>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+        </is>
+      </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>962024141</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.016</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr"/>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.017</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr"/>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F116" s="18">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G116" s="18" t="inlineStr"/>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.018 → HSV6.018a</t>
+        </is>
+      </c>
+      <c r="J116" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K116" s="18" t="inlineStr">
+        <is>
+          <t>Bourání.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
+      <c r="H117" s="9" t="n"/>
+      <c r="I117" s="9" t="n"/>
+      <c r="J117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C103" s="11" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="E118" s="12" t="n">
         <v>276.7</v>
       </c>
-      <c r="F103" s="11" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
         <is>
           <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G118" s="11" t="inlineStr">
         <is>
           <t>622401110</t>
         </is>
       </c>
-      <c r="H103" s="10" t="inlineStr">
+      <c r="H118" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I103" s="11" t="inlineStr">
+      <c r="I118" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.001</t>
         </is>
       </c>
-      <c r="J103" s="11" t="inlineStr">
+      <c r="J118" s="11" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K103" s="11" t="inlineStr">
+      <c r="K118" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="14" t="n">
-        <v>96</v>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="B119" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C104" s="15" t="inlineStr">
+      <c r="C119" s="15" t="inlineStr">
         <is>
           <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
-      <c r="D104" s="14" t="inlineStr">
+      <c r="D119" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E104" s="16" t="n">
+      <c r="E119" s="16" t="n">
         <v>276.7</v>
       </c>
-      <c r="F104" s="15">
+      <c r="F119" s="15">
         <f> HSV7.002 plocha fasády 276.7 m²</f>
         <v/>
       </c>
-      <c r="G104" s="15" t="inlineStr">
+      <c r="G119" s="15" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="H104" s="14" t="inlineStr">
+      <c r="H119" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I104" s="15" t="inlineStr">
+      <c r="I119" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.002 → HSV7.002a</t>
         </is>
       </c>
-      <c r="J104" s="15" t="inlineStr">
+      <c r="J119" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K104" s="15" t="inlineStr">
+      <c r="K119" s="15" t="inlineStr">
         <is>
           <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="14" t="n">
-        <v>97</v>
-      </c>
-      <c r="B105" s="15" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C105" s="15" t="inlineStr">
+      <c r="C120" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
         </is>
       </c>
-      <c r="D105" s="14" t="inlineStr">
+      <c r="D120" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E105" s="16" t="n">
+      <c r="E120" s="16" t="n">
         <v>276.7</v>
       </c>
-      <c r="F105" s="15">
+      <c r="F120" s="15">
         <f> HSV7.002 plocha 276.7 m²</f>
         <v/>
       </c>
-      <c r="G105" s="15" t="inlineStr">
+      <c r="G120" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H105" s="14" t="inlineStr">
+      <c r="H120" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I105" s="15" t="inlineStr">
+      <c r="I120" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.002 → HSV7.002b</t>
         </is>
       </c>
-      <c r="J105" s="15" t="inlineStr">
+      <c r="J120" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K105" s="15" t="inlineStr">
+      <c r="K120" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="14" t="n">
-        <v>98</v>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C106" s="15" t="inlineStr">
+      <c r="C121" s="15" t="inlineStr">
         <is>
           <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
-      <c r="D106" s="14" t="inlineStr">
+      <c r="D121" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E106" s="16" t="n">
+      <c r="E121" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="F106" s="15">
+      <c r="F121" s="15">
         <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
-      <c r="G106" s="15" t="inlineStr">
+      <c r="G121" s="15" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="H106" s="14" t="inlineStr">
+      <c r="H121" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I106" s="15" t="inlineStr">
+      <c r="I121" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
-      <c r="J106" s="15" t="inlineStr">
+      <c r="J121" s="15" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K106" s="15" t="inlineStr">
+      <c r="K121" s="15" t="inlineStr">
         <is>
           <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C107" s="15" t="inlineStr">
+      <c r="C122" s="15" t="inlineStr">
         <is>
           <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
         </is>
       </c>
-      <c r="D107" s="14" t="inlineStr">
+      <c r="D122" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E107" s="16" t="n">
+      <c r="E122" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="F107" s="15">
+      <c r="F122" s="15">
         <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
-      <c r="G107" s="15" t="inlineStr">
+      <c r="G122" s="15" t="inlineStr">
         <is>
           <t>781</t>
         </is>
       </c>
-      <c r="H107" s="14" t="inlineStr">
+      <c r="H122" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I107" s="15" t="inlineStr">
+      <c r="I122" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.003 → HSV7.003b</t>
         </is>
       </c>
-      <c r="J107" s="15" t="inlineStr">
+      <c r="J122" s="15" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="K107" s="15" t="inlineStr">
+      <c r="K122" s="15" t="inlineStr">
         <is>
           <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="B108" s="15" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C108" s="15" t="inlineStr">
+      <c r="C123" s="15" t="inlineStr">
         <is>
           <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
-      <c r="D108" s="14" t="inlineStr">
+      <c r="D123" s="14" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E108" s="16" t="n">
+      <c r="E123" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F108" s="15">
+      <c r="F123" s="15">
         <f> HSV7.004 obvod špalet 82.2 bm</f>
         <v/>
       </c>
-      <c r="G108" s="15" t="inlineStr">
+      <c r="G123" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H108" s="14" t="inlineStr">
+      <c r="H123" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I108" s="15" t="inlineStr">
+      <c r="I123" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004a</t>
         </is>
       </c>
-      <c r="J108" s="15" t="inlineStr">
+      <c r="J123" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K108" s="15" t="inlineStr">
+      <c r="K123" s="15" t="inlineStr">
         <is>
           <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="B109" s="15" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B124" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C109" s="15" t="inlineStr">
+      <c r="C124" s="15" t="inlineStr">
         <is>
           <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
+      <c r="D124" s="14" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E109" s="16" t="n">
+      <c r="E124" s="16" t="n">
         <v>82.2</v>
       </c>
-      <c r="F109" s="15">
+      <c r="F124" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G109" s="15" t="inlineStr">
+      <c r="G124" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H109" s="14" t="inlineStr">
+      <c r="H124" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I109" s="15" t="inlineStr">
+      <c r="I124" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J109" s="15" t="inlineStr">
+      <c r="J124" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K109" s="15" t="inlineStr">
+      <c r="K124" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>102</v>
-      </c>
-      <c r="B110" s="11" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C110" s="11" t="inlineStr">
+      <c r="C125" s="11" t="inlineStr">
         <is>
           <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D125" s="10" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="E125" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F110" s="11" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G125" s="11" t="inlineStr">
         <is>
           <t>622221221</t>
         </is>
       </c>
-      <c r="H110" s="10" t="inlineStr">
+      <c r="H125" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr">
+      <c r="I125" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.005</t>
         </is>
       </c>
-      <c r="J110" s="11" t="inlineStr">
+      <c r="J125" s="11" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K110" s="11" t="inlineStr">
+      <c r="K125" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C111" s="11" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
         <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D111" s="10" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E111" s="12" t="n">
+      <c r="E126" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F111" s="11" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G111" s="13" t="inlineStr">
+      <c r="G126" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="H126" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I111" s="11" t="inlineStr">
+      <c r="I126" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J111" s="11" t="inlineStr">
+      <c r="J126" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K111" s="11" t="inlineStr">
+      <c r="K126" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda + zateplení  (5 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="9" t="n"/>
+      <c r="H127" s="9" t="n"/>
+      <c r="I127" s="9" t="n"/>
+      <c r="J127" s="9" t="n"/>
+      <c r="K127" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F128" s="18">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G128" s="18" t="inlineStr"/>
+      <c r="H128" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I128" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.007 → HSV7.007a</t>
+        </is>
+      </c>
+      <c r="J128" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K128" s="18" t="inlineStr">
+        <is>
+          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F129" s="18">
+        <f> 23 × 1.05</f>
+        <v/>
+      </c>
+      <c r="G129" s="18" t="inlineStr"/>
+      <c r="H129" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I129" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.007 → HSV7.007b</t>
+        </is>
+      </c>
+      <c r="J129" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K129" s="18" t="inlineStr">
+        <is>
+          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="F130" s="18">
+        <f> 23 × 1.10</f>
+        <v/>
+      </c>
+      <c r="G130" s="18" t="inlineStr"/>
+      <c r="H130" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.008 → HSV7.008a</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K130" s="18" t="inlineStr">
+        <is>
+          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F131" s="18">
+        <f> 23 (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G131" s="18" t="inlineStr"/>
+      <c r="H131" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I131" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.009 → HSV7.009a</t>
+        </is>
+      </c>
+      <c r="J131" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K131" s="18" t="inlineStr">
+        <is>
+          <t>Rošt.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr">
+        <is>
+          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F132" s="15">
+        <f> 23 × 1.05</f>
+        <v/>
+      </c>
+      <c r="G132" s="15" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.009 → HSV7.009b</t>
+        </is>
+      </c>
+      <c r="J132" s="15" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K132" s="15" t="inlineStr">
+        <is>
+          <t>Obklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A127:K127"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A117:K117"/>
+    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A44:K44"/>
     <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A102:K102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7405,7 +8404,7 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -7431,7 +8430,11 @@
           <t>260219_dum.PSV71.002</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
@@ -15262,7 +16265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15512,17 +16515,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.002</t>
+          <t>260219_dum.HSV5.016</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, </t>
+          <t>Vikýře — provětrávaná fasáda min. vata + plech falcovaný hliník (4 vikýře × ~6 m² fasády)</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -15531,21 +16534,21 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>276.7</v>
+        <v>24</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>HSV7.002a, HSV7.002b</t>
+          <t>HSV5.016a, HSV5.016b, HSV5.016c, HSV5.016d, HSV5.016e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003</t>
+          <t>260219_dum.HSV7.002</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -15555,7 +16558,7 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t xml:space="preserve">ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, </t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -15564,21 +16567,21 @@
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>HSV7.003a, HSV7.003b</t>
+          <t>HSV7.002a, HSV7.002b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004</t>
+          <t>260219_dum.HSV7.003</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -15588,40 +16591,40 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>HSV7.004a, HSV7.004b</t>
+          <t>HSV7.003a, HSV7.003b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.HSV7.004</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -15630,64 +16633,64 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>43.5</v>
+        <v>82.2</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>PSV76.003a, PSV76.003b</t>
+          <t>HSV7.004a, HSV7.004b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.003</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>9.23</v>
+        <v>43.5</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>PSV76.002a, PSV76.002b</t>
+          <t>PSV76.003a, PSV76.003b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002</t>
+          <t>260219_dum.PSV76.002</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -15696,21 +16699,21 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>13.5</v>
+        <v>9.23</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>PSV77.002a, PSV77.002b</t>
+          <t>PSV76.002a, PSV76.002b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003</t>
+          <t>260219_dum.PSV77.002</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -15720,7 +16723,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -15729,31 +16732,31 @@
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>PSV77.003a, PSV77.003b</t>
+          <t>PSV77.002a, PSV77.002b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001</t>
+          <t>260219_dum.PSV77.003</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -15762,21 +16765,21 @@
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>78.2</v>
+        <v>32.4</v>
       </c>
       <c r="F15" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>PSV78.001a, PSV78.001b</t>
+          <t>PSV77.003a, PSV77.003b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002</t>
+          <t>260219_dum.PSV78.001</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -15786,7 +16789,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -15795,21 +16798,21 @@
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="F16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>PSV78.002a, PSV78.002b</t>
+          <t>PSV78.001a, PSV78.001b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003</t>
+          <t>260219_dum.PSV78.002</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -15819,7 +16822,7 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -15828,21 +16831,21 @@
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>PSV78.003a, PSV78.003b</t>
+          <t>PSV78.002a, PSV78.002b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004</t>
+          <t>260219_dum.PSV78.003</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -15852,7 +16855,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -15861,54 +16864,54 @@
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="F18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>PSV78.004a, PSV78.004b</t>
+          <t>PSV78.003a, PSV78.003b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.004</t>
+          <t>260219_dum.PSV78.004</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>179.1</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
+          <t>PSV78.004a, PSV78.004b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.005</t>
+          <t>260219_dum.PSV72.004</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
@@ -15918,7 +16921,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -15934,14 +16937,14 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
+          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.006</t>
+          <t>260219_dum.PSV72.005</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -15951,7 +16954,7 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -15967,14 +16970,14 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
+          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.008</t>
+          <t>260219_dum.PSV72.006</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
@@ -15984,89 +16987,510 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>set</t>
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.015</t>
+          <t>260219_dum.PSV72.008</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
+          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t>260219_dum.HSV1.015</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
           <t>260219_dum.HSV5.017</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorn</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E25" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F25" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>HSV5.017a, HSV5.017b, HSV5.017c, HSV5.017d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.015</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.015a, HSV4.015b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.016</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.016a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.017</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.017a, HSV4.017b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.018</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.018a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.019</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.019a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.020</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.020a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.021</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>HSV4.021a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.007</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou +</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>HSV7.007a, HSV7.007b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.008</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>HSV7.008a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.009</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>HSV7.009a, HSV7.009b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.018</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>HSV5.018a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV6.018</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>HSV6.018a</t>
         </is>
       </c>
     </row>
@@ -16081,7 +17505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16276,27 +17700,127 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>S08 strop cihelná klemba mezi patry — plocha / poloha</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Karle/projektante: má dům cihelnou klembu mezi patry (S08)? Pokud ano — kde (které místnosti) a jaká plocha m²? Doplníme množství.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>S12 podkroví — vnitřní omítka sádrová vs vápenocementová</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Karle: v podkroví (3.NP) sádrová stříkaná omítka, nebo sjednotit na vápenocementovou?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Otlučení stávajících vnitřních omítek (S01/S02/S03)</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Karle: otloukají se vnitřní omítky kompletně, nebo zůstávají soudržné části? Pokud bourat → doplníme m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>S05 betonová deska 1.NP — 120 mm (skladba) vs 150 mm (statika/items)</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>Projektante/statiku: potvrdit tl. ŽB desky 1.NP (120 vs 150 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -8383,7 +8383,7 @@
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.PSV71.001</t>
+          <t>260219_dum.PSV71.101</t>
         </is>
       </c>
       <c r="J7" s="18" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.PSV71.002</t>
+          <t>260219_dum.PSV71.102</t>
         </is>
       </c>
       <c r="J8" s="18" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.101</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr"/>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.102</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr"/>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003 → PSV76.003a</t>
+          <t>260219_dum.PSV76.103 → PSV76.103a</t>
         </is>
       </c>
       <c r="J50" s="15" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003 → PSV76.003b</t>
+          <t>260219_dum.PSV76.103 → PSV76.103b</t>
         </is>
       </c>
       <c r="J51" s="15" t="inlineStr"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.104</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.301</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002 → PSV76.002a</t>
+          <t>260219_dum.PSV76.302 → PSV76.302a</t>
         </is>
       </c>
       <c r="J55" s="15" t="inlineStr"/>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002 → PSV76.002b</t>
+          <t>260219_dum.PSV76.302 → PSV76.302b</t>
         </is>
       </c>
       <c r="J56" s="15" t="inlineStr"/>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.201</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.202</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr"/>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.203</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.204</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr"/>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.101</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr"/>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.102</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.003</t>
+          <t>260219_dum.VRN.103</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr"/>
@@ -13928,7 +13928,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.201</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr"/>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.301</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr"/>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.302</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.401</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr"/>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.402</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.501</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.601</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.701</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.801</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr"/>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.001</t>
+          <t>260217_sklad.VRN.101</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr"/>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.001</t>
+          <t>260217_sklad.VRN.201</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr"/>
@@ -16647,7 +16647,7 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.103</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -16673,14 +16673,14 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>PSV76.003a, PSV76.003b</t>
+          <t>PSV76.103a, PSV76.103b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.302</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>PSV76.002a, PSV76.002b</t>
+          <t>PSV76.302a, PSV76.302b</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -708,247 +708,247 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -958,289 +958,289 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>VRN — Revize</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
-        </is>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>✓ verified (leaf ověřen)</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>166</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (leaf z ÚRS online)</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>58</v>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>✓ verified (leaf ověřen)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (leaf z ÚRS online)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="B54" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>• PRÁCE JE KOMPLETNÍ bez ohledu na stav kódu — seznam (postup prací) = primary deliverable. Code = secondary, doplní se v ÚRS online / KROS.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Família</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Počet ops</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -1250,37 +1250,37 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -1290,37 +1290,37 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -1330,37 +1330,37 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -1370,7 +1370,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
@@ -1380,37 +1380,37 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -1420,7 +1420,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -1430,7 +1430,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1440,7 +1440,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1450,7 +1450,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -1460,7 +1460,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -1470,7 +1470,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -1480,37 +1480,37 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -1520,7 +1520,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -1530,7 +1530,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,7 +1590,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -1600,7 +1600,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -1610,85 +1610,115 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
-        </is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>METODIKA + PATTERN COMPLIANCE</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
           <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A121:C121"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8098,7 +8128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12924,7 +12954,7 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-95 Detekce požární  (2 atomic operací) ━━</t>
+          <t>━━ PSV-95 Detekce požární  (3 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B106" s="9" t="n"/>
@@ -13037,70 +13067,65 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>━━ M-21 ELI silnoproud  (7 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="n"/>
-      <c r="C109" s="9" t="n"/>
-      <c r="D109" s="9" t="n"/>
-      <c r="E109" s="9" t="n"/>
-      <c r="F109" s="9" t="n"/>
-      <c r="G109" s="9" t="n"/>
-      <c r="H109" s="9" t="n"/>
-      <c r="I109" s="9" t="n"/>
-      <c r="J109" s="9" t="n"/>
-      <c r="K109" s="9" t="n"/>
+      <c r="A109" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>PSV-95 Detekce požární</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="18">
+        <f> 1 soubor</f>
+        <v/>
+      </c>
+      <c r="G109" s="18" t="inlineStr"/>
+      <c r="H109" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV95.003 → PSV95.003a</t>
+        </is>
+      </c>
+      <c r="J109" s="18" t="inlineStr"/>
+      <c r="K109" s="18" t="inlineStr">
+        <is>
+          <t>PBŘ. Revize spalin NEDUBLOVAT (PSV73.007).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="B110" s="11" t="inlineStr">
-        <is>
-          <t>M-21 ELI silnoproud</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="11" t="inlineStr">
-        <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
-        </is>
-      </c>
-      <c r="G110" s="11" t="inlineStr">
-        <is>
-          <t>210010011</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I110" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.M21.001</t>
-        </is>
-      </c>
-      <c r="J110" s="11" t="inlineStr"/>
-      <c r="K110" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>━━ M-21 ELI silnoproud  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="9" t="n"/>
+      <c r="H110" s="9" t="n"/>
+      <c r="I110" s="9" t="n"/>
+      <c r="J110" s="9" t="n"/>
+      <c r="K110" s="9" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="n">
@@ -13113,25 +13138,25 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
@@ -13141,7 +13166,7 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.002</t>
+          <t>260219_dum.M21.001</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -13162,25 +13187,25 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -13190,7 +13215,7 @@
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.003</t>
+          <t>260219_dum.M21.002</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr"/>
@@ -13211,25 +13236,25 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -13239,7 +13264,7 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.004</t>
+          <t>260219_dum.M21.003</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -13260,7 +13285,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -13269,16 +13294,16 @@
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -13288,7 +13313,7 @@
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.005</t>
+          <t>260219_dum.M21.004</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr"/>
@@ -13309,25 +13334,25 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -13337,7 +13362,7 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.006</t>
+          <t>260219_dum.M21.005</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr"/>
@@ -13358,7 +13383,7 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -13371,12 +13396,12 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
@@ -13386,13 +13411,150 @@
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.M21.007</t>
+          <t>260219_dum.M21.006</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr"/>
       <c r="K116" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>996019011</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.M21.007</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr"/>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="18">
+        <f> 1 soubor</f>
+        <v/>
+      </c>
+      <c r="G118" s="18" t="inlineStr"/>
+      <c r="H118" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.M21.008 → M21.008a</t>
+        </is>
+      </c>
+      <c r="J118" s="18" t="inlineStr"/>
+      <c r="K118" s="18" t="inlineStr">
+        <is>
+          <t>PBŘ 16.05.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="18">
+        <f> 1 soubor</f>
+        <v/>
+      </c>
+      <c r="G119" s="18" t="inlineStr"/>
+      <c r="H119" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.M21.008 → M21.008b</t>
+        </is>
+      </c>
+      <c r="J119" s="18" t="inlineStr"/>
+      <c r="K119" s="18" t="inlineStr">
+        <is>
+          <t>PBŘ 16.06.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -13402,10 +13564,10 @@
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A53:K53"/>
     <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A109:K109"/>
     <mergeCell ref="A57:K57"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A110:K110"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="A85:K85"/>
     <mergeCell ref="A75:K75"/>
@@ -14581,7 +14743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15931,7 +16093,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
+          <t>━━ PSV-76 Zámečnictví  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B31" s="9" t="n"/>
@@ -15951,26 +16113,25 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E32" s="19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F32" s="18">
+        <f> 1 brána</f>
+        <v/>
       </c>
       <c r="G32" s="18" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
@@ -15980,24 +16141,20 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV77.001</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.PSV76.002 → PSV76.002a</t>
+        </is>
+      </c>
+      <c r="J32" s="18" t="inlineStr"/>
       <c r="K32" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dodatek PD č.1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
+          <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B33" s="9" t="n"/>
@@ -16012,119 +16169,119 @@
       <c r="K33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr"/>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV77.001</t>
+        </is>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="K34" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.001</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr"/>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>VRN — Doprava + odpad</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>997013211</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.VRN.002</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr"/>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -16132,30 +16289,30 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -16165,7 +16322,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.101</t>
+          <t>260217_sklad.VRN.002</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr"/>
@@ -16178,7 +16335,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
+          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B38" s="9" t="n"/>
@@ -16198,17 +16355,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
@@ -16216,12 +16373,12 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -16231,7 +16388,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.201</t>
+          <t>260217_sklad.VRN.101</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr"/>
@@ -16241,16 +16398,292 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.201</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Komunikace + vjezd  (3 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr"/>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002a</t>
+        </is>
+      </c>
+      <c r="J43" s="18" t="inlineStr"/>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>Dlažba (Dodatek PD č.1).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr"/>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
+        </is>
+      </c>
+      <c r="J44" s="18" t="inlineStr"/>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr"/>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr"/>
+      <c r="K45" s="18" t="inlineStr">
+        <is>
+          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="18">
+        <f> 1 soubor</f>
+        <v/>
+      </c>
+      <c r="G47" s="18" t="inlineStr"/>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.003 → VRN.003a</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr"/>
+      <c r="K47" s="18" t="inlineStr">
+        <is>
+          <t>DI PČR.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <mergeCells count="10">
+  <mergeCells count="13">
+    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A27:K27"/>
     <mergeCell ref="A31:K31"/>
@@ -16265,7 +16698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17494,6 +17927,202 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťov</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>HSV5.002a, HSV5.002b, HSV5.002c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.002</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnictví</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>PSV76.002a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.003</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>VRN.003a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.M24.001</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>M-24 VZT</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>M24.001a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.M21.008</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>M21.008a, M21.008b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV95.003</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>PSV-95 Detekce požární</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá </t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>PSV95.003a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17505,7 +18134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17800,27 +18429,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Rozpor v B zprávě — systém vytápění (TČ vzduch-vzduch vs vzduch/voda)</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: potvrďte systém vytápění — TČ vzduch-vzduch (multisplit, bez otopné vody) NEBO TČ vzduch/voda (radiátory/podlahovka)? Ovlivní PSV73 + rozvody.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53">
@@ -1490,7 +1490,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -1500,17 +1500,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -1520,7 +1520,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -1530,7 +1530,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,7 +1590,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -1600,7 +1600,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -1610,7 +1610,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -1620,7 +1620,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -1630,7 +1630,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -1731,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6468,7 +6468,7 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-6 Bourací práce  (18 atomic operací) ━━</t>
+          <t>━━ HSV-6 Bourací práce  (17 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B98" s="9" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -6937,16 +6937,16 @@
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.010</t>
+          <t>260219_dum.HSV6.011</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr"/>
@@ -6977,25 +6977,25 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>12</v>
+        <v>56.5</v>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.011</t>
+          <t>260219_dum.HSV6.012</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr"/>
@@ -7026,35 +7026,35 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>56.5</v>
+        <v>16</v>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
-        </is>
-      </c>
-      <c r="G110" s="11" t="inlineStr">
-        <is>
-          <t>997013501</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+        </is>
+      </c>
+      <c r="G110" s="13" t="inlineStr">
+        <is>
+          <t>978013181</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.012</t>
+          <t>260219_dum.HSV6.013</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr"/>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -7084,11 +7084,11 @@
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.013</t>
+          <t>260219_dum.HSV6.014</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr"/>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -7133,26 +7133,26 @@
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
-        </is>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
-        <is>
-          <t>978013181</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>968072456</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.014</t>
+          <t>260219_dum.HSV6.015</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr"/>
@@ -7173,25 +7173,25 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>15</v>
+        <v>0.6</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
-        </is>
-      </c>
-      <c r="G113" s="11" t="inlineStr">
-        <is>
-          <t>968072456</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>962024141</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.015</t>
+          <t>260219_dum.HSV6.016</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr"/>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -7231,16 +7231,16 @@
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.016</t>
+          <t>260219_dum.HSV6.017</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr"/>
@@ -7261,169 +7261,172 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="n">
+      <c r="A115" s="17" t="n">
         <v>108</v>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B115" s="18" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="C115" s="11" t="inlineStr">
-        <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
-        </is>
-      </c>
-      <c r="D115" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F115" s="11" t="inlineStr">
-        <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
-        </is>
-      </c>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>961044111</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I115" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV6.017</t>
-        </is>
-      </c>
-      <c r="J115" s="11" t="inlineStr"/>
-      <c r="K115" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="17" t="n">
-        <v>109</v>
-      </c>
-      <c r="B116" s="18" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
+      <c r="C115" s="18" t="inlineStr">
         <is>
           <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
         </is>
       </c>
-      <c r="D116" s="17" t="inlineStr">
+      <c r="D115" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E116" s="19" t="n">
+      <c r="E115" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="F116" s="18">
+      <c r="F115" s="18">
         <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
         <v/>
       </c>
-      <c r="G116" s="18" t="inlineStr"/>
-      <c r="H116" s="17" t="inlineStr">
+      <c r="G115" s="18" t="inlineStr"/>
+      <c r="H115" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I116" s="18" t="inlineStr">
+      <c r="I115" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV6.018 → HSV6.018a</t>
         </is>
       </c>
-      <c r="J116" s="18" t="inlineStr">
+      <c r="J115" s="18" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="K116" s="18" t="inlineStr">
+      <c r="K115" s="18" t="inlineStr">
         <is>
           <t>Bourání.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="9" t="n"/>
+      <c r="H116" s="9" t="n"/>
+      <c r="I116" s="9" t="n"/>
+      <c r="J116" s="9" t="n"/>
+      <c r="K116" s="9" t="n"/>
+    </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="n"/>
-      <c r="C117" s="9" t="n"/>
-      <c r="D117" s="9" t="n"/>
-      <c r="E117" s="9" t="n"/>
-      <c r="F117" s="9" t="n"/>
-      <c r="G117" s="9" t="n"/>
-      <c r="H117" s="9" t="n"/>
-      <c r="I117" s="9" t="n"/>
-      <c r="J117" s="9" t="n"/>
-      <c r="K117" s="9" t="n"/>
+      <c r="A117" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>622401110</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.001</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="n">
+      <c r="A118" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B118" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr">
-        <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="E118" s="16" t="n">
         <v>276.7</v>
       </c>
-      <c r="F118" s="11" t="inlineStr">
-        <is>
-          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
-        </is>
-      </c>
-      <c r="G118" s="11" t="inlineStr">
-        <is>
-          <t>622401110</t>
-        </is>
-      </c>
-      <c r="H118" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I118" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.001</t>
-        </is>
-      </c>
-      <c r="J118" s="11" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="K118" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+      <c r="F118" s="15">
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
+        <v/>
+      </c>
+      <c r="G118" s="15" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I118" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.002 → HSV7.002a</t>
+        </is>
+      </c>
+      <c r="J118" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K118" s="15" t="inlineStr">
+        <is>
+          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7441,7 @@
       </c>
       <c r="C119" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
@@ -7450,12 +7453,12 @@
         <v>276.7</v>
       </c>
       <c r="F119" s="15">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
+        <f> HSV7.002 plocha 276.7 m²</f>
         <v/>
       </c>
       <c r="G119" s="15" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr">
@@ -7465,7 +7468,7 @@
       </c>
       <c r="I119" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.002 → HSV7.002a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002b</t>
         </is>
       </c>
       <c r="J119" s="15" t="inlineStr">
@@ -7475,7 +7478,7 @@
       </c>
       <c r="K119" s="15" t="inlineStr">
         <is>
-          <t>Lepení+kotvení EPS (713/622 família). Leaf dle tl. 160 mm — verify.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7493,7 @@
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
@@ -7499,15 +7502,15 @@
         </is>
       </c>
       <c r="E120" s="16" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="F120" s="15">
-        <f> HSV7.002 plocha 276.7 m²</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr">
@@ -7517,17 +7520,17 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.002 → HSV7.002b</t>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
       <c r="J120" s="15" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K120" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7545,7 @@
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
@@ -7559,7 +7562,7 @@
       </c>
       <c r="G121" s="15" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>781</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr">
@@ -7569,7 +7572,7 @@
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
         </is>
       </c>
       <c r="J121" s="15" t="inlineStr">
@@ -7579,7 +7582,7 @@
       </c>
       <c r="K121" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7594,24 +7597,24 @@
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E122" s="16" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="F122" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
         <v/>
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr">
@@ -7621,17 +7624,17 @@
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
         </is>
       </c>
       <c r="J122" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K122" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7649,7 @@
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
@@ -7658,84 +7661,85 @@
         <v>82.2</v>
       </c>
       <c r="F123" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
-        <v/>
-      </c>
-      <c r="G123" s="15" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="H123" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
-        </is>
-      </c>
-      <c r="J123" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K123" s="15" t="inlineStr">
-        <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="inlineStr">
-        <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
-        </is>
-      </c>
-      <c r="D124" s="14" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="F124" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G124" s="15" t="inlineStr">
+      <c r="G123" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H124" s="14" t="inlineStr">
+      <c r="H123" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I124" s="15" t="inlineStr">
+      <c r="I123" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J124" s="15" t="inlineStr">
+      <c r="J123" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K124" s="15" t="inlineStr">
+      <c r="K123" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>622221221</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.005</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -7750,25 +7754,25 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
-        <v>1</v>
+        <v>290.2</v>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
-        </is>
-      </c>
-      <c r="G125" s="11" t="inlineStr">
-        <is>
-          <t>622221221</t>
+          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>622521111</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
@@ -7778,12 +7782,12 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.005</t>
+          <t>260219_dum.HSV7.006</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01, S12a, S12b</t>
         </is>
       </c>
       <c r="K125" s="11" t="inlineStr">
@@ -7793,74 +7797,69 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda + zateplení  (5 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="9" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="9" t="n"/>
+      <c r="G126" s="9" t="n"/>
+      <c r="H126" s="9" t="n"/>
+      <c r="I126" s="9" t="n"/>
+      <c r="J126" s="9" t="n"/>
+      <c r="K126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="n">
         <v>118</v>
       </c>
-      <c r="B126" s="11" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="inlineStr">
-        <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E126" s="12" t="n">
-        <v>290.2</v>
-      </c>
-      <c r="F126" s="11" t="inlineStr">
-        <is>
-          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
-        </is>
-      </c>
-      <c r="G126" s="13" t="inlineStr">
-        <is>
-          <t>622521111</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.006</t>
-        </is>
-      </c>
-      <c r="J126" s="11" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
-      <c r="K126" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda + zateplení  (5 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="n"/>
-      <c r="C127" s="9" t="n"/>
-      <c r="D127" s="9" t="n"/>
-      <c r="E127" s="9" t="n"/>
-      <c r="F127" s="9" t="n"/>
-      <c r="G127" s="9" t="n"/>
-      <c r="H127" s="9" t="n"/>
-      <c r="I127" s="9" t="n"/>
-      <c r="J127" s="9" t="n"/>
-      <c r="K127" s="9" t="n"/>
+      <c r="E127" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F127" s="18">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G127" s="18" t="inlineStr"/>
+      <c r="H127" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I127" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.007 → HSV7.007a</t>
+        </is>
+      </c>
+      <c r="J127" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K127" s="18" t="inlineStr">
+        <is>
+          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="n">
@@ -7873,7 +7872,7 @@
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -7882,10 +7881,10 @@
         </is>
       </c>
       <c r="E128" s="19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F128" s="18">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
       <c r="G128" s="18" t="inlineStr"/>
@@ -7896,7 +7895,7 @@
       </c>
       <c r="I128" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.007 → HSV7.007a</t>
+          <t>260219_dum.HSV7.007 → HSV7.007b</t>
         </is>
       </c>
       <c r="J128" s="18" t="inlineStr">
@@ -7906,7 +7905,7 @@
       </c>
       <c r="K128" s="18" t="inlineStr">
         <is>
-          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7920,7 @@
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
         </is>
       </c>
       <c r="D129" s="17" t="inlineStr">
@@ -7930,10 +7929,10 @@
         </is>
       </c>
       <c r="E129" s="19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F129" s="18">
-        <f> 23 × 1.05</f>
+        <f> 23 × 1.10</f>
         <v/>
       </c>
       <c r="G129" s="18" t="inlineStr"/>
@@ -7944,7 +7943,7 @@
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.007 → HSV7.007b</t>
+          <t>260219_dum.HSV7.008 → HSV7.008a</t>
         </is>
       </c>
       <c r="J129" s="18" t="inlineStr">
@@ -7954,7 +7953,7 @@
       </c>
       <c r="K129" s="18" t="inlineStr">
         <is>
-          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7968,7 @@
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
-          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
@@ -7978,10 +7977,10 @@
         </is>
       </c>
       <c r="E130" s="19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F130" s="18">
-        <f> 23 × 1.10</f>
+        <f> 23 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="G130" s="18" t="inlineStr"/>
@@ -7992,7 +7991,7 @@
       </c>
       <c r="I130" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.008 → HSV7.008a</t>
+          <t>260219_dum.HSV7.009 → HSV7.009a</t>
         </is>
       </c>
       <c r="J130" s="18" t="inlineStr">
@@ -8002,105 +8001,57 @@
       </c>
       <c r="K130" s="18" t="inlineStr">
         <is>
-          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Rošt.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="17" t="n">
+      <c r="A131" s="14" t="n">
         <v>122</v>
       </c>
-      <c r="B131" s="18" t="inlineStr">
+      <c r="B131" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
-        </is>
-      </c>
-      <c r="D131" s="17" t="inlineStr">
+      <c r="C131" s="15" t="inlineStr">
+        <is>
+          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E131" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F131" s="18">
-        <f> 23 (OVĚŘIT)</f>
-        <v/>
-      </c>
-      <c r="G131" s="18" t="inlineStr"/>
-      <c r="H131" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I131" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.009 → HSV7.009a</t>
-        </is>
-      </c>
-      <c r="J131" s="18" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="K131" s="18" t="inlineStr">
-        <is>
-          <t>Rošt.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="14" t="n">
-        <v>123</v>
-      </c>
-      <c r="B132" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda + zateplení</t>
-        </is>
-      </c>
-      <c r="C132" s="15" t="inlineStr">
-        <is>
-          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
-        </is>
-      </c>
-      <c r="D132" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E132" s="16" t="n">
+      <c r="E131" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="F132" s="15">
+      <c r="F131" s="15">
         <f> 23 × 1.05</f>
         <v/>
       </c>
-      <c r="G132" s="15" t="inlineStr">
+      <c r="G131" s="15" t="inlineStr">
         <is>
           <t>781</t>
         </is>
       </c>
-      <c r="H132" s="14" t="inlineStr">
+      <c r="H131" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I132" s="15" t="inlineStr">
+      <c r="I131" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.009 → HSV7.009b</t>
         </is>
       </c>
-      <c r="J132" s="15" t="inlineStr">
+      <c r="J131" s="15" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="K132" s="15" t="inlineStr">
+      <c r="K131" s="15" t="inlineStr">
         <is>
           <t>Obklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
@@ -8110,13 +8061,13 @@
   <autoFilter ref="A1:K1"/>
   <mergeCells count="8">
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A127:K127"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A117:K117"/>
     <mergeCell ref="A98:K98"/>
     <mergeCell ref="A68:K68"/>
     <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A116:K116"/>
     <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A126:K126"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18134,7 +18085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18454,27 +18405,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Sklad výkop — svahovaná jáma 1:0,5 v prudkém svahu (hloubka &gt;2 m)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Statiku/projektante: potvrďte, že objem výkopu skladu počítá se svahováním 1:0,5 + je dostupný prostor pro svah v prudkém svahu; pažení jen rýhy přípojek dle BOZP?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -1220,7 +1220,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1230,7 +1230,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -1240,17 +1240,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -1731,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7311,7 +7311,7 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-7 Fasáda ETICS  (9 atomic operací) ━━</t>
+          <t>━━ HSV-7 Fasáda ETICS  (10 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B116" s="9" t="n"/>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C119" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+          <t>Armovací vrstva ETICS — lepicí/stěrková hmota (zatírací) + vmáčknutí tkaniny</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K119" s="15" t="inlineStr">
         <is>
-          <t>Armovací vrstva síťka+stěrka (622 família). Finální omítka je samostatně HSV7.006.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Stěrková hmota armovací vrstvy (622 família). Pletivo viz suffix c.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Výztužná síťka — sklovláknité pletivo vtlačené do tmelu, stěn (ETICS)</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
@@ -7502,35 +7502,35 @@
         </is>
       </c>
       <c r="E120" s="16" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="F120" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha 276.7 m² (přesahy v spotřebě)</f>
         <v/>
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622142001</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>⚠ família ??? (ÚRS online)</t>
+          <t>✓ verified</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+          <t>260219_dum.HSV7.002 → HSV7.002c</t>
         </is>
       </c>
       <c r="J120" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K120" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>ÚRS 622142001 — uživatelem ověřeno z KROS katalogu (Pletivo vnějších ploch sklovláknité, stěn, m²).</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G121" s="15" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>713</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
+          <t>260219_dum.HSV7.003 → HSV7.003a</t>
         </is>
       </c>
       <c r="J121" s="15" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="K121" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7597,24 +7597,24 @@
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E122" s="16" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="F122" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>781</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr">
@@ -7624,17 +7624,17 @@
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+          <t>260219_dum.HSV7.003 → HSV7.003b</t>
         </is>
       </c>
       <c r="J122" s="15" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="K122" s="15" t="inlineStr">
         <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
@@ -7661,85 +7661,84 @@
         <v>82.2</v>
       </c>
       <c r="F123" s="15">
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <v/>
+      </c>
+      <c r="G123" s="15" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
+        </is>
+      </c>
+      <c r="J123" s="15" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K123" s="15" t="inlineStr">
+        <is>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F124" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G123" s="15" t="inlineStr">
+      <c r="G124" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H123" s="14" t="inlineStr">
+      <c r="H124" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I123" s="15" t="inlineStr">
+      <c r="I124" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J123" s="15" t="inlineStr">
+      <c r="J124" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K123" s="15" t="inlineStr">
+      <c r="K124" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="10" t="n">
-        <v>116</v>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C124" s="11" t="inlineStr">
-        <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="11" t="inlineStr">
-        <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
-        </is>
-      </c>
-      <c r="G124" s="11" t="inlineStr">
-        <is>
-          <t>622221221</t>
-        </is>
-      </c>
-      <c r="H124" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I124" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.005</t>
-        </is>
-      </c>
-      <c r="J124" s="11" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K124" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
@@ -7754,112 +7753,117 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>622221221</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.005</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
           <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E125" s="12" t="n">
+      <c r="E126" s="12" t="n">
         <v>290.2</v>
       </c>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
-      <c r="G125" s="13" t="inlineStr">
+      <c r="G126" s="13" t="inlineStr">
         <is>
           <t>622521111</t>
         </is>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="H126" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I125" s="11" t="inlineStr">
+      <c r="I126" s="11" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.006</t>
         </is>
       </c>
-      <c r="J125" s="11" t="inlineStr">
+      <c r="J126" s="11" t="inlineStr">
         <is>
           <t>S01, S12a, S12b</t>
         </is>
       </c>
-      <c r="K125" s="11" t="inlineStr">
+      <c r="K126" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-7 Fasáda + zateplení  (5 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n"/>
-      <c r="C126" s="9" t="n"/>
-      <c r="D126" s="9" t="n"/>
-      <c r="E126" s="9" t="n"/>
-      <c r="F126" s="9" t="n"/>
-      <c r="G126" s="9" t="n"/>
-      <c r="H126" s="9" t="n"/>
-      <c r="I126" s="9" t="n"/>
-      <c r="J126" s="9" t="n"/>
-      <c r="K126" s="9" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="B127" s="18" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda + zateplení</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
-        </is>
-      </c>
-      <c r="D127" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E127" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F127" s="18">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
-        <v/>
-      </c>
-      <c r="G127" s="18" t="inlineStr"/>
-      <c r="H127" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I127" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.007 → HSV7.007a</t>
-        </is>
-      </c>
-      <c r="J127" s="18" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="K127" s="18" t="inlineStr">
-        <is>
-          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="9" t="n"/>
+      <c r="H127" s="9" t="n"/>
+      <c r="I127" s="9" t="n"/>
+      <c r="J127" s="9" t="n"/>
+      <c r="K127" s="9" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="17" t="n">
@@ -7872,7 +7876,7 @@
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -7881,10 +7885,10 @@
         </is>
       </c>
       <c r="E128" s="19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F128" s="18">
-        <f> 23 × 1.05</f>
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="G128" s="18" t="inlineStr"/>
@@ -7895,7 +7899,7 @@
       </c>
       <c r="I128" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.007 → HSV7.007b</t>
+          <t>260219_dum.HSV7.007 → HSV7.007a</t>
         </is>
       </c>
       <c r="J128" s="18" t="inlineStr">
@@ -7905,7 +7909,7 @@
       </c>
       <c r="K128" s="18" t="inlineStr">
         <is>
-          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
         </is>
       </c>
       <c r="D129" s="17" t="inlineStr">
@@ -7929,10 +7933,10 @@
         </is>
       </c>
       <c r="E129" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F129" s="18">
-        <f> 23 × 1.10</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
       <c r="G129" s="18" t="inlineStr"/>
@@ -7943,7 +7947,7 @@
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.008 → HSV7.008a</t>
+          <t>260219_dum.HSV7.007 → HSV7.007b</t>
         </is>
       </c>
       <c r="J129" s="18" t="inlineStr">
@@ -7953,7 +7957,7 @@
       </c>
       <c r="K129" s="18" t="inlineStr">
         <is>
-          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7968,90 +7972,138 @@
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="F130" s="18">
+        <f> 23 × 1.10</f>
+        <v/>
+      </c>
+      <c r="G130" s="18" t="inlineStr"/>
+      <c r="H130" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.008 → HSV7.008a</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K130" s="18" t="inlineStr">
+        <is>
+          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
           <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
         </is>
       </c>
-      <c r="D130" s="17" t="inlineStr">
+      <c r="D131" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E130" s="19" t="n">
+      <c r="E131" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="F130" s="18">
+      <c r="F131" s="18">
         <f> 23 (OVĚŘIT)</f>
         <v/>
       </c>
-      <c r="G130" s="18" t="inlineStr"/>
-      <c r="H130" s="17" t="inlineStr">
+      <c r="G131" s="18" t="inlineStr"/>
+      <c r="H131" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I130" s="18" t="inlineStr">
+      <c r="I131" s="18" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.009 → HSV7.009a</t>
         </is>
       </c>
-      <c r="J130" s="18" t="inlineStr">
+      <c r="J131" s="18" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="K130" s="18" t="inlineStr">
+      <c r="K131" s="18" t="inlineStr">
         <is>
           <t>Rošt.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="14" t="n">
-        <v>122</v>
-      </c>
-      <c r="B131" s="15" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
-      <c r="C131" s="15" t="inlineStr">
+      <c r="C132" s="15" t="inlineStr">
         <is>
           <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
         </is>
       </c>
-      <c r="D131" s="14" t="inlineStr">
+      <c r="D132" s="14" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E131" s="16" t="n">
+      <c r="E132" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="F131" s="15">
+      <c r="F132" s="15">
         <f> 23 × 1.05</f>
         <v/>
       </c>
-      <c r="G131" s="15" t="inlineStr">
+      <c r="G132" s="15" t="inlineStr">
         <is>
           <t>781</t>
         </is>
       </c>
-      <c r="H131" s="14" t="inlineStr">
+      <c r="H132" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I131" s="15" t="inlineStr">
+      <c r="I132" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.009 → HSV7.009b</t>
         </is>
       </c>
-      <c r="J131" s="15" t="inlineStr">
+      <c r="J132" s="15" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="K131" s="15" t="inlineStr">
+      <c r="K132" s="15" t="inlineStr">
         <is>
           <t>Obklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
@@ -8061,13 +8113,13 @@
   <autoFilter ref="A1:K1"/>
   <mergeCells count="8">
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A127:K127"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A98:K98"/>
     <mergeCell ref="A68:K68"/>
     <mergeCell ref="A44:K44"/>
     <mergeCell ref="A116:K116"/>
     <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A126:K126"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16954,11 +17006,11 @@
         <v>276.7</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>HSV7.002a, HSV7.002b</t>
+          <t>HSV7.002a, HSV7.002b, HSV7.002c</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54">
@@ -1200,7 +1200,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -1210,17 +1210,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1240,17 +1240,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -1260,7 +1260,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -1270,7 +1270,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1731,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7311,7 +7311,7 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-7 Fasáda ETICS  (10 atomic operací) ━━</t>
+          <t>━━ HSV-7 Fasáda ETICS  (8 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B116" s="9" t="n"/>
@@ -7545,24 +7545,24 @@
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E121" s="16" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="F121" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
         <v/>
       </c>
       <c r="G121" s="15" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr">
@@ -7572,17 +7572,17 @@
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003 → HSV7.003a</t>
+          <t>260219_dum.HSV7.004 → HSV7.004a</t>
         </is>
       </c>
       <c r="J121" s="15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="K121" s="15" t="inlineStr">
         <is>
-          <t>Sokl XPS lepení + soklový profil (713/622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7597,273 +7597,265 @@
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E122" s="16" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="F122" s="15">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
-        <v/>
-      </c>
-      <c r="G122" s="15" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.003 → HSV7.003b</t>
-        </is>
-      </c>
-      <c r="J122" s="15" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="K122" s="15" t="inlineStr">
-        <is>
-          <t>Cihelný obklad spárovaný (781 família obklady).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="B123" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="inlineStr">
-        <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
-        </is>
-      </c>
-      <c r="D123" s="14" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="F123" s="15">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
-        <v/>
-      </c>
-      <c r="G123" s="15" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="H123" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.004 → HSV7.004a</t>
-        </is>
-      </c>
-      <c r="J123" s="15" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K123" s="15" t="inlineStr">
-        <is>
-          <t>Špalety EPS přesah (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="inlineStr">
-        <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
-        </is>
-      </c>
-      <c r="D124" s="14" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="F124" s="15">
         <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
-      <c r="G124" s="15" t="inlineStr">
+      <c r="G122" s="15" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="H124" s="14" t="inlineStr">
+      <c r="H122" s="14" t="inlineStr">
         <is>
           <t>⚠ família ??? (ÚRS online)</t>
         </is>
       </c>
-      <c r="I124" s="15" t="inlineStr">
+      <c r="I122" s="15" t="inlineStr">
         <is>
           <t>260219_dum.HSV7.004 → HSV7.004b</t>
         </is>
       </c>
-      <c r="J124" s="15" t="inlineStr">
+      <c r="J122" s="15" t="inlineStr">
         <is>
           <t>S01, S12a</t>
         </is>
       </c>
-      <c r="K124" s="15" t="inlineStr">
+      <c r="K122" s="15" t="inlineStr">
         <is>
           <t>Armovací vrstva + omítka špalet (622 família).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>622221221</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.005</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>ETICS fasáda 276.7 m² (sokl = keramický obklad S03, NE omítka)</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>622521111</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.006</t>
+        </is>
+      </c>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
     <row r="125">
-      <c r="A125" s="10" t="n">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-7 Fasáda + zateplení  (5 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="n"/>
+      <c r="C125" s="9" t="n"/>
+      <c r="D125" s="9" t="n"/>
+      <c r="E125" s="9" t="n"/>
+      <c r="F125" s="9" t="n"/>
+      <c r="G125" s="9" t="n"/>
+      <c r="H125" s="9" t="n"/>
+      <c r="I125" s="9" t="n"/>
+      <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="n">
         <v>117</v>
       </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr">
-        <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="E125" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
-        </is>
-      </c>
-      <c r="G125" s="11" t="inlineStr">
-        <is>
-          <t>622221221</t>
-        </is>
-      </c>
-      <c r="H125" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I125" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.005</t>
-        </is>
-      </c>
-      <c r="J125" s="11" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="K125" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="n">
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F126" s="18">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G126" s="18" t="inlineStr"/>
+      <c r="H126" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I126" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.007 → HSV7.007a</t>
+        </is>
+      </c>
+      <c r="J126" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K126" s="18" t="inlineStr">
+        <is>
+          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="n">
         <v>118</v>
       </c>
-      <c r="B126" s="11" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="inlineStr">
-        <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E126" s="12" t="n">
-        <v>290.2</v>
-      </c>
-      <c r="F126" s="11" t="inlineStr">
-        <is>
-          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
-        </is>
-      </c>
-      <c r="G126" s="13" t="inlineStr">
-        <is>
-          <t>622521111</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.006</t>
-        </is>
-      </c>
-      <c r="J126" s="11" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
-      <c r="K126" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-7 Fasáda + zateplení  (5 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="n"/>
-      <c r="C127" s="9" t="n"/>
-      <c r="D127" s="9" t="n"/>
-      <c r="E127" s="9" t="n"/>
-      <c r="F127" s="9" t="n"/>
-      <c r="G127" s="9" t="n"/>
-      <c r="H127" s="9" t="n"/>
-      <c r="I127" s="9" t="n"/>
-      <c r="J127" s="9" t="n"/>
-      <c r="K127" s="9" t="n"/>
+      <c r="E127" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F127" s="18">
+        <f> 23 × 1.05</f>
+        <v/>
+      </c>
+      <c r="G127" s="18" t="inlineStr"/>
+      <c r="H127" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I127" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.007 → HSV7.007b</t>
+        </is>
+      </c>
+      <c r="J127" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K127" s="18" t="inlineStr">
+        <is>
+          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="n">
@@ -7876,7 +7868,7 @@
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -7885,10 +7877,10 @@
         </is>
       </c>
       <c r="E128" s="19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F128" s="18">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> 23 × 1.10</f>
         <v/>
       </c>
       <c r="G128" s="18" t="inlineStr"/>
@@ -7899,7 +7891,7 @@
       </c>
       <c r="I128" s="18" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.007 → HSV7.007a</t>
+          <t>260219_dum.HSV7.008 → HSV7.008a</t>
         </is>
       </c>
       <c r="J128" s="18" t="inlineStr">
@@ -7909,7 +7901,7 @@
       </c>
       <c r="K128" s="18" t="inlineStr">
         <is>
-          <t>Montáž.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7916,7 @@
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
         </is>
       </c>
       <c r="D129" s="17" t="inlineStr">
@@ -7933,177 +7925,81 @@
         </is>
       </c>
       <c r="E129" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F129" s="18">
+        <f> 23 (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G129" s="18" t="inlineStr"/>
+      <c r="H129" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I129" s="18" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.009 → HSV7.009a</t>
+        </is>
+      </c>
+      <c r="J129" s="18" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="K129" s="18" t="inlineStr">
+        <is>
+          <t>Rošt.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda + zateplení</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="F129" s="18">
+      <c r="F130" s="15">
         <f> 23 × 1.05</f>
         <v/>
       </c>
-      <c r="G129" s="18" t="inlineStr"/>
-      <c r="H129" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I129" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.007 → HSV7.007b</t>
-        </is>
-      </c>
-      <c r="J129" s="18" t="inlineStr">
+      <c r="G130" s="15" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (ÚRS online)</t>
+        </is>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.009 → HSV7.009b</t>
+        </is>
+      </c>
+      <c r="J130" s="15" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
-      <c r="K129" s="18" t="inlineStr">
-        <is>
-          <t>Materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="17" t="n">
-        <v>121</v>
-      </c>
-      <c r="B130" s="18" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda + zateplení</t>
-        </is>
-      </c>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
-        </is>
-      </c>
-      <c r="D130" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E130" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="F130" s="18">
-        <f> 23 × 1.10</f>
-        <v/>
-      </c>
-      <c r="G130" s="18" t="inlineStr"/>
-      <c r="H130" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I130" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.008 → HSV7.008a</t>
-        </is>
-      </c>
-      <c r="J130" s="18" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="K130" s="18" t="inlineStr">
-        <is>
-          <t>Montáž+materiál.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="17" t="n">
-        <v>122</v>
-      </c>
-      <c r="B131" s="18" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda + zateplení</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
-        </is>
-      </c>
-      <c r="D131" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E131" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F131" s="18">
-        <f> 23 (OVĚŘIT)</f>
-        <v/>
-      </c>
-      <c r="G131" s="18" t="inlineStr"/>
-      <c r="H131" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I131" s="18" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.009 → HSV7.009a</t>
-        </is>
-      </c>
-      <c r="J131" s="18" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="K131" s="18" t="inlineStr">
-        <is>
-          <t>Rošt.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="14" t="n">
-        <v>123</v>
-      </c>
-      <c r="B132" s="15" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda + zateplení</t>
-        </is>
-      </c>
-      <c r="C132" s="15" t="inlineStr">
-        <is>
-          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
-        </is>
-      </c>
-      <c r="D132" s="14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="F132" s="15">
-        <f> 23 × 1.05</f>
-        <v/>
-      </c>
-      <c r="G132" s="15" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="H132" s="14" t="inlineStr">
-        <is>
-          <t>⚠ família ??? (ÚRS online)</t>
-        </is>
-      </c>
-      <c r="I132" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.HSV7.009 → HSV7.009b</t>
-        </is>
-      </c>
-      <c r="J132" s="15" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="K132" s="15" t="inlineStr">
+      <c r="K130" s="15" t="inlineStr">
         <is>
           <t>Obklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
@@ -8113,7 +8009,7 @@
   <autoFilter ref="A1:K1"/>
   <mergeCells count="8">
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A127:K127"/>
+    <mergeCell ref="A125:K125"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A98:K98"/>
     <mergeCell ref="A68:K68"/>
@@ -16701,7 +16597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17017,7 +16913,7 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.003</t>
+          <t>260219_dum.HSV7.004</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -17027,40 +16923,40 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>HSV7.003a, HSV7.003b</t>
+          <t>HSV7.004a, HSV7.004b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.004</t>
+          <t>260219_dum.PSV76.103</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -17069,64 +16965,64 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>82.2</v>
+        <v>43.5</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>HSV7.004a, HSV7.004b</t>
+          <t>PSV76.103a, PSV76.103b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.103</t>
+          <t>260219_dum.PSV76.302</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>43.5</v>
+        <v>9.23</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>PSV76.103a, PSV76.103b</t>
+          <t>PSV76.302a, PSV76.302b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.302</t>
+          <t>260219_dum.PSV77.002</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčíc</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -17135,21 +17031,21 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>9.23</v>
+        <v>13.5</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>PSV76.302a, PSV76.302b</t>
+          <t>PSV77.002a, PSV77.002b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.002</t>
+          <t>260219_dum.PSV77.003</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -17159,7 +17055,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -17168,31 +17064,31 @@
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>PSV77.002a, PSV77.002b</t>
+          <t>PSV77.003a, PSV77.003b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV77.003</t>
+          <t>260219_dum.PSV78.001</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -17201,21 +17097,21 @@
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>32.4</v>
+        <v>78.2</v>
       </c>
       <c r="F15" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>PSV77.003a, PSV77.003b</t>
+          <t>PSV78.001a, PSV78.001b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.001</t>
+          <t>260219_dum.PSV78.002</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -17225,7 +17121,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -17234,21 +17130,21 @@
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="F16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>PSV78.001a, PSV78.001b</t>
+          <t>PSV78.002a, PSV78.002b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.002</t>
+          <t>260219_dum.PSV78.003</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -17258,7 +17154,7 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -17267,21 +17163,21 @@
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>PSV78.002a, PSV78.002b</t>
+          <t>PSV78.003a, PSV78.003b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.003</t>
+          <t>260219_dum.PSV78.004</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -17291,7 +17187,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -17300,54 +17196,54 @@
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="F18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>PSV78.003a, PSV78.003b</t>
+          <t>PSV78.004a, PSV78.004b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV78.004</t>
+          <t>260219_dum.PSV72.004</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>set</t>
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>179.1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>PSV78.004a, PSV78.004b</t>
+          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.004</t>
+          <t>260219_dum.PSV72.005</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
@@ -17357,7 +17253,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -17373,14 +17269,14 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>PSV72.004a, PSV72.004b, PSV72.004c</t>
+          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.005</t>
+          <t>260219_dum.PSV72.006</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -17390,7 +17286,7 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -17406,14 +17302,14 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>PSV72.005a, PSV72.005b, PSV72.005c</t>
+          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.006</t>
+          <t>260219_dum.PSV72.008</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
@@ -17423,129 +17319,129 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standa</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>PSV72.006a, PSV72.006b, PSV72.006c</t>
+          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.PSV72.008</t>
+          <t>260219_dum.HSV1.015</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační</t>
+          <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>PSV72.008a, PSV72.008b, PSV72.008c, PSV72.008d</t>
+          <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV1.015</t>
+          <t>260219_dum.HSV5.017</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie +</t>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorn</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>HSV1.015a, HSV1.015b, HSV1.015c</t>
+          <t>HSV5.017a, HSV5.017b, HSV5.017c, HSV5.017d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.017</t>
+          <t>260219_dum.HSV4.015</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorn</t>
+          <t>Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HSV5.017a, HSV5.017b, HSV5.017c, HSV5.017d</t>
+          <t>HSV4.015a, HSV4.015b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.015</t>
+          <t>260219_dum.HSV4.016</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
@@ -17555,7 +17451,7 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -17567,18 +17463,18 @@
         <v>59.5</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>HSV4.015a, HSV4.015b</t>
+          <t>HSV4.016a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.016</t>
+          <t>260219_dum.HSV4.017</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
@@ -17588,7 +17484,7 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
@@ -17597,21 +17493,21 @@
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>HSV4.016a</t>
+          <t>HSV4.017a, HSV4.017b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.017</t>
+          <t>260219_dum.HSV4.018</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -17621,7 +17517,7 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -17629,22 +17525,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="E28" s="16" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="E28" s="16" t="n"/>
       <c r="F28" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>HSV4.017a, HSV4.017b</t>
+          <t>HSV4.018a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.018</t>
+          <t>260219_dum.HSV4.019</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
@@ -17654,7 +17548,7 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -17668,14 +17562,14 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>HSV4.018a</t>
+          <t>HSV4.019a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.019</t>
+          <t>260219_dum.HSV4.020</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
@@ -17685,7 +17579,7 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -17699,14 +17593,14 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>HSV4.019a</t>
+          <t>HSV4.020a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.020</t>
+          <t>260219_dum.HSV4.021</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
@@ -17716,7 +17610,7 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -17730,24 +17624,24 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>HSV4.020a</t>
+          <t>HSV4.021a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV4.021</t>
+          <t>260219_dum.HSV7.007</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou +</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -17755,20 +17649,22 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="E32" s="16" t="n"/>
+      <c r="E32" s="16" t="n">
+        <v>23</v>
+      </c>
       <c r="F32" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>HSV4.021a</t>
+          <t>HSV7.007a, HSV7.007b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.007</t>
+          <t>260219_dum.HSV7.008</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
@@ -17778,7 +17674,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou +</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -17790,18 +17686,18 @@
         <v>23</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>HSV7.007a, HSV7.007b</t>
+          <t>HSV7.008a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.008</t>
+          <t>260219_dum.HSV7.009</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
@@ -17811,7 +17707,7 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -17823,28 +17719,28 @@
         <v>23</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>HSV7.008a</t>
+          <t>HSV7.009a, HSV7.009b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV7.009</t>
+          <t>260219_dum.HSV5.018</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -17853,31 +17749,31 @@
         </is>
       </c>
       <c r="E35" s="16" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>HSV7.009a, HSV7.009b</t>
+          <t>HSV5.018a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV5.018</t>
+          <t>260219_dum.HSV6.018</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -17886,31 +17782,31 @@
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="F36" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>HSV5.018a</t>
+          <t>HSV6.018a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.HSV6.018</t>
+          <t>260217_sklad.HSV5.002</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťov</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -17918,68 +17814,68 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>23</v>
-      </c>
+      <c r="E37" s="16" t="n"/>
       <c r="F37" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>HSV6.018a</t>
+          <t>HSV5.002a, HSV5.002b, HSV5.002c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV5.002</t>
+          <t>260217_sklad.PSV76.002</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťov</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="n"/>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="F38" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>HSV5.002a, HSV5.002b, HSV5.002c</t>
+          <t>PSV76.002a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV76.002</t>
+          <t>260217_sklad.VRN.003</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="E39" s="16" t="n">
@@ -17990,90 +17886,90 @@
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>PSV76.002a</t>
+          <t>VRN.003a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.003</t>
+          <t>260219_dum.M24.001</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E40" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>VRN.003a</t>
+          <t>M24.001a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.M24.001</t>
+          <t>260219_dum.M21.008</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>M-24 VZT</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="E41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="14" t="n">
-        <v>1</v>
-      </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>M24.001a</t>
+          <t>M21.008a, M21.008b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>260219_dum.M21.008</t>
+          <t>260219_dum.PSV95.003</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t xml:space="preserve">Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá </t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
@@ -18085,42 +17981,9 @@
         <v>1</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>M21.008a, M21.008b</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>260219_dum.PSV95.003</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>PSV-95 Detekce požární</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá </t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
         <is>
           <t>PSV95.003a</t>
         </is>
@@ -18137,7 +18000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18482,27 +18345,52 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Sokl — rozpor PD: TZ ARS (XPS + cihelný) vs výkres S03/pohledy (sanační Styrcon + keramický)</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: potvrďte sokl = sanační Styrcon 200 + keramický obklad (výkres), NE XPS + cihelný (TZ ARS text). + délka soklu (řadovka): plocha ≈16 nebo 23 m²?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="E115" s="19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F115" s="18">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> obvod 38.7 × 0.6 × řadovka 0.7 ≈ 16 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="G115" s="18" t="inlineStr"/>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="E126" s="19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F126" s="18">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> obvod 38.7 × 0.6 × řadovka 0.7 ≈ 16 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="G126" s="18" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="E127" s="19" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F127" s="18">
-        <f> 23 × 1.05</f>
+        <f> 16 × 1.05</f>
         <v/>
       </c>
       <c r="G127" s="18" t="inlineStr"/>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="E128" s="19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F128" s="18">
-        <f> 23 × 1.10</f>
+        <f> 16 × 1.10</f>
         <v/>
       </c>
       <c r="G128" s="18" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="E129" s="19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F129" s="18">
-        <f> 23 (OVĚŘIT)</f>
+        <f> 16 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="G129" s="18" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="E130" s="16" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F130" s="15">
-        <f> 23 × 1.05</f>
+        <f> 16 × 1.05</f>
         <v/>
       </c>
       <c r="G130" s="15" t="inlineStr">
@@ -14642,7 +14642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14948,11 +14948,11 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>podlaha sklad 21.2 m² × 0.15 m štěrku</t>
+          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -15258,11 +15258,11 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>21.2 × 0.10 = 2.12</t>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -15347,7 +15347,7 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-3 Svislé konstrukce  (3 atomic operací) ━━</t>
+          <t>━━ HSV-3 Svislé konstrukce  (6 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -15521,179 +15521,165 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F20" s="18">
+        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G20" s="18" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F21" s="18">
+        <f> 33 m² (2 vrstvy ve spotřebě)</f>
+        <v/>
+      </c>
+      <c r="G21" s="18" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004b</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>HI + protiradon (711). Materiál 2×4mm.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="F22" s="18">
+        <f> 33 × 1.10 přesahy</f>
+        <v/>
+      </c>
+      <c r="G22" s="18" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.005 → HSV3.005a</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>Drenáž nopová folie (711).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-4 Vodorovné  (6 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>rozpon 3.34 × počet stropnic (6.35/0.625 = 10) = ~10 ks × 3.34 = 33.4</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="F22" s="11">
-        <f> 21.2 m² strop skladu</f>
-        <v/>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.002</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>22.26945</v>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>21.2 × 1.05 přesah</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>712331101</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -15706,25 +15692,25 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>921</v>
+        <v>36.74</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
+          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -15734,7 +15720,7 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.004</t>
+          <t>260217_sklad.HSV4.001</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -15759,7 +15745,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -15768,16 +15754,15 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>411321515</t>
+        <v>21.209</v>
+      </c>
+      <c r="F25" s="11">
+        <f> 21.2 m² strop skladu</f>
+        <v/>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>762331110</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -15787,7 +15772,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.005</t>
+          <t>260217_sklad.HSV4.002</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -15812,429 +15797,473 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>22.26945</v>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>21.2 × 1.05 přesah</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>712331101</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.003</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>921</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>411321414</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>411321515</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.005</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
           <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>1551</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F29" s="11">
         <f> hmotnost IPE180 (921 kg) + odhad pororoštů (21 m² × 30 kg/m²) = ~1551</f>
         <v/>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>783201001</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-5 Komunikace + schodiště  (1 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>5.5</v>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>121301101</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV5.001</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>S05_sklad</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-76 Výplně otvorů  (1 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>1 ks vstupní dveře skladu</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>766682111</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.PSV76.001</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr"/>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-76 Zámečnictví  (1 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E32" s="19" t="n">
+      <c r="E35" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F35" s="18">
         <f> 1 brána</f>
         <v/>
       </c>
-      <c r="G32" s="18" t="inlineStr"/>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr"/>
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.PSV76.002 → PSV76.002a</t>
         </is>
       </c>
-      <c r="J32" s="18" t="inlineStr"/>
-      <c r="K32" s="18" t="inlineStr">
+      <c r="J35" s="18" t="inlineStr"/>
+      <c r="K35" s="18" t="inlineStr">
         <is>
           <t>Dodatek PD č.1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>PSV-77 Podlahy</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E34" s="19" t="n">
+      <c r="E37" s="19" t="n">
         <v>17.6</v>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr"/>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr"/>
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I34" s="18" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.PSV77.001</t>
         </is>
       </c>
-      <c r="J34" s="18" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>S01_sklad</t>
         </is>
       </c>
-      <c r="K34" s="18" t="inlineStr">
+      <c r="K37" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>VRN — Doprava + odpad</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>031032000</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.VRN.001</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr"/>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>VRN — Doprava + odpad</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>997013211</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.VRN.002</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
+          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B38" s="9" t="n"/>
@@ -16250,16 +16279,16 @@
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -16272,12 +16301,12 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -16287,7 +16316,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.101</t>
+          <t>260217_sklad.VRN.001</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr"/>
@@ -16298,273 +16327,388 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.002</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Standard geodet vytýčení pro nový objekt</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.101</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic — no decomposition needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>VRN — Společné</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>030001000</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.201</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr"/>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic — no decomposition needed)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-5 Komunikace + vjezd  (3 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="18" t="inlineStr">
         <is>
           <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr"/>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="G46" s="18" t="inlineStr"/>
+      <c r="H46" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV5.002 → HSV5.002a</t>
         </is>
       </c>
-      <c r="J43" s="18" t="inlineStr"/>
-      <c r="K43" s="18" t="inlineStr">
+      <c r="J46" s="18" t="inlineStr"/>
+      <c r="K46" s="18" t="inlineStr">
         <is>
           <t>Dlažba (Dodatek PD č.1).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
-      </c>
-      <c r="G44" s="18" t="inlineStr"/>
-      <c r="H44" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
-        </is>
-      </c>
-      <c r="J44" s="18" t="inlineStr"/>
-      <c r="K44" s="18" t="inlineStr">
-        <is>
-          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
-      </c>
-      <c r="G45" s="18" t="inlineStr"/>
-      <c r="H45" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
-        </is>
-      </c>
-      <c r="J45" s="18" t="inlineStr"/>
-      <c r="K45" s="18" t="inlineStr">
-        <is>
-          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr"/>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr"/>
+      <c r="K47" s="18" t="inlineStr">
+        <is>
+          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr"/>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr"/>
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
           <t>VRN — Geodet / PČR</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E47" s="19" t="n">
+      <c r="E50" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F50" s="18">
         <f> 1 soubor</f>
         <v/>
       </c>
-      <c r="G47" s="18" t="inlineStr"/>
-      <c r="H47" s="17" t="inlineStr">
+      <c r="G50" s="18" t="inlineStr"/>
+      <c r="H50" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I47" s="18" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.003 → VRN.003a</t>
         </is>
       </c>
-      <c r="J47" s="18" t="inlineStr"/>
-      <c r="K47" s="18" t="inlineStr">
+      <c r="J50" s="18" t="inlineStr"/>
+      <c r="K50" s="18" t="inlineStr">
         <is>
           <t>DI PČR.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
@@ -16573,19 +16717,19 @@
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <mergeCells count="13">
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16597,7 +16741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17650,7 +17794,7 @@
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F32" s="14" t="n">
         <v>2</v>
@@ -17683,7 +17827,7 @@
         </is>
       </c>
       <c r="E33" s="16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F33" s="14" t="n">
         <v>1</v>
@@ -17716,7 +17860,7 @@
         </is>
       </c>
       <c r="E34" s="16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F34" s="14" t="n">
         <v>2</v>
@@ -17782,7 +17926,7 @@
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F36" s="14" t="n">
         <v>1</v>
@@ -17986,6 +18130,72 @@
       <c r="G42" s="15" t="inlineStr">
         <is>
           <t>PSV95.003a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>HSV3.004a, HSV3.004b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.005</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>HSV3.005a</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -18577,7 +18577,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>odhad — výška ~1.6 m × šíře 6.35 m / blok 0.8×0.4 = ~32 bloků × 2 řady = 64; round 60</t>
+          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -18573,11 +18573,11 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² ÷ 1.08 m²/blok (H-BLOK Standard 1800×600mm líc, web-ověřeno) = 17.6 → 18 ks; layout: 4 bloky/řada × 5 řad = 20 ks (s řezy) — použito 18 ks plocha-přesné</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -18577,7 +18577,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m² ÷ 1.08 m²/blok (H-BLOK Standard 1800×600mm líc, web-ověřeno) = 17.6 → 18 ks; layout: 4 bloky/řada × 5 řad = 20 ks (s řezy) — použito 18 ks plocha-přesné</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -18573,11 +18573,11 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -18038,7 +18038,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Hloubení patek pro stojky IPE180 zastřešení parkingu, 500×500 mm × 1.0 m hl. × 7 ks</t>
+          <t>Hloubení patek pro stojky IPE180 zastřešení parkingu, 500×500 mm × 1.0 m hl. × 6 ks</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -18047,11 +18047,11 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>DXF: 7 patek × 0.5 × 0.5 × 1.0 (TZ rozteč 1000 mm × 7 m parking)</t>
+          <t>6 patek × 0.5 × 0.5 × 1.0 m hl. = 1.5 m³</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>32.1</v>
+        <v>31.85</v>
       </c>
       <c r="F8" s="18">
-        <f> součet hloubení sklad + figura + patky (25.5+4.85+1.75)</f>
+        <f> součet hloubení sklad + figura + patky (25.5+4.85+1.5)</f>
         <v/>
       </c>
       <c r="G8" s="18" t="inlineStr"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 7 ks</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -18259,11 +18259,11 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>DXF: 7 ks (rozteč 1000 mm × 7000 mm parking délka)</t>
+          <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 7 ks</t>
+          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -18308,11 +18308,11 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>7 ks (= spodní)</t>
+          <t>6 ks (= spodní, výkres D.1.1.02)</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -18357,7 +18357,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>7.21</v>
+        <v>6.18</v>
       </c>
       <c r="F13" s="18">
         <f> montáž × 1.03</f>
@@ -18401,11 +18401,11 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×7) + zídka (odhad ~1 m³)</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -19243,11 +19243,11 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>921</v>
+        <v>790</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="E33" s="19" t="n">
-        <v>948.63</v>
+        <v>813.7</v>
       </c>
       <c r="F33" s="18">
         <f> montáž × 1.03</f>
@@ -19397,11 +19397,12 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>1551</v>
-      </c>
-      <c r="F35" s="11">
-        <f> hmotnost IPE180 (921 kg) + odhad pororoštů (21 m² × 30 kg/m²) = ~1551</f>
-        <v/>
+        <v>1420</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+        </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -19449,7 +19450,7 @@
         </is>
       </c>
       <c r="E36" s="19" t="n">
-        <v>1582.02</v>
+        <v>1448.4</v>
       </c>
       <c r="F36" s="18">
         <f> montáž × 1.02</f>
@@ -20591,7 +20592,7 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 7 ks</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -20600,7 +20601,7 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>2</v>
@@ -20987,7 +20988,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -20996,7 +20997,7 @@
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>921</v>
+        <v>790</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>2</v>
@@ -21029,7 +21030,7 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>1551</v>
+        <v>1420</v>
       </c>
       <c r="F23" s="14" t="n">
         <v>2</v>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -848,57 +848,57 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -908,37 +908,37 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -948,7 +948,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -958,17 +958,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -978,17 +978,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -998,7 +998,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -1008,149 +1008,149 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B49" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>✓ verified (leaf ověřen)</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
+          <t>✓ verified (leaf ověřen)</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>165</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>⚠ família ??? (leaf z ÚRS online)</t>
+          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>56</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>⚠ família ??? (leaf z ÚRS online)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
+      <c r="B55" s="5" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>• PRÁCE JE KOMPLETNÍ bez ohledu na stav kódu — seznam (postup prací) = primary deliverable. Code = secondary, doplní se v ÚRS online / KROS.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Família</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Počet ops</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>24</v>
+        <v>124</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -1160,27 +1160,27 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1190,7 +1190,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -1200,27 +1200,27 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1230,7 +1230,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -1240,17 +1240,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -1260,7 +1260,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -1270,7 +1270,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1280,27 +1280,27 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -1310,7 +1310,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1320,17 +1320,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -1340,7 +1340,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1350,7 +1350,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -1360,27 +1360,27 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -1390,7 +1390,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -1400,7 +1400,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -1410,17 +1410,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -1430,7 +1430,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1440,7 +1440,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1450,7 +1450,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -1460,7 +1460,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -1470,7 +1470,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -1480,7 +1480,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -1490,7 +1490,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -1500,17 +1500,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -1520,7 +1520,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -1530,7 +1530,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,7 +1590,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -1600,7 +1600,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -1610,7 +1610,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -1620,7 +1620,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -1630,7 +1630,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -1640,85 +1640,95 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
           <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A60:C60"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A121:C121"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17790,7 +17800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17866,7 +17876,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-1 Zemní práce  (6 atomic operací) ━━</t>
+          <t>━━ HSV-1 Zemní práce  (8 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -18096,11 +18106,11 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
+          <t>S01 plocha 23.6 m² (místnost 17.6 + vynos za stěnu 6.0 dle řezu) × 0.15 m podkladní drť 4-8 = 3.54 m³</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -18174,210 +18184,219 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>S01 plocha 23.6 m² × 0.04 m = 0.94 m³</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>564231111</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.007</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>průřez zásypu 3.61 m² (řez A-A) × délka 6.5 m = 23.5 m³</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.008</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-2 Základové a ŽB  (7 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E12" s="19" t="n">
         <v>4.84</v>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.001</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>273313811</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.002</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>6 ks (= spodní, výkres D.1.1.02)</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>311233812</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Dvoustupňové patky pro IPE180 — horní část z t)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="F13" s="18">
-        <f> montáž × 1.03</f>
-        <v/>
-      </c>
-      <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18392,25 +18411,25 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
+          <t>6 ks (= spodní, výkres D.1.1.02)</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -18420,66 +18439,57 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV2.004</t>
+          <t>260217_sklad.HSV2.003</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr"/>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+          <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>174101101</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.005</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Dvoustupňové patky pro IPE180 — horní část z t)</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F15" s="18">
+        <f> montáž × 1.03</f>
+        <v/>
+      </c>
+      <c r="G15" s="18" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.003</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr"/>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18494,7 +18504,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -18503,16 +18513,16 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -18522,14 +18532,10 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV2.006</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.HSV2.004</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
@@ -18537,173 +18543,178 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-3 Svislé konstrukce  (8 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+      <c r="A17" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.005</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>S01_sklad, S05_sklad</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.006</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-3 Svislé konstrukce  (8 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>311233815</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.001</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>S04_sklad</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>obvod 19.4 m × výška 2.4 m = 46.6</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>311233811</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu — tvarovky ztraceného be)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F20" s="18">
-        <f> montáž 1:1</f>
-        <v/>
-      </c>
-      <c r="G20" s="18" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Pronájem.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18718,25 +18729,25 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Montáž — Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Montáž — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>1398</v>
+        <v>62.5</v>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>46.6 × 30 kg/m² = 1398</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>273361821</t>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>311233811</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -18746,7 +18757,7 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV3.003</t>
+          <t>260217_sklad.HSV3.002</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -18771,16 +18782,16 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Dodávka — Dodávka betonářské oceli B500B (Výztuž B500B do tvarovek ztraceného bednění (~)</t>
+          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu S03a/b — tvarovky ztrace)</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E22" s="19" t="n">
-        <v>1398</v>
+        <v>62.5</v>
       </c>
       <c r="F22" s="18">
         <f> montáž 1:1</f>
@@ -18794,65 +18805,70 @@
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
+          <t>260217_sklad.HSV3.002</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Pronájem.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Montáž — Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
           <t>260217_sklad.HSV3.003</t>
         </is>
       </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>33</v>
-      </c>
-      <c r="F23" s="18">
-        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
-        <v/>
-      </c>
-      <c r="G23" s="18" t="inlineStr"/>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S04_sklad</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
@@ -18867,19 +18883,19 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
+          <t>Dodávka — Dodávka betonářské oceli B500B (Výztuž B500B do tvarovek ztraceného bednění (~)</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E24" s="19" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="F24" s="18">
-        <f> 33 m² (2 vrstvy ve spotřebě)</f>
+        <f> montáž 1:1</f>
         <v/>
       </c>
       <c r="G24" s="18" t="inlineStr"/>
@@ -18890,17 +18906,17 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV3.004 → HSV3.004b</t>
+          <t>260217_sklad.HSV3.003</t>
         </is>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>HI + protiradon (711). Materiál 2×4mm.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18915,160 +18931,155 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
+          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F25" s="18">
+        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G25" s="18" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F26" s="18">
+        <f> 33 m² (2 vrstvy ve spotřebě)</f>
+        <v/>
+      </c>
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004b</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>HI + protiradon (711). Materiál 2×4mm.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
           <t>Drenážní nopová folie 20 mm — dodávka+montáž, stěny pod terénem (S03a+S04)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E27" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F27" s="18">
         <f> 33 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="G25" s="18" t="inlineStr"/>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I25" s="18" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.005 → HSV3.005a</t>
         </is>
       </c>
-      <c r="J25" s="18" t="inlineStr">
+      <c r="J27" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
-      <c r="K25" s="18" t="inlineStr">
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Drenáž nopová folie (711).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-4 Vodorovné  (10 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka řeziva C24 (impregnované) (Dřevěné stropnice 100/160 mm á 625 mm primární)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="F28" s="18">
-        <f> montáž × 1.10</f>
-        <v/>
-      </c>
-      <c r="G28" s="18" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -19081,145 +19092,145 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
+          <t>Montáž — Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>762341110</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.001</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka řeziva C24 (impregnované) (Dřevěné stropnice 100/160 mm á 625 mm primární)</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="F30" s="18">
+        <f> montáž × 1.10</f>
+        <v/>
+      </c>
+      <c r="G30" s="18" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.001</t>
+        </is>
+      </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
           <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>21.209</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F31" s="11">
         <f> 21.2 m² strop skladu</f>
         <v/>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>762331110</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.002</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>22.26945</v>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>21.2 × 1.05 přesah</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>712331101</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka folie/pásu (Hydroizolační střešní souvrství skladu (modifi)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F31" s="18">
-        <f> montáž × 1.10</f>
-        <v/>
-      </c>
-      <c r="G31" s="18" t="inlineStr"/>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -19234,25 +19245,25 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Montáž — Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>790</v>
+        <v>22.26945</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+          <t>21.2 × 1.05 přesah</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -19262,7 +19273,7 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.004</t>
+          <t>260217_sklad.HSV4.003</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -19287,19 +19298,19 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Sekundární zastřešení parkingu — IPE180 v rozt)</t>
+          <t>Dodávka — Dodávka folie/pásu (Hydroizolační střešní souvrství skladu (modifi)</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E33" s="19" t="n">
-        <v>813.7</v>
+        <v>24.5</v>
       </c>
       <c r="F33" s="18">
-        <f> montáž × 1.03</f>
+        <f> montáž × 1.10</f>
         <v/>
       </c>
       <c r="G33" s="18" t="inlineStr"/>
@@ -19310,7 +19321,7 @@
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.004</t>
+          <t>260217_sklad.HSV4.003</t>
         </is>
       </c>
       <c r="J33" s="18" t="inlineStr">
@@ -19320,7 +19331,7 @@
       </c>
       <c r="K33" s="18" t="inlineStr">
         <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -19335,223 +19346,254 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>790</v>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>411321414</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Sekundární zastřešení parkingu — IPE180 v rozt)</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>813.7</v>
+      </c>
+      <c r="F35" s="18">
+        <f> montáž × 1.03</f>
+        <v/>
+      </c>
+      <c r="G35" s="18" t="inlineStr"/>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K35" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
           <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E36" s="12" t="n">
         <v>44.6</v>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
         </is>
       </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>411321515</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.005</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Montáž — Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>1420</v>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>783201001</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Dodávka — Dodávka ocelových pororoštů (Žárově zinková povrchová úprava IPE180 + poror)</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E38" s="19" t="n">
         <v>1448.4</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F38" s="18">
         <f> montáž × 1.02</f>
         <v/>
       </c>
-      <c r="G36" s="18" t="inlineStr"/>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr"/>
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="J36" s="18" t="inlineStr">
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K36" s="18" t="inlineStr">
+      <c r="K38" s="18" t="inlineStr">
         <is>
           <t>Materiál (dodávka). Ztratné 2 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-5 Komunikace + schodiště  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.001</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
-      <c r="K38" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-76 Výplně otvorů  (2 atomic operací) ━━</t>
+          <t>━━ HSV-5 Komunikace + schodiště  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -19567,140 +19609,149 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
+          <t>HSV-5 Komunikace + schodiště</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>121301101</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.001</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>━━ PSV-76 Výplně otvorů  (2 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
           <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Montáž — Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>1 ks vstupní dveře skladu</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>766682111</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.PSV76.001</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr"/>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>Dodávka — Dodávka oceli S235 (válcované profily) (Bezpečnostní dveře RC3 v ocelové zárubni — vra)</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E41" s="19" t="n">
+      <c r="E43" s="19" t="n">
         <v>1.03</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F43" s="18">
         <f> montáž × 1.03</f>
         <v/>
       </c>
-      <c r="G41" s="18" t="inlineStr"/>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.PSV76.001</t>
-        </is>
-      </c>
-      <c r="J41" s="18" t="inlineStr"/>
-      <c r="K41" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>━━ PSV-76 Zámečnictví  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>PSV-76 Zámečnictví</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>Vjezdová brána ocelová — dodávka + montáž</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="18">
-        <f> 1 brána</f>
-        <v/>
-      </c>
       <c r="G43" s="18" t="inlineStr"/>
       <c r="H43" s="17" t="inlineStr">
         <is>
@@ -19709,20 +19760,20 @@
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV76.002 → PSV76.002a</t>
+          <t>260217_sklad.PSV76.001</t>
         </is>
       </c>
       <c r="J43" s="18" t="inlineStr"/>
       <c r="K43" s="18" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
+          <t>━━ PSV-76 Zámečnictví  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B44" s="9" t="n"/>
@@ -19738,30 +19789,29 @@
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E45" s="19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F45" s="18">
+        <f> 1 brána</f>
+        <v/>
       </c>
       <c r="G45" s="18" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
@@ -19771,24 +19821,20 @@
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV77.001</t>
-        </is>
-      </c>
-      <c r="J45" s="18" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.PSV76.002 → PSV76.002a</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr"/>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dodatek PD č.1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
+          <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B46" s="9" t="n"/>
@@ -19803,150 +19849,150 @@
       <c r="K46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="A47" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr"/>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV77.001</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="K47" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.001</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr"/>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>VRN — Doprava + odpad</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>997013211</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.VRN.002</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr"/>
-      <c r="K48" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n"/>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -19956,7 +20002,7 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.101</t>
+          <t>260217_sklad.VRN.002</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr"/>
@@ -19969,7 +20015,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
+          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B51" s="9" t="n"/>
@@ -19985,21 +20031,21 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
@@ -20007,12 +20053,12 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -20022,7 +20068,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.201</t>
+          <t>260217_sklad.VRN.101</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr"/>
@@ -20035,7 +20081,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-5 Komunikace + vjezd  (3 atomic operací) ━━</t>
+          <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B53" s="9" t="n"/>
@@ -20050,90 +20096,70 @@
       <c r="K53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E54" s="19" t="n"/>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="inlineStr"/>
-      <c r="H54" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I54" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002a</t>
-        </is>
-      </c>
-      <c r="J54" s="18" t="inlineStr"/>
-      <c r="K54" s="18" t="inlineStr">
-        <is>
-          <t>Dlažba (Dodatek PD č.1).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="A54" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.201</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
-      </c>
-      <c r="G55" s="18" t="inlineStr"/>
-      <c r="H55" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
-        </is>
-      </c>
-      <c r="J55" s="18" t="inlineStr"/>
-      <c r="K55" s="18" t="inlineStr">
-        <is>
-          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Komunikace + vjezd  (3 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n">
@@ -20146,18 +20172,18 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E56" s="19" t="n"/>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>neurčeno — OVĚŘIT</t>
+          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr"/>
@@ -20168,93 +20194,331 @@
       </c>
       <c r="I56" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
+          <t>260217_sklad.HSV5.002 → HSV5.002a</t>
         </is>
       </c>
       <c r="J56" s="18" t="inlineStr"/>
       <c r="K56" s="18" t="inlineStr">
         <is>
-          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dlažba (Dodatek PD č.1).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="n"/>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
-      <c r="H57" s="9" t="n"/>
-      <c r="I57" s="9" t="n"/>
-      <c r="J57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
+      <c r="A57" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr"/>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr"/>
+      <c r="K57" s="18" t="inlineStr">
+        <is>
+          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr"/>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
+        </is>
+      </c>
+      <c r="J58" s="18" t="inlineStr"/>
+      <c r="K58" s="18" t="inlineStr">
+        <is>
+          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
           <t>VRN — Geodet / PČR</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C60" s="18" t="inlineStr">
         <is>
           <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>soubor</t>
         </is>
       </c>
-      <c r="E58" s="19" t="n">
+      <c r="E60" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="18">
+      <c r="F60" s="18">
         <f> 1 soubor</f>
         <v/>
       </c>
-      <c r="G58" s="18" t="inlineStr"/>
-      <c r="H58" s="17" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr"/>
+      <c r="H60" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I58" s="18" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.003 → VRN.003a</t>
         </is>
       </c>
-      <c r="J58" s="18" t="inlineStr"/>
-      <c r="K58" s="18" t="inlineStr">
+      <c r="J60" s="18" t="inlineStr"/>
+      <c r="K60" s="18" t="inlineStr">
         <is>
           <t>DI PČR.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>━━ PSV-76 Zámečnické konstrukce  (3 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>šířka 7775 − 4000 (posuvná vrata) = 3775 mm ≈ 3.8 bm</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr"/>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.003</t>
+        </is>
+      </c>
+      <c r="J62" s="18" t="inlineStr"/>
+      <c r="K62" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>Montáž — Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>obvod části stání ≈ 18.5 bm (D.1.1.01), výška 1.0 m</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr"/>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.004</t>
+        </is>
+      </c>
+      <c r="J63" s="18" t="inlineStr"/>
+      <c r="K63" s="18" t="inlineStr">
+        <is>
+          <t>Montáž (práce).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka výrobku (Zábradlí v. 1.0 m kolem části stání — materiál)</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F64" s="18">
+        <f> montáž 1:1</f>
+        <v/>
+      </c>
+      <c r="G64" s="18" t="inlineStr"/>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.004</t>
+        </is>
+      </c>
+      <c r="J64" s="18" t="inlineStr"/>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A61:K61"/>
     <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A48:K48"/>
     <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A19:K19"/>
     <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A46:K46"/>
     <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20266,7 +20530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -20724,7 +20988,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -20733,7 +20997,7 @@
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>46.5</v>
+        <v>62.5</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>2</v>
@@ -20766,7 +21030,7 @@
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>1398</v>
+        <v>1875</v>
       </c>
       <c r="F15" s="14" t="n">
         <v>2</v>
@@ -24295,6 +24559,39 @@
       <c r="G122" s="15" t="inlineStr">
         <is>
           <t>HSV3.005a</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.004</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="inlineStr">
+        <is>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" s="15" t="inlineStr">
+        <is>
+          <t>PSV76.004a, PSV76.004b</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24679,27 +24976,102 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Zásyp za prefa opěrnou stěnou S04 — materiál neuveden v legendě</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: čím se provádí zásyp za opěrnou stěnou S04? (zemina / štěrkopísek / drť)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Oplocení (plot) u vjezdu — materiál + délka</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: materiál + výška + přesná délka oplocení u vjezdu? + specifikace sloupku u vrat?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Zábradlí stání 1.0 m — materiál</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: materiál + provedení zábradlí stání (1.0 m)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -718,197 +718,197 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>M-24 VZT</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -918,37 +918,37 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -958,7 +958,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -968,17 +968,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -988,17 +988,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -1008,7 +1008,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -1018,149 +1018,149 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
           <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B50" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>✓ verified (leaf ověřen)</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
+          <t>✓ verified (leaf ověřen)</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>167</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>⚠ família ??? (leaf z ÚRS online)</t>
+          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>56</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>⚠ família ??? (leaf z ÚRS online)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
+      <c r="B56" s="5" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>• PRÁCE JE KOMPLETNÍ bez ohledu na stav kódu — seznam (postup prací) = primary deliverable. Code = secondary, doplní se v ÚRS online / KROS.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Família</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Počet ops</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>24</v>
+        <v>129</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -1170,11 +1170,11 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
@@ -1184,23 +1184,23 @@
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -1210,37 +1210,37 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -1250,27 +1250,27 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1280,7 +1280,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -1290,7 +1290,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -1300,17 +1300,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1320,7 +1320,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -1330,17 +1330,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1350,7 +1350,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -1360,7 +1360,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -1370,7 +1370,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
@@ -1380,17 +1380,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -1400,7 +1400,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -1410,7 +1410,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -1420,17 +1420,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1440,7 +1440,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1450,7 +1450,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -1460,7 +1460,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -1470,7 +1470,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -1480,7 +1480,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -1490,7 +1490,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -1500,7 +1500,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -1510,17 +1510,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -1530,7 +1530,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,7 +1590,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -1600,7 +1600,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -1610,7 +1610,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -1620,7 +1620,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -1630,7 +1630,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -1640,7 +1640,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
@@ -1650,86 +1650,96 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>968</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
           <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A122:C122"/>
     <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17800,7 +17810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17876,7 +17886,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-1 Zemní práce  (8 atomic operací) ━━</t>
+          <t>━━ HSV-1 Zemní práce  (10 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -18286,47 +18296,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-2 Základové a ŽB  (7 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="A11" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>délka jako prefa stěna ≈ 6.35 m; Ø ~150 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.009</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E12" s="19" t="n">
-        <v>4.84</v>
+        <v>6.01</v>
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
+          <t>délka 6010 mm; Ø 120-130 mm (měřeno z řezu, nepopsáno)</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr"/>
@@ -18337,159 +18375,128 @@
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
+          <t>260217_sklad.HSV1.010</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr"/>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-2 Základové a ŽB  (7 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
           <t>260217_sklad.HSV2.001</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>273313811</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.002</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>6 ks (= spodní, výkres D.1.1.02)</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>311233812</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Dvoustupňové patky pro IPE180 — horní část z t)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="F15" s="18">
-        <f> montáž × 1.03</f>
-        <v/>
-      </c>
-      <c r="G15" s="18" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr"/>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18504,25 +18511,25 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + zídka lemující + věnec nad patkami (odhad ~1.5 m³) = ~1.75 m³</t>
+          <t>6 ks (= spodní, výkres D.1.1.02)</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -18532,66 +18539,57 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV2.004</t>
+          <t>260217_sklad.HSV2.003</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+          <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>174101101</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>✓ verified</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.005</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Dvoustupňové patky pro IPE180 — horní část z t)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F17" s="18">
+        <f> montáž × 1.03</f>
+        <v/>
+      </c>
+      <c r="G17" s="18" t="inlineStr"/>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.003</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr"/>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18604,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -18615,16 +18613,16 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -18634,14 +18632,10 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV2.006</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.HSV2.004</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
@@ -18649,173 +18643,178 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-3 Svislé konstrukce  (8 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+      <c r="A19" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.005</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>S01_sklad, S05_sklad</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.006</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-3 Svislé konstrukce  (8 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>311233815</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.001</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>S04_sklad</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>311233811</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu S03a/b — tvarovky ztrace)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F22" s="18">
-        <f> montáž 1:1</f>
-        <v/>
-      </c>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Pronájem.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18830,25 +18829,25 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Montáž — Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Montáž — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>1875</v>
+        <v>62.5</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>273361821</t>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>311233811</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -18858,7 +18857,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV3.003</t>
+          <t>260217_sklad.HSV3.002</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -18883,16 +18882,16 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Dodávka — Dodávka betonářské oceli B500B (Výztuž B500B do tvarovek ztraceného bednění (~)</t>
+          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu S03a/b — tvarovky ztrace)</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E24" s="19" t="n">
-        <v>1875</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="18">
         <f> montáž 1:1</f>
@@ -18906,65 +18905,70 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
+          <t>260217_sklad.HSV3.002</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Pronájem.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Montáž — Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
           <t>260217_sklad.HSV3.003</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="n">
-        <v>33</v>
-      </c>
-      <c r="F25" s="18">
-        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
-        <v/>
-      </c>
-      <c r="G25" s="18" t="inlineStr"/>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S04_sklad</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
@@ -18979,19 +18983,19 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
+          <t>Dodávka — Dodávka betonářské oceli B500B (Výztuž B500B do tvarovek ztraceného bednění (~)</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E26" s="19" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="F26" s="18">
-        <f> 33 m² (2 vrstvy ve spotřebě)</f>
+        <f> montáž 1:1</f>
         <v/>
       </c>
       <c r="G26" s="18" t="inlineStr"/>
@@ -19002,17 +19006,17 @@
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV3.004 → HSV3.004b</t>
+          <t>260217_sklad.HSV3.003</t>
         </is>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>HI + protiradon (711). Materiál 2×4mm.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -19027,160 +19031,155 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
+          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F27" s="18">
+        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F28" s="18">
+        <f> 33 m² (2 vrstvy ve spotřebě)</f>
+        <v/>
+      </c>
+      <c r="G28" s="18" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004b</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>HI + protiradon (711). Materiál 2×4mm.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
           <t>Drenážní nopová folie 20 mm — dodávka+montáž, stěny pod terénem (S03a+S04)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E29" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F29" s="18">
         <f> 33 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I27" s="18" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.005 → HSV3.005a</t>
         </is>
       </c>
-      <c r="J27" s="18" t="inlineStr">
+      <c r="J29" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
-      <c r="K27" s="18" t="inlineStr">
+      <c r="K29" s="18" t="inlineStr">
         <is>
           <t>Drenáž nopová folie (711).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-4 Vodorovné  (10 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka řeziva C24 (impregnované) (Dřevěné stropnice 100/160 mm á 625 mm primární)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="F30" s="18">
-        <f> montáž × 1.10</f>
-        <v/>
-      </c>
-      <c r="G30" s="18" t="inlineStr"/>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.001</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -19193,24 +19192,25 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Montáž — Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="F31" s="11">
-        <f> 21.2 m² strop skladu</f>
-        <v/>
+        <v>31</v>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
+        </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.002</t>
+          <t>260217_sklad.HSV4.001</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -19230,108 +19230,108 @@
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+          <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>22.26945</v>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>21.2 × 1.05 přesah</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>712331101</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka folie/pásu (Hydroizolační střešní souvrství skladu (modifi)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F33" s="18">
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka řeziva C24 (impregnované) (Dřevěné stropnice 100/160 mm á 625 mm primární)</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F32" s="18">
         <f> montáž × 1.10</f>
         <v/>
       </c>
-      <c r="G33" s="18" t="inlineStr"/>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr"/>
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.001</t>
+        </is>
+      </c>
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K33" s="18" t="inlineStr">
+      <c r="K32" s="18" t="inlineStr">
         <is>
           <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>762331110</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.002</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
@@ -19346,25 +19346,25 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Montáž — Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>790</v>
+        <v>19</v>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+          <t>18.1 × 1.05 přesah = 19.0 m²</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.004</t>
+          <t>260217_sklad.HSV4.003</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -19399,19 +19399,19 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Sekundární zastřešení parkingu — IPE180 v rozt)</t>
+          <t>Dodávka — Dodávka folie/pásu (Hydroizolační střešní souvrství skladu (modifi)</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E35" s="19" t="n">
-        <v>813.7</v>
+        <v>20.9</v>
       </c>
       <c r="F35" s="18">
-        <f> montáž × 1.03</f>
+        <f> montáž × 1.10</f>
         <v/>
       </c>
       <c r="G35" s="18" t="inlineStr"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV4.004</t>
+          <t>260217_sklad.HSV4.003</t>
         </is>
       </c>
       <c r="J35" s="18" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="K35" s="18" t="inlineStr">
         <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -19447,223 +19447,254 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
+          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>790</v>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>411321414</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Sekundární zastřešení parkingu — IPE180 v rozt)</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>813.7</v>
+      </c>
+      <c r="F37" s="18">
+        <f> montáž × 1.03</f>
+        <v/>
+      </c>
+      <c r="G37" s="18" t="inlineStr"/>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
           <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E38" s="12" t="n">
         <v>44.6</v>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>411321515</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.005</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Montáž — Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>1420</v>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>783201001</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Dodávka — Dodávka ocelových pororoštů (Žárově zinková povrchová úprava IPE180 + poror)</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E40" s="19" t="n">
         <v>1448.4</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F40" s="18">
         <f> montáž × 1.02</f>
         <v/>
       </c>
-      <c r="G38" s="18" t="inlineStr"/>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr"/>
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="J38" s="18" t="inlineStr">
+      <c r="J40" s="18" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K38" s="18" t="inlineStr">
+      <c r="K40" s="18" t="inlineStr">
         <is>
           <t>Materiál (dodávka). Ztratné 2 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-5 Komunikace + schodiště  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.001</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-76 Výplně otvorů  (2 atomic operací) ━━</t>
+          <t>━━ HSV-5 Komunikace + schodiště  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B41" s="9" t="n"/>
@@ -19679,140 +19710,149 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
+          <t>HSV-5 Komunikace + schodiště</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>121301101</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.001</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>━━ PSV-76 Výplně otvorů  (2 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Montáž — Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>1 ks vstupní dveře skladu</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>766682111</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.PSV76.001</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr"/>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="17" t="n">
-        <v>36</v>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>Dodávka — Dodávka oceli S235 (válcované profily) (Bezpečnostní dveře RC3 v ocelové zárubni — vra)</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="E43" s="19" t="n">
+      <c r="E45" s="19" t="n">
         <v>1.03</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F45" s="18">
         <f> montáž × 1.03</f>
         <v/>
       </c>
-      <c r="G43" s="18" t="inlineStr"/>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I43" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.PSV76.001</t>
-        </is>
-      </c>
-      <c r="J43" s="18" t="inlineStr"/>
-      <c r="K43" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>━━ PSV-76 Zámečnictví  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>PSV-76 Zámečnictví</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Vjezdová brána ocelová — dodávka + montáž</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="18">
-        <f> 1 brána</f>
-        <v/>
-      </c>
       <c r="G45" s="18" t="inlineStr"/>
       <c r="H45" s="17" t="inlineStr">
         <is>
@@ -19821,20 +19861,20 @@
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV76.002 → PSV76.002a</t>
+          <t>260217_sklad.PSV76.001</t>
         </is>
       </c>
       <c r="J45" s="18" t="inlineStr"/>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
+          <t>━━ PSV-76 Zámečnictví  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B46" s="9" t="n"/>
@@ -19850,30 +19890,29 @@
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E47" s="19" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F47" s="18">
+        <f> 1 brána</f>
+        <v/>
       </c>
       <c r="G47" s="18" t="inlineStr"/>
       <c r="H47" s="17" t="inlineStr">
@@ -19883,24 +19922,20 @@
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV77.001</t>
-        </is>
-      </c>
-      <c r="J47" s="18" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.PSV76.002 → PSV76.002a</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr"/>
       <c r="K47" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dodatek PD č.1.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
+          <t>━━ PSV-77 Podlahy  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B48" s="9" t="n"/>
@@ -19915,150 +19950,150 @@
       <c r="K48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="A49" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>plocha S01 = místnost 17.6 (legenda) + vynos za stěnu 6.0 (6010×1000 řez) = 23.6 m²</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr"/>
+      <c r="H49" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV77.001</t>
+        </is>
+      </c>
+      <c r="J49" s="18" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="K49" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>━━ VRN — Doprava + odpad  (2 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.VRN.001</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr"/>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>VRN — Doprava + odpad</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>997013211</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.VRN.002</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr"/>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
-      <c r="K51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -20068,7 +20103,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.101</t>
+          <t>260217_sklad.VRN.002</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr"/>
@@ -20081,7 +20116,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
+          <t>━━ VRN — Geodet  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B53" s="9" t="n"/>
@@ -20097,21 +20132,21 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
@@ -20119,12 +20154,12 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -20134,7 +20169,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.201</t>
+          <t>260217_sklad.VRN.101</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr"/>
@@ -20147,7 +20182,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-5 Komunikace + vjezd  (3 atomic operací) ━━</t>
+          <t>━━ VRN — Společné  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B55" s="9" t="n"/>
@@ -20162,90 +20197,70 @@
       <c r="K55" s="9" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="B56" s="18" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="18" t="inlineStr">
-        <is>
-          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
-        </is>
-      </c>
-      <c r="G56" s="18" t="inlineStr"/>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I56" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002a</t>
-        </is>
-      </c>
-      <c r="J56" s="18" t="inlineStr"/>
-      <c r="K56" s="18" t="inlineStr">
-        <is>
-          <t>Dlažba (Dodatek PD č.1).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+      <c r="A56" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.VRN.201</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="B57" s="18" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
-      </c>
-      <c r="G57" s="18" t="inlineStr"/>
-      <c r="H57" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
-        </is>
-      </c>
-      <c r="J57" s="18" t="inlineStr"/>
-      <c r="K57" s="18" t="inlineStr">
-        <is>
-          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Komunikace + vjezd  (3 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n">
@@ -20258,18 +20273,18 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E58" s="19" t="n"/>
       <c r="F58" s="18" t="inlineStr">
         <is>
-          <t>neurčeno — OVĚŘIT</t>
+          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
         </is>
       </c>
       <c r="G58" s="18" t="inlineStr"/>
@@ -20280,45 +20295,71 @@
       </c>
       <c r="I58" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
+          <t>260217_sklad.HSV5.002 → HSV5.002a</t>
         </is>
       </c>
       <c r="J58" s="18" t="inlineStr"/>
       <c r="K58" s="18" t="inlineStr">
         <is>
-          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Dlažba (Dodatek PD č.1).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="n"/>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
+      <c r="A59" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr"/>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.002 → HSV5.002b</t>
+        </is>
+      </c>
+      <c r="J59" s="18" t="inlineStr"/>
+      <c r="K59" s="18" t="inlineStr">
+        <is>
+          <t>Podklad.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -20326,12 +20367,11 @@
           <t>soubor</t>
         </is>
       </c>
-      <c r="E60" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="18">
-        <f> 1 soubor</f>
-        <v/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
       </c>
       <c r="G60" s="18" t="inlineStr"/>
       <c r="H60" s="17" t="inlineStr">
@@ -20341,20 +20381,20 @@
       </c>
       <c r="I60" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.003 → VRN.003a</t>
+          <t>260217_sklad.HSV5.002 → HSV5.002c</t>
         </is>
       </c>
       <c r="J60" s="18" t="inlineStr"/>
       <c r="K60" s="18" t="inlineStr">
         <is>
-          <t>DI PČR.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>Odvodnění dle DI PČR (ne na komunikaci).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>━━ PSV-76 Zámečnické konstrukce  (3 atomic operací) ━━</t>
+          <t>━━ VRN — Geodet / PČR  (1 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B61" s="9" t="n"/>
@@ -20370,30 +20410,29 @@
     </row>
     <row r="62">
       <c r="A62" s="17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="E62" s="19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F62" s="18" t="inlineStr">
-        <is>
-          <t>šířka 7775 − 4000 (posuvná vrata) = 3775 mm ≈ 3.8 bm</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F62" s="18">
+        <f> 1 soubor</f>
+        <v/>
       </c>
       <c r="G62" s="18" t="inlineStr"/>
       <c r="H62" s="17" t="inlineStr">
@@ -20403,60 +20442,32 @@
       </c>
       <c r="I62" s="18" t="inlineStr">
         <is>
-          <t>260217_sklad.PSV76.003</t>
+          <t>260217_sklad.VRN.003 → VRN.003a</t>
         </is>
       </c>
       <c r="J62" s="18" t="inlineStr"/>
       <c r="K62" s="18" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+          <t>DI PČR.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="n">
-        <v>48</v>
-      </c>
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>Montáž — Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>obvod části stání ≈ 18.5 bm (D.1.1.01), výška 1.0 m</t>
-        </is>
-      </c>
-      <c r="G63" s="18" t="inlineStr"/>
-      <c r="H63" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.PSV76.004</t>
-        </is>
-      </c>
-      <c r="J63" s="18" t="inlineStr"/>
-      <c r="K63" s="18" t="inlineStr">
-        <is>
-          <t>Montáž (práce).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>━━ PSV-76 Zámečnické konstrukce  (3 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="9" t="n"/>
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="9" t="n"/>
+      <c r="K63" s="9" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n">
@@ -20469,56 +20480,503 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>šířka 7775 − 4000 (posuvná vrata) = 3775 mm ≈ 3.8 bm</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr"/>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.003</t>
+        </is>
+      </c>
+      <c r="J64" s="18" t="inlineStr"/>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>Montáž — Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>obvod části stání ≈ 18.5 bm (D.1.1.01), výška 1.0 m</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr"/>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.PSV76.004</t>
+        </is>
+      </c>
+      <c r="J65" s="18" t="inlineStr"/>
+      <c r="K65" s="18" t="inlineStr">
+        <is>
+          <t>Montáž (práce).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
           <t>Dodávka — Dodávka výrobku (Zábradlí v. 1.0 m kolem části stání — materiál)</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E64" s="19" t="n">
+      <c r="E66" s="19" t="n">
         <v>18.5</v>
       </c>
-      <c r="F64" s="18">
+      <c r="F66" s="18">
         <f> montáž 1:1</f>
         <v/>
       </c>
-      <c r="G64" s="18" t="inlineStr"/>
-      <c r="H64" s="17" t="inlineStr">
+      <c r="G66" s="18" t="inlineStr"/>
+      <c r="H66" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.PSV76.004</t>
         </is>
       </c>
-      <c r="J64" s="18" t="inlineStr"/>
-      <c r="K64" s="18" t="inlineStr">
+      <c r="J66" s="18" t="inlineStr"/>
+      <c r="K66" s="18" t="inlineStr">
         <is>
           <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-5 Komunikace + zpevněné plochy  (7 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n"/>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="9" t="n"/>
+      <c r="K67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>7.0 m² × 0.04 m = 0.28 m³</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>564751111</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.003</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>7.0 m² × 0.15 m = 1.05 m³</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>564861111</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.004</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="n">
+        <v>7.775</v>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>délka po hraně dlážděné plochy = 7775 mm = 7.775 bm</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr"/>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.005</t>
+        </is>
+      </c>
+      <c r="J70" s="18" t="inlineStr"/>
+      <c r="K70" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>0.06 m² (detail) × 7.775 m = 0.47 m³</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>273321411</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.006</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>strana 6010 mm ≈ 6.0 bm</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr"/>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.007</t>
+        </is>
+      </c>
+      <c r="J72" s="18" t="inlineStr"/>
+      <c r="K72" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>plocha schodiště 5.5 m² (legenda) — podkladní deska</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>273313611</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.008</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>5.5 m² × 0.05 m kladecí beton = 0.28 m³</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr"/>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV5.009</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K74" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A61:K61"/>
     <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A50:K50"/>
     <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21195,7 +21653,7 @@
         </is>
       </c>
       <c r="E20" s="16" t="n">
-        <v>36.74</v>
+        <v>31</v>
       </c>
       <c r="F20" s="14" t="n">
         <v>2</v>
@@ -21228,7 +21686,7 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>22.26945</v>
+        <v>19</v>
       </c>
       <c r="F21" s="14" t="n">
         <v>2</v>
@@ -24313,7 +24771,7 @@
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťov</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -24321,7 +24779,9 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="E115" s="16" t="n"/>
+      <c r="E115" s="16" t="n">
+        <v>7</v>
+      </c>
       <c r="F115" s="14" t="n">
         <v>3</v>
       </c>
@@ -24606,7 +25066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25051,27 +25511,102 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Trubky u pasů — účel (drenáž vs odvětrání radonu) + Ø</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: trubky u pasů = drenáž NEBO odvětrání radonu? + jmenovitý Ø + materiál (PVC/PE flexi)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Dveřní otvor sklad — výška</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: výška dveřního otvoru skladu (RC3 dveře)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Schodiště S05 — komplet prefa s podestou vs rozložit na vrstvy</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>NEPŘIDÁNO (verify-first)</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Projektante: schodiště S05 = monolit na místě (prefa stupně + lože + deska) NEBO dodávka komplet prefa schodiště s podestou?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>PM05</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Okapový chodník + obvodová drenáž domu — NOT_IN_TZ (žádná zmínka v TZ)</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>SKIP (rekonstrukce — možná existuje)</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Volitelné: ověřit zda okapový chodník po obvodu domu je v scope (mimo BV drenáž HSV1.015). Pokud ano → HSV-1 položka.</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_ATOMIC_WORKLIST_2026-05-27.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C6" s="2">
         <f> carried 1:1 + decomposed children</f>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -718,237 +718,237 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>M-24 VZT</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -958,47 +958,47 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -1008,269 +1008,269 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>VRN — Revize</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
           <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B50" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>STAV KÓDŮ (4 tiers — práce kompletní bez ohledu na stav kódu)</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>✓ verified (leaf ověřen)</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>165</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>⚠ família ??? (leaf z ÚRS online)</t>
+          <t>✓ verified (leaf ověřen)</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>⚠ kandidát-verify (leaf generátor, neověřen)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>⚠ família ??? (leaf z ÚRS online)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
-        </is>
+      <c r="B56" s="5" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>• Kódy: leaf binding doplnit z CS ÚRS online (app.urs.cz, cenová úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>• Reconciliation consensus: HSV1.004 dvorek 596811220 · HSV1.005 terasa = podkladní skladba 564 (dlaždice ROZNÁŠECÍ POD terče, ŘEZ C-C) · dřevo 762 = PSV76.002 Truhlář · HSV2.003/008 bednění 274.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>• PRÁCE JE KOMPLETNÍ bez ohledu na stav kódu — seznam (postup prací) = primary deliverable. Code = secondary, doplní se v ÚRS online / KROS.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>URS FAMÍLIA DISTRIBUCE (54 distinct)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Família</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Počet ops</t>
         </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>14</v>
+        <v>129</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>❌ MANUAL LOOKUP — Pattern 26 honest blank (NE fabrikováno)</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>962</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -1280,37 +1280,37 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -1320,27 +1320,27 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -1350,7 +1350,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -1360,37 +1360,37 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>997</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -1400,7 +1400,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -1410,27 +1410,27 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1440,7 +1440,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -1450,7 +1450,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -1460,7 +1460,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -1470,7 +1470,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -1480,7 +1480,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -1490,7 +1490,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -1500,27 +1500,27 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>978</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -1530,7 +1530,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -1540,7 +1540,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1550,7 +1550,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -1560,7 +1560,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -1570,7 +1570,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -1580,7 +1580,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -1590,7 +1590,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -1600,7 +1600,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -1610,7 +1610,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -1620,7 +1620,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -1630,7 +1630,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>961</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -1640,86 +1640,106 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>METODIKA + PATTERN COMPLIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
+          <t>• HK212 028a..f princip: composite → atomic codeable operace (per vrstva / per fixture)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
+          <t>• Pattern 15 Work-First: atomic ops = codeable units, catalog matching downstream</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+          <t>• Pattern 26: família-level URS kde leaf neznámý + status flag; 9 BLANK ops (NE 999/TBD)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+          <t>• Pattern 28: (id, kapitola) compound key — řeší PSV76.003 ×3 + VRN.001 ×9 collisions</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
+          <t>• Pattern 32: separate deliverable — items.json frozen + File A audit NEDOTČENO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>• Traceability: každá atomic op → parent_frozen_item_id (100% coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
           <t>• Terasa ŘEZ C-C oprava: dlaždice = roznášecí vrstva POD terče (564, NE '636311 na terče'); dřevěná pochozí vrstva (762) = PSV76.002 Truhlář (split-by-trade). Plochy situace: terasa 9.23 / dvorek 16.54 m².</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A122:C122"/>
     <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17790,7 +17810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17866,7 +17886,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>━━ HSV-1 Zemní práce  (6 atomic operací) ━━</t>
+          <t>━━ HSV-1 Zemní práce  (10 atomic operací) ━━</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -18038,7 +18058,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Hloubení patek pro stojky IPE180 zastřešení parkingu, 500×500 mm × 1.0 m hl. × 7 ks</t>
+          <t>Hloubení patek pro stojky IPE180 zastřešení parkingu, 500×500 mm × 1.0 m hl. × 6 ks</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -18047,11 +18067,11 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>DXF: 7 patek × 0.5 × 0.5 × 1.0 (TZ rozteč 1000 mm × 7 m parking)</t>
+          <t>6 patek × 0.5 × 0.5 × 1.0 m hl. = 1.5 m³</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -18096,11 +18116,11 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
+          <t>S01 plocha 23.6 m² (místnost 17.6 + vynos za stěnu 6.0 dle řezu) × 0.15 m podkladní drť 4-8 = 3.54 m³</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -18149,10 +18169,10 @@
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>32.1</v>
+        <v>31.85</v>
       </c>
       <c r="F8" s="18">
-        <f> součet hloubení sklad + figura + patky (25.5+4.85+1.75)</f>
+        <f> součet hloubení sklad + figura + patky (25.5+4.85+1.5)</f>
         <v/>
       </c>
       <c r="G8" s="18" t="inlineStr"/>
@@ -18174,259 +18194,260 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>S01 plocha 23.6 m² × 0.04 m = 0.94 m³</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>564231111</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.007</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>průřez zásypu 3.61 m² (řez A-A) × délka 6.5 m = 23.5 m³</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.008</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>délka jako prefa stěna ≈ 6.35 m; Ø ~150 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.009</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>délka 6010 mm; Ø 120-130 mm (měřeno z řezu, nepopsáno)</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV1.010</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr"/>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-2 Základové a ŽB  (7 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E14" s="19" t="n">
         <v>4.84</v>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>0.5 × 0.5 × 19.4 obvod = 4.85</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV2.001</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 7 ks</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>DXF: 7 ks (rozteč 1000 mm × 7000 mm parking délka)</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>273313811</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.002</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr"/>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 7 ks</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>7 ks (= spodní)</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>311233812</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Dvoustupňové patky pro IPE180 — horní část z t)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="F13" s="18">
-        <f> montáž × 1.03</f>
-        <v/>
-      </c>
-      <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.003</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>HSV-2 Základové a ŽB</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>patky horní (0.3×0.3×0.5×7) + zídka (odhad ~1 m³)</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>273321321</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV2.004</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
@@ -18441,42 +18462,38 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>174101101</t>
+          <t>6 ks (výkres D.1.1.02 — 6 štvercových patek pod IPE180)</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>273313811</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>✓ verified</t>
+          <t>⚠ kandidát-verify</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV2.005</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.HSV2.002</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
@@ -18494,25 +18511,25 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Montáž — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+          <t>6 ks (= spodní, výkres D.1.1.02)</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -18522,67 +18539,90 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV2.006</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.HSV2.003</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+          <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>━━ HSV-3 Svislé konstrukce  (8 atomic operací) ━━</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+      <c r="A17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Dvoustupňové patky pro IPE180 — horní část z t)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F17" s="18">
+        <f> montáž × 1.03</f>
+        <v/>
+      </c>
+      <c r="G17" s="18" t="inlineStr"/>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.003</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr"/>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>18</v>
+        <v>1.75</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
+          <t>patky horní (0.3×0.3×0.5×6 = 0.27) + věnec nad patkami 2 řady ztrac.bednění (0.5 v × 6.35 d × 0.3 š = 0.95) + zídka lemující (~0.5) = ~1.72 ≈ 1.75 m³</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -18592,14 +18632,10 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>260217_sklad.HSV3.001</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>S04_sklad</t>
-        </is>
-      </c>
+          <t>260217_sklad.HSV2.004</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
@@ -18608,251 +18644,230 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>174101101</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>✓ verified</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.005</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>S01_sklad, S05_sklad</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>odhad 3 m schodů × 0.8 × 0.30 = 0.72 (ručně)</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV2.006</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>━━ HSV-3 Svislé konstrukce  (8 atomic operací) ━━</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m²; blok 1800×600 mm (výkres D.1.1.02/03: délka 1800, 5 řad × 600 výška = 3000) → 3 celé (1800×3=5400) + 1 kus 950 mm na řadu, vazba na zámek; 5 řad × ~3.5 bloku ≈ 18 ks</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>311233815</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.001</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>S04_sklad</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Montáž — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>obvod 19.4 m × výška 2.4 m = 46.6</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="E23" s="12" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>3 strany trapézu (6010-1000 dveře)+(7000-600 prefa)+(7033-600 prefa)=17843 mm = 17.84 m × výška 14 řad×0.25 = 3.5 m = 62.5 m²</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>311233811</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.002</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu — tvarovky ztraceného be)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F20" s="18">
-        <f> montáž 1:1</f>
-        <v/>
-      </c>
-      <c r="G20" s="18" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.002</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Pronájem.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>1398</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>46.6 × 30 kg/m² = 1398</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>273361821</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.003</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka betonářské oceli B500B (Výztuž B500B do tvarovek ztraceného bednění (~)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>1398</v>
-      </c>
-      <c r="F22" s="18">
-        <f> montáž 1:1</f>
-        <v/>
-      </c>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.003</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>HSV-3 Svislé konstrukce</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>33</v>
-      </c>
-      <c r="F23" s="18">
-        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
-        <v/>
-      </c>
-      <c r="G23" s="18" t="inlineStr"/>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S04_sklad</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -18867,460 +18882,456 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
+          <t>Dodávka — Pronájem bednění (Obvodové stěny skladu S03a/b — tvarovky ztrace)</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F24" s="18">
+        <f> montáž 1:1</f>
+        <v/>
+      </c>
+      <c r="G24" s="18" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.002</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Pronájem.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Montáž — Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>62.5 m² × 30 kg/m² (zalití C25/30) = 1875 kg</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>273361821</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.003</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka betonářské oceli B500B (Výztuž B500B do tvarovek ztraceného bednění (~)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F26" s="18">
+        <f> montáž 1:1</f>
+        <v/>
+      </c>
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.003</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 0 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F27" s="18">
+        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004 → HSV3.004a</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>Penetrace.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
           <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E28" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F28" s="18">
         <f> 33 m² (2 vrstvy ve spotřebě)</f>
         <v/>
       </c>
-      <c r="G24" s="18" t="inlineStr"/>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.004 → HSV3.004b</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>HI + protiradon (711). Materiál 2×4mm.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>Drenážní nopová folie 20 mm — dodávka+montáž, stěny pod terénem (S03a+S04)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E29" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F29" s="18">
         <f> 33 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="G25" s="18" t="inlineStr"/>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I25" s="18" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV3.005 → HSV3.005a</t>
         </is>
       </c>
-      <c r="J25" s="18" t="inlineStr">
+      <c r="J29" s="18" t="inlineStr">
         <is>
           <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
-      <c r="K25" s="18" t="inlineStr">
+      <c r="K29" s="18" t="inlineStr">
         <is>
           <t>Drenáž nopová folie (711).  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>━━ HSV-4 Vodorovné  (10 atomic operací) ━━</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Montáž — Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="E31" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>10 ks (počítáno na výkrese D.1.1.02, rozteč 625 mm po 5850) × 3.1 m rozpon = 31 bm</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>762341110</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.001</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Montáž (práce).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>Dodávka — Dodávka řeziva C24 (impregnované) (Dřevěné stropnice 100/160 mm á 625 mm primární)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>bm</t>
         </is>
       </c>
-      <c r="E28" s="19" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="F28" s="18">
+      <c r="E32" s="19" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F32" s="18">
         <f> montáž × 1.10</f>
         <v/>
       </c>
-      <c r="G28" s="18" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr"/>
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>❌ blank — ÚRS online</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.001</t>
         </is>
       </c>
-      <c r="J28" s="18" t="inlineStr">
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K28" s="18" t="inlineStr">
+      <c r="K32" s="18" t="inlineStr">
         <is>
           <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="F29" s="11">
-        <f> 21.2 m² strop skladu</f>
-        <v/>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="E33" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>strop skladu nad trámy = 5.85 × 3.1 = 18.1 m² (báze 10 trámů)</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>762331110</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.002</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>22.26945</v>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>21.2 × 1.05 přesah</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>712331101</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka folie/pásu (Hydroizolační střešní souvrství skladu (modifi)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F31" s="18">
-        <f> montáž × 1.10</f>
-        <v/>
-      </c>
-      <c r="G31" s="18" t="inlineStr"/>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.003</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>921</v>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>411321414</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>⚠ kandidát-verify</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.004</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Montáž (práce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Sekundární zastřešení parkingu — IPE180 v rozt)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="n">
-        <v>948.63</v>
-      </c>
-      <c r="F33" s="18">
-        <f> montáž × 1.03</f>
-        <v/>
-      </c>
-      <c r="G33" s="18" t="inlineStr"/>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>❌ blank — ÚRS online</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>260217_sklad.HSV4.004</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="K33" s="18" t="inlineStr">
-        <is>
-          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
         </is>
       </c>
     </row>
@@ -19335,433 +19346,513 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>Montáž — Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>18.1 × 1.05 přesah = 19.0 m²</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>712331101</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.003</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka folie/pásu (Hydroizolační střešní souvrství skladu (modifi)</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F35" s="18">
+        <f> montáž × 1.10</f>
+        <v/>
+      </c>
+      <c r="G35" s="18" t="inlineStr"/>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.003</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K35" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 10 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Montáž — Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>790</v>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>6 ks IPE180 × 7.0 m × 18.8 kg/m = 789.6 → 790 kg (výkres D.1.1.02: 6 nosníků)</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>411321414</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>⚠ kandidát-verify</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>Montáž (práce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Dodávka — Dodávka oceli S235 (válcované profily) (Sekundární zastřešení parkingu — IPE180 v rozt)</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>813.7</v>
+      </c>
+      <c r="F37" s="18">
+        <f> montáž × 1.03</f>
+        <v/>
+      </c>
+      <c r="G37" s="18" t="inlineStr"/>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>❌ blank — ÚRS online</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV4.004</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>Materiál (dodávka). Ztratné 3 %.  Doplnit leaf z CS ÚRS online (app.urs.cz, cen. úroveň 2026 01) dle família + popis + Vzorec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
           <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E38" s="12" t="n">
         <v>44.6</v>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
         </is>
       </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>411321515</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.005</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>Carried 1:1 (atomic / komplet / služba — no split)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Montáž — Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
-        <v>1551</v>
-      </c>
-      <c r="F35" s="11">
-        <f> hmotnost IPE180 (921 kg) + odhad pororoštů (21 m² × 30 kg/m²) = ~1551</f>
-        <v/>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="E39" s="12" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>IPE 790 kg + pororošt 630 kg = 1420 kg žárově zinkováno (IPE 6 ks)</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>783201001</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>⚠ kandidát-verify</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>260217_sklad.HSV4.006</t>
         </is>
       </c>
-      <c r="J35" s=